--- a/tools/excel/pci-dss/pcidss-4_0.xlsx
+++ b/tools/excel/pci-dss/pcidss-4_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\pci-dss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890D3021-4CFE-409F-B9CE-6AA307E0D530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464575E1-C45A-4BD9-81FB-3436128585DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="-15870" windowWidth="25440" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="-15750" windowWidth="12570" windowHeight="15855" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -243,11 +243,6 @@
     <t>1.3.1</t>
   </si>
   <si>
-    <t>Inbound traffic to the CDE is restricted as follows:
-• To only traffic that is necessary,
-• All other traffic is specifically denied.</t>
-  </si>
-  <si>
     <t>1.3.2</t>
   </si>
   <si>
@@ -327,12 +322,6 @@
   </si>
   <si>
     <t>1.5.1</t>
-  </si>
-  <si>
-    <t>Security controls are implemented on any computing devices, including company- and employee-owned devices, that connect to both untrusted networks (including the Internet) and the CDE as follows.
-• Specific configuration settings are defined to prevent threats being introduced into the entity’s network.
-• Security controls are actively running.
-• Security controls are not alterable by users of the computing devices unless specifically documented and authorized by management on a case-by-case basis for a limited period.</t>
   </si>
   <si>
     <t>2</t>
@@ -493,17 +482,7 @@
     <t>3.1</t>
   </si>
   <si>
-    <t>Processes and mechanisms for performing activities in Requirement 3 are defined and understood.</t>
-  </si>
-  <si>
     <t>3.1.1</t>
-  </si>
-  <si>
-    <t>All security policies and operational procedures that are identified in Requirement 3 are:
-•	Documented.
-•	Kept up to date.
-•	In use.
-•	Known to all affected parties.</t>
   </si>
   <si>
     <t>3.1.2</t>
@@ -533,9 +512,6 @@
     <t>3.3</t>
   </si>
   <si>
-    <t>Sensitive authentication data is not stored after authorization.</t>
-  </si>
-  <si>
     <t>3.3.1</t>
   </si>
   <si>
@@ -598,27 +574,13 @@
     <t>3.5</t>
   </si>
   <si>
-    <t>PAN is secured wherever it is stored.</t>
-  </si>
-  <si>
     <t>3.5.1</t>
   </si>
   <si>
-    <t>PAN is rendered unreadable anywhere it is stored by using any of the following approaches:
-• One-way hashes based on strong cryptography of the entire PAN.
-• Truncation (hashing cannot be used to replace the truncated segment of PAN).
-• Index tokens.
-• Strong cryptography with associated key-management processes and procedures.
-• Where hashed and truncated versions of the same PAN, or different truncation formats of the same PAN, are present in an environment, additional controls are in place to ensure that the different versions cannot be correlated to reconstruct the original PAN.</t>
-  </si>
-  <si>
     <t>3.5.2</t>
   </si>
   <si>
     <t>3.5.1.1</t>
-  </si>
-  <si>
-    <t>Hashes used to render PAN unreadable (per the first bullet of Requirement 3.5.1), are keyed cryptographic hashes of the entire PAN, with associated key-management processes and procedures in accordance with Requirements 3.6 and 3.7.</t>
   </si>
   <si>
     <t>3.5.3</t>
@@ -640,12 +602,6 @@
     <t>3.5.1.3</t>
   </si>
   <si>
-    <t>If disk-level or partition-level encryption is used (rather than file-, column-, or field--level database encryption) to render PAN unreadable, it is managed as follows:,
-•	Logical access is managed separately and independently of native operating system authentication and access control mechanisms.
-•	Decryption keys are not associated with user accounts.
-•	Authentication factors (passwords, passphrases, or cryptographic keys) that allow access to unencrypted data are stored securely.</t>
-  </si>
-  <si>
     <t>3.6</t>
   </si>
   <si>
@@ -744,9 +700,6 @@
     <t>3.7.6</t>
   </si>
   <si>
-    <t>Where manual cleartext cryptographic key-management operations are performed by personnel, key-management policies and procedures are implemented including managing these operations using split knowledge and dual control.</t>
-  </si>
-  <si>
     <t>3.7.7</t>
   </si>
   <si>
@@ -771,26 +724,13 @@
     <t>Requirement 4</t>
   </si>
   <si>
-    <t>Protect Cardholder Data with Strong Cryptography During Transmission</t>
-  </si>
-  <si>
     <t>Exigence 4</t>
   </si>
   <si>
     <t>4.1</t>
   </si>
   <si>
-    <t>Processes and mechanisms for performing activities in Requirement 4 are defined and understood.</t>
-  </si>
-  <si>
     <t>4.1.1</t>
-  </si>
-  <si>
-    <t>All security policies and operational procedures that are identified in Requirement 4 are:
-• Documented
-• Kept up to date
-• In use
-• Known to all affected parties</t>
   </si>
   <si>
     <t>4.1.2</t>
@@ -821,9 +761,6 @@
     <t>4.2.1.1</t>
   </si>
   <si>
-    <t>An inventory of the entity’s trusted keys and certificates is maintained.</t>
-  </si>
-  <si>
     <t>4.2.1.2</t>
   </si>
   <si>
@@ -870,13 +807,6 @@
   </si>
   <si>
     <t>5.1.1</t>
-  </si>
-  <si>
-    <t>All security policies and operational procedures that are identified in Requirement 5 are:
-• Documented
-• Kept up to date
-• In use
-• Known to all affected parties</t>
   </si>
   <si>
     <t>5.1.2</t>
@@ -953,12 +883,6 @@
   </si>
   <si>
     <t>5.3.2</t>
-  </si>
-  <si>
-    <t>The anti-malware solution(s):
-• Performs periodic scans and active or real-time scans
-OR
-• Performs continuous behavioral analysis of systems or processes.</t>
   </si>
   <si>
     <t>5.3.2.1</t>
@@ -1043,14 +967,7 @@
     <t>6.1.2</t>
   </si>
   <si>
-    <t>Roles and responsibilities for performing activities in Requirement 6 are documented, assigned, and understood.
-New requirement - effective immediately</t>
-  </si>
-  <si>
     <t>6.2</t>
-  </si>
-  <si>
-    <t>Bespoke and custom software is developed securely.</t>
   </si>
   <si>
     <t>Les logiciels sur mesure et personnalisés sont développés de manière sécurisée.</t>
@@ -1068,16 +985,6 @@
     <t>6.2.2</t>
   </si>
   <si>
-    <t>Software development personnel working on bespoke and custom software are trained at least once every 12 months as follows:
-• On software security relevant to their job function and development languages.
-• Including secure software design and secure coding techniques.
-• Including, if security testing tools are used, how to use the tools for detecting vulnerabilities in software.
-Applicability Notes:
-This requirement for code reviews applies to all bespoke and custom software (both internal and public facing), as part of the system development lifecycle.
-Public-facing web applications are also subject to additional controls, to address ongoing threats and vulnerabilities after implementation, as defined at PCI DSS Requirement 6.4.
-Code reviews may be performed using either manual or automated processes, or a combination of both.</t>
-  </si>
-  <si>
     <t>6.2.3</t>
   </si>
   <si>
@@ -1098,15 +1005,6 @@
     <t>6.2.4</t>
   </si>
   <si>
-    <t>Software engineering techniques or other methods are defined and in use by software development personnel to prevent or mitigate common software attacks and related vulnerabilities for bespoke and custom software, including but not limited to the following:
-• Injection attacks, including SQL, LDAP, XPath, or other command, parameter, object, fault, or injection-type flaws.
-• Attacks on data and data structures, including attempts to manipulate buffers, pointers, input data, or shared data.
-• Attacks on cryptography usage, including attempts to exploit weak, insecure, or inappropriate cryptographic implementations, algorithms, cipher suites, or modes of operation.
-• Attacks on business logic, including attempts to abuse or bypass application features and functionalities through the manipulation of APIs, communication protocols and channels, client-side functionality, or other system/application functions and resources. This includes cross-site scripting (XSS) and cross-site request forgery (CSRF).
-• Attacks on access control mechanisms, including attempts to bypass or abuse identification, authentication, or authorization mechanisms, or attempts to exploit weaknesses in the implementation of such mechanisms.
-• Attacks via any “high-risk” vulnerabilities identified in the vulnerability identification process, as defined in Requirement 6.3.1.</t>
-  </si>
-  <si>
     <t>6.3</t>
   </si>
   <si>
@@ -1117,13 +1015,6 @@
   </si>
   <si>
     <t>6.3.1</t>
-  </si>
-  <si>
-    <t>Security vulnerabilities are identified and managed as follows:
-• New security vulnerabilities are identified using industry-recognized sources for security vulnerability information, including alerts from international and national computer emergency response teams (CERTs).
-• Vulnerabilities are assigned a risk ranking based on industry best practices and consideration of potential impact.
-• Risk rankings, at a minimum, identify all vulnerabilities considered to be a high-risk or critical to the environment.
-• Vulnerabilities for bespoke and custom, and third-party software (for example operating systems and databases) are covered.</t>
   </si>
   <si>
     <t>6.3.2</t>
@@ -1150,22 +1041,6 @@
   </si>
   <si>
     <t>6.4.1</t>
-  </si>
-  <si>
-    <t>For public-facing web applications, new threats and vulnerabilities are addressed on an ongoing basis and these applications are protected against known attacks as follows:
-• Reviewing public-facing web applications via manual or automated application vulnerability security assessment tools or methods as follows:
-• At least once every 12 months and after significant changes.
-• By an entity that specializes in application security.
-• Including, at a minimum, all common software attacks in Requirement 6.2.4.
-• All vulnerabilities are ranked in accordance with requirement 6.3.1.
-• All vulnerabilities are corrected.
-• The application is re-evaluated after the corrections.
-OR
-• Installing an automated technical solution(s) that continually detects and prevents web-based attacks as follows:
-• Installed in front of public-facing web applications to detect and prevent web-based attacks.
-• Actively running and up to date as applicable.
-• Generating audit logs.
-• Configured to either block web-based attacks or generate an alert that is immediately investigated.</t>
   </si>
   <si>
     <t>6.4.2</t>
@@ -1206,15 +1081,6 @@
     <t>6.5.1</t>
   </si>
   <si>
-    <t>Changes to all system components in the production environment are made according to established procedures that include:
-•	Reason for, and description of, the change.
-•	Documentation of security impact.
-•	Documented change approval by authorized parties.
-•	Testing to verify that the change does not adversely impact system security.
-•	For bespoke and custom software changes, all updates are tested for compliance with Requirement 6.2.4 before being deployed into production.
-•	Procedures to address failures and return to a secure state.</t>
-  </si>
-  <si>
     <t>6.5.2</t>
   </si>
   <si>
@@ -1285,13 +1151,6 @@
   </si>
   <si>
     <t>7.1.1</t>
-  </si>
-  <si>
-    <t>All security policies and operational procedures that are identified in Requirement 7 are:
-•	Documented,
-•	Kept up to date
-• In use
-•	Known to all affected parties.</t>
   </si>
   <si>
     <t>7.1.2</t>
@@ -1344,13 +1203,6 @@
     <t>7.2.4</t>
   </si>
   <si>
-    <t>All user accounts and related access privileges, including third-party/vendor accounts, are reviewed as follows:
-• At least once every six months
-• To ensure user accounts and access remain appropriate based on job function.
-• Any inappropriate access is addressed.
-• Management acknowledges that access remains appropriate.</t>
-  </si>
-  <si>
     <t>7.2.5</t>
   </si>
   <si>
@@ -1362,13 +1214,6 @@
     <t>7.2.5.1</t>
   </si>
   <si>
-    <t>All access by application and system accounts and related access privileges are reviewed as follows:
-• Periodically (at the frequency defined in the entity’s targeted risk analysis, which is performed according to all elements specified in Requirement 12.3.1).
-• The application/ system access remains appropriate for the function being performed.
-• Any inappropriate access is addressed.
-• Management acknowledges that access remains appropriate.</t>
-  </si>
-  <si>
     <t>7.2.6</t>
   </si>
   <si>
@@ -1380,9 +1225,6 @@
     <t>7.3</t>
   </si>
   <si>
-    <t>Logical access to system components and data is managed via an access control system(s).</t>
-  </si>
-  <si>
     <t>7.3.1</t>
   </si>
   <si>
@@ -1392,9 +1234,6 @@
     <t>7.3.2</t>
   </si>
   <si>
-    <t>The access control system(s) is configured to enforce privileges assigned to individuals, applications, and systems based on job classification and function.</t>
-  </si>
-  <si>
     <t>Le ou les systèmes de contrôle d'accès sont configurés pour appliquer les autorisations attribuées aux personnes, aux applications et aux systèmes sur la base de la classification et la fonction des tâches.</t>
   </si>
   <si>
@@ -1420,9 +1259,6 @@
   </si>
   <si>
     <t>8.1</t>
-  </si>
-  <si>
-    <t>Processes and mechanisms to perform activities in Requirement 8 are defined and understood.</t>
   </si>
   <si>
     <t>8.1.1</t>
@@ -1485,9 +1321,6 @@
     <t>8.2.5</t>
   </si>
   <si>
-    <t>Access for terminated users is immediately revoked</t>
-  </si>
-  <si>
     <t>8.2.6</t>
   </si>
   <si>
@@ -1577,13 +1410,6 @@
     <t>8.3.8</t>
   </si>
   <si>
-    <t>Authentication policies and procedures are documented and communicated to all users including:
-• Guidance on selecting strong authentication factors.
-•	Guidance for how users should protect their authentication factors.
-•	Instructions not to reuse previously used passwords/passphrases.
-•	Instructions to change passwords/passphrases if there is any suspicion or knowledge that the password/passphrases have been compromised and how to report the incident.</t>
-  </si>
-  <si>
     <t>8.3.9</t>
   </si>
   <si>
@@ -1621,9 +1447,6 @@
     <t>8.4</t>
   </si>
   <si>
-    <t>Multi-factor authentication (MFA) systems are configured to prevent misuse.</t>
-  </si>
-  <si>
     <t>8.4.1</t>
   </si>
   <si>
@@ -1651,17 +1474,7 @@
     <t>8.5.1</t>
   </si>
   <si>
-    <t>MFA systems are implemented as follows:
-•	The MFA system is not susceptible to replay attacks.
-•	MFA systems cannot be bypassed by any users, including administrative users unless specifically documented, and authorized by management on an exception basis, for a limited time period.
-•	At least two different types of authentication factors are used.
-•	Success of all authentication factors is required before access is granted.</t>
-  </si>
-  <si>
     <t>8.6</t>
-  </si>
-  <si>
-    <t>Use of application and system accounts and associated authentication factors are strictly managed.</t>
   </si>
   <si>
     <t>8.6.1</t>
@@ -1679,9 +1492,6 @@
     <t>8.6.2</t>
   </si>
   <si>
-    <t>Passwords/passphrases for any application and system accounts that can be used for interactive login are not hard coded in scripts, configuration/property files, or bespoke and custom source code. Note: stored passwords/ passphrases are required to be encrypted in accordance with PCI DSS Requirement 8.3.2.</t>
-  </si>
-  <si>
     <t>8.6.3</t>
   </si>
   <si>
@@ -1706,9 +1516,6 @@
   </si>
   <si>
     <t>9.1</t>
-  </si>
-  <si>
-    <t>Processes and mechanisms for performing activities in Requirement 9 are defined and understood.</t>
   </si>
   <si>
     <t>9.1.1</t>
@@ -1730,9 +1537,6 @@
     <t>9.2</t>
   </si>
   <si>
-    <t>Physical access controls manage entry into the cardholder data environment.</t>
-  </si>
-  <si>
     <t>9.2.1</t>
   </si>
   <si>
@@ -1780,9 +1584,6 @@
     <t>9.3</t>
   </si>
   <si>
-    <t>Physical access to the cardholder data environment for personnel and visitors is authorized and managed.</t>
-  </si>
-  <si>
     <t>9.3.1</t>
   </si>
   <si>
@@ -1993,9 +1794,6 @@
   </si>
   <si>
     <t>10.1</t>
-  </si>
-  <si>
-    <t>Processes and mechanisms for performing activities in Requirement 10 are defined and understood.</t>
   </si>
   <si>
     <t>10.1.1</t>
@@ -2280,17 +2078,6 @@
   </si>
   <si>
     <t>10.7.1</t>
-  </si>
-  <si>
-    <t>Additional requirement for service providers only: Failures of critical security control systems are detected, alerted, and addressed promptly, including but not limited to failure of the following critical security control systems:
-• Network security controls
-• IDS/IPS
-• FIM
-• Anti-malware solutions
-• Physical access controls
-• Logical access controls
-• Audit logging mechanisms
-• Segmentation controls (if used)</t>
   </si>
   <si>
     <t>10.7.2</t>
@@ -2340,9 +2127,6 @@
     <t>11.1</t>
   </si>
   <si>
-    <t>Processes and mechanisms for performing activities in Requirement 11 are defined and understood.</t>
-  </si>
-  <si>
     <t>11.1.1</t>
   </si>
   <si>
@@ -2410,12 +2194,6 @@
   </si>
   <si>
     <t>11.3.1.2</t>
-  </si>
-  <si>
-    <t>Internal vulnerability scans are performed via authenticated scanning as follows:
-• Systems that are unable to accept credentials for authenticated scanning are documented.
-• Sufficient privileges are used, for those systems that accept credentials for scanning.
-• If accounts used for authenticated scanning can be used for interactive login, they are managed in accordance with Requirement 8.2.2.</t>
   </si>
   <si>
     <t>11.3.1.3</t>
@@ -2470,14 +2248,6 @@
     <t>11.4.2</t>
   </si>
   <si>
-    <t>Internal penetration testing is performed:
-• Per the entity’s defined methodology
-• At least once every 12 months
-• After any significant infrastructure or application upgrade or change
-• By a qualified internal resource or qualified external third-party
-• Organizational independence of the tester exists (not required to be a QSA or ASV).</t>
-  </si>
-  <si>
     <t>11.4.3</t>
   </si>
   <si>
@@ -2490,11 +2260,6 @@
   </si>
   <si>
     <t>11.4.4</t>
-  </si>
-  <si>
-    <t>Exploitable vulnerabilities and security weaknesses found during penetration testing are corrected as follows:
-• In accordance with the entity’s assessment of the risk posed by the security issue as defined in Require ment 6.3.1.
-• Penetration testing is repeated to verify the corrections.</t>
   </si>
   <si>
     <t>11.4.5</t>
@@ -2526,9 +2291,6 @@
     <t>11.4.7</t>
   </si>
   <si>
-    <t>Additional requirement for third-party hosted/cloud service providers only: Third-party hosted/cloud service providers support to their customers for external penetration testing per Requirement 11.4.3 and 11.4.4.</t>
-  </si>
-  <si>
     <t>11.5</t>
   </si>
   <si>
@@ -2557,11 +2319,6 @@
     <t>11.5.2</t>
   </si>
   <si>
-    <t>A change-detection mechanism (for example, file integrity monitoring tools) is deployed as follows:
-• To alert personnel to unauthorized modification (including changes, additions, and deletions) of critical files
-• To perform critical file comparisons at least once weekly.</t>
-  </si>
-  <si>
     <t>Un mécanisme de détection des modifications (par exemple, des outils de surveillance de l'intégrité des fichiers) est déployé de la façon suivante :
 • Pour alerter le personnel de modifications non autorisées (y compris les modifications, les ajouts et les suppressions) de fichiers critiques
 • Pour effectuer des comparaisons de fichiers critiques au moins une fois par semaine.</t>
@@ -2579,15 +2336,6 @@
     <t>11.6.1</t>
   </si>
   <si>
-    <t>A change- and tamper-detection mechanism is deployed as follows:
-• To alert personnel to unauthorized modification (including indicators of compromise, changes, additions, and deletions) to the security-impacting HTTP headers and the script contents of payment pages as received by the consumer browser.
-• The mechanism is configured to evaluate the received HTTP header and payment pages.
-• The mechanism functions are performed as follows:
-- At least once weeky,
-OR
-- Periodically (at the frequency defined in the entity’s targeted risk analysis, which is performed according to all elements specified in Requirement 12.3.1).</t>
-  </si>
-  <si>
     <t>Maintain an Information Security Policy</t>
   </si>
   <si>
@@ -2598,9 +2346,6 @@
   </si>
   <si>
     <t>Requirement 12</t>
-  </si>
-  <si>
-    <t>Support information security with organizational policies and programs</t>
   </si>
   <si>
     <t>Exigence 12</t>
@@ -2633,9 +2378,6 @@
     <t>12.1.3</t>
   </si>
   <si>
-    <t>The security policy clearly defines information security roles and responsibilities for all personnel, and all personnel are aware and acknowledge their information security responsibilities.</t>
-  </si>
-  <si>
     <t>12.1.4</t>
   </si>
   <si>
@@ -2661,9 +2403,6 @@
   </si>
   <si>
     <t>12.3</t>
-  </si>
-  <si>
-    <t>Targeted risks to the cardholder data environment are formally identified, evaluated, and managed.</t>
   </si>
   <si>
     <t>Les risques pour l'environnement des données des titulaires de cartes sont formellement identifiés, évalués et gérés.</t>
@@ -2684,12 +2423,6 @@
     <t>12.3.2</t>
   </si>
   <si>
-    <t>A targeted risk analysis is performed for each PCI DSS requirement that the entity meets with the customized approach, to include:
-• Documented evidence detailing each element specified in Appendix B: Guidance and Instructions for Using Customized Approach (including, at a minimum, a controls matrix and risk analysis).
-• Approval of documented evidence by senior management.
-• Performance of the targeted analysis of risk at least once every 12 months.</t>
-  </si>
-  <si>
     <t>12.3.3</t>
   </si>
   <si>
@@ -2727,14 +2460,6 @@
   </si>
   <si>
     <t>12.4.2</t>
-  </si>
-  <si>
-    <t>Additional requirement for service providers only: Reviews are performed at least once every three months to confirm personnel are performing their tasks in accordance with all security policies and all operational procedures. Reviews are performed by personnel other than those responsible for performing the given task and include, but not limited to, the following tasks:
-• Daily log reviews.
-• Configuration reviews for network security controls.
-• Applying configuration standards to new systems.
-• Responding to security alerts.
-• Change-management processes.</t>
   </si>
   <si>
     <t>12.4.2.1</t>
@@ -2774,9 +2499,6 @@
     <t>12.5.2.1</t>
   </si>
   <si>
-    <t>Additional requirement for service providers only: PCI DSS scope is documented and confirmed by the entity at least once every six months and after significant changes. At a minimum, the scoping validation includes all the elements specified in Requirement 12.5.2.</t>
-  </si>
-  <si>
     <t>12.5.3</t>
   </si>
   <si>
@@ -2790,9 +2512,6 @@
   </si>
   <si>
     <t>12.6.1</t>
-  </si>
-  <si>
-    <t>A formal security awareness program is implemented to make all personnel aware of the entity’s information security policy and procedures and their role in protecting the cardholder data.</t>
   </si>
   <si>
     <t>12.6.2</t>
@@ -2953,9 +2672,6 @@
     <t>12.10.4.1</t>
   </si>
   <si>
-    <t>The frequency of periodic training for incident response personnel is defined in the entity’s targeted risk analysis which is performed according to all elements specified in Requirement 12.3.1.</t>
-  </si>
-  <si>
     <t>12.10.5</t>
   </si>
   <si>
@@ -3016,9 +2732,6 @@
     <t>A1.1</t>
   </si>
   <si>
-    <t>Multi-tenant service providers protect and segregate all customer environments and data.</t>
-  </si>
-  <si>
     <t>A1.1.1</t>
   </si>
   <si>
@@ -3082,9 +2795,6 @@
     <t>Appendix A2</t>
   </si>
   <si>
-    <t>Additional PCI DSS Requirements for Entities using SSL/Early TLS for Card-Present POS POI Terminal Connections</t>
-  </si>
-  <si>
     <t>Annexe A2</t>
   </si>
   <si>
@@ -3225,17 +2935,6 @@
   </si>
   <si>
     <t>A3.5.1</t>
-  </si>
-  <si>
-    <t>PCI DSS scope is documented and confirmed for accuracy at least once every three months and upon significant changes to the in- scope environment. At a minimum, the scoping validation includes: 
-• Identifying all data flows for the various payment stages (for example, authorization, capture, settlement, chargebacks, and refunds) and acceptance channels (for example, card- present, card-not-present, and e-commerce). 
-• Updating all data-flow diagrams per Requirement 1.2.4. 
-• Identifying all locations where account data is stored, processed, and transmitted, including but not limited to 1) any locations outside of the currently defined CDE, 2) applications that process CHD, 3) transmissions between systems and networks, and 4) file backups. 
-• For any account data found outside of the currently defined CDE, either 1) securely delete it, 2) migrate it into the currently defined CDE, or 3) expand the currently defined CDE to include it. 
-• Identifying all system components in the CDE, connected to the CDE, or that could impact security of the CDE.
-• Identifying all segmentation controls in use and the environment(s) from which the CDE is segmented, including justification for environments being out of scope 
-• Identifying all connections to third-party entities with access to the CDE. 
-• Confirming that all identified data flows, account data, system components, segmentation controls, and connections from third parties with access to the CDE are included in scope.</t>
   </si>
   <si>
     <t>PCI DSS scope impact for all changes to systems or networks is determined, including additions of new systems and new network connections. Processes include: 
@@ -3334,9 +3033,6 @@
   </si>
   <si>
     <t>Logical access to the cardholder data environment is controlled and managed.</t>
-  </si>
-  <si>
-    <t>User accounts and access privileges to in- scope system components are reviewed at least once every six months to ensure user accounts and access privileges remain appropriate based on job function, and that all access is authorized.</t>
   </si>
   <si>
     <t>Suspicious events are identified and responded to.</t>
@@ -4688,6 +4384,306 @@
 • L’identification des anomalies ou activités suspectes au moment où elles se produisent.
 • L’émission rapide d’alertes en cas de détection d’une activité suspecte ou d’une anomalie, à destination du personnel responsable.
 • La réponse aux alertes conformément aux procédures de réponse documentées.</t>
+  </si>
+  <si>
+    <t>Processes and mechanisms for protecting stored account data are defined and understood.</t>
+  </si>
+  <si>
+    <t>Inbound traffic to the CDE is restricted as follows:
+• To only traffic that is necessary.
+• All other traffic is specifically denied.</t>
+  </si>
+  <si>
+    <t>Security controls are implemented on any computing devices, including company- and employee-owned devices, that connect to both untrusted networks (including the Internet) and the CDE as follows:
+• Specific configuration settings are defined to prevent threats being introduced into the entity’s network.
+• Security controls are actively running.
+• Security controls are not alterable by users of the computing devices unless specifically documented and authorized by management on a case-by-case basis for a limited period.</t>
+  </si>
+  <si>
+    <t>All security policies and operational procedures that are identified in Requirement 3 are:
+• Documented.
+• Kept up to date.
+• In use.
+• Known to all affected parties.</t>
+  </si>
+  <si>
+    <t>Sensitive authentication data (SAD) is not stored after authorization.</t>
+  </si>
+  <si>
+    <t>Primary account number (PAN) is secured wherever it is stored.</t>
+  </si>
+  <si>
+    <t>PAN is rendered unreadable anywhere it is stored by using any of the following approaches:
+• One-way hashes based on strong cryptography of the entire PAN.
+• Truncation (hashing cannot be used to replace the truncated segment of PAN).
+	– If hashed and truncated versions of the same PAN, or different truncation formats of the same PAN, are present in an environment, additional controls are in place such that the different versions cannot be correlated to reconstruct the original PAN.
+• Index tokens.
+• Strong cryptography with associated key-management processes and procedures.</t>
+  </si>
+  <si>
+    <t>Hashes used to render PAN unreadable (per the first bullet of Requirement 3.5.1) are keyed cryptographic hashes of the entire PAN, with associated key-management processes and procedures in accordance with Requirements 3.6 and 3.7.</t>
+  </si>
+  <si>
+    <t>If disk-level or partition-level encryption is used (rather than file-, column-, or field--level database encryption) to render PAN unreadable, it is managed as follows:
+• Logical access is managed separately and independently of native operating system authentication and access control mechanisms.
+• Decryption keys are not associated with user accounts.
+• Authentication factors (passwords, passphrases, or cryptographic keys) that allow access to unencrypted data are stored securely.</t>
+  </si>
+  <si>
+    <t>Where manual cleartext cryptographic key-management operations are performed by personnel, key-management policies and procedures are implemented, including managing these operations using split knowledge and dual control.</t>
+  </si>
+  <si>
+    <t>Protect Cardholder Data with Strong Cryptography During Transmission Over Open, Public Networks</t>
+  </si>
+  <si>
+    <t>Processes and mechanisms for protecting cardholder data with strong cryptography during transmission over open, public networks are defined and understood.</t>
+  </si>
+  <si>
+    <t>All security policies and operational procedures that are identified in Requirement 4 are:
+• Documented.
+• Kept up to date.
+• In use.
+• Known to all affected parties.</t>
+  </si>
+  <si>
+    <t>An inventory of the entity’s trusted keys and certificates used to protect PAN during transmission is maintained.</t>
+  </si>
+  <si>
+    <t>All security policies and operational procedures that are identified in Requirement 5 are:
+• Documented.
+• Kept up to date.
+• In use.
+• Known to all affected parties.</t>
+  </si>
+  <si>
+    <t>The anti-malware solution(s):
+• Performs periodic scans and active or real-time scans.
+OR
+• Performs continuous behavioral analysis of systems or processes.</t>
+  </si>
+  <si>
+    <t>Roles and responsibilities for performing activities in Requirement 6 are documented, assigned, and understood.</t>
+  </si>
+  <si>
+    <t>Bespoke and custom software are developed securely.</t>
+  </si>
+  <si>
+    <t>Software development personnel working on bespoke and custom software are trained at least once every 12 months as follows:
+• On software security relevant to their job function and development languages.
+• Including secure software design and secure coding techniques.
+• Including, if security testing tools are used, how to use the tools for detecting vulnerabilities in software.</t>
+  </si>
+  <si>
+    <t>Software engineering techniques or other methods are defined and in use by software development personnel to prevent or mitigate common software attacks and related vulnerabilities in bespoke and custom software, including but not limited to the following: 
+• Injection attacks, including SQL, LDAP, XPath, or other command, parameter, object, fault, or injection-type flaws. 
+• Attacks on data and data structures, including attempts to manipulate buffers, pointers, input data, or shared data. 
+• Attacks on cryptography usage, including attempts to exploit weak, insecure, or inappropriate cryptographic implementations, algorithms, cipher suites, or modes of operation. 
+• Attacks on business logic, including attempts to abuse or bypass application features and functionalities through the manipulation of APIs, communication protocols and channels, client-side functionality, or other system/application functions and resources. This includes cross-site scripting (XSS) and cross-site request forgery (CSRF). 
+• Attacks on access control mechanisms, including attempts to bypass or abuse identification, authentication, or authorization mechanisms, or attempts to exploit weaknesses in the implementation of such mechanisms. 
+• Attacks via any “high-risk” vulnerabilities identified in the vulnerability identification process, as defined in Requirement 6.3.1.</t>
+  </si>
+  <si>
+    <t>Security vulnerabilities are identified and managed as follows: 
+• New security vulnerabilities are identified using industry-recognized sources for security vulnerability information, including alerts from international and national computer emergency response teams (CERTs). 
+• Vulnerabilities are assigned a risk ranking based on industry best practices and consideration of potential impact. 
+• Risk rankings identify, at a minimum, all vulnerabilities considered to be a high-risk or critical to the environment. 
+• Vulnerabilities for bespoke and custom, and third-party software (for example operating systems and databases) are covered.</t>
+  </si>
+  <si>
+    <t>For public-facing web applications, new threats and vulnerabilities are addressed on an ongoing basis and these applications are protected against known attacks as follows:
+• Reviewing public-facing web applications via manual or automated application vulnerability security assessment tools or methods as follows:
+	- At least once every 12 months and after significant changes.
+	- By an entity that specializes in application security.
+	- Including, at a minimum, all common software attacks in Requirement 6.2.4.
+	- All vulnerabilities are ranked in accordance with requirement 6.3.1.
+	- All vulnerabilities are corrected.
+	- The application is re-evaluated after the corrections.
+OR
+• Installing an automated technical solution(s) that continually detects and prevents web-based attacks as follows:
+	- Installed in front of public-facing web applications to detect and prevent web-based attacks.
+	- Actively running and up to date as applicable.
+	- Generating audit logs.
+	- Configured to either block web-based attacks or generate an alert that is immediately investigated.</t>
+  </si>
+  <si>
+    <t>Changes to all system components in the production environment are made according to established procedures that include:
+• Reason for, and description of, the change.
+• Documentation of security impact.
+• Documented change approval by authorized parties.
+• Testing to verify that the change does not adversely impact system security.
+• For bespoke and custom software changes, all updates are tested for compliance with Requirement 6.2.4 before being deployed into production.
+• Procedures to address failures and return to a secure state.</t>
+  </si>
+  <si>
+    <t>All security policies and operational procedures that are identified in Requirement 7 are:
+• Documented.
+• Kept up to date.
+• In use.
+• Known to all affected parties.</t>
+  </si>
+  <si>
+    <t>All user accounts and related access privileges, including third-party/vendor accounts, are reviewed as follows:
+• At least once every six months.
+• To ensure user accounts and access remain appropriate based on job function.
+• Any inappropriate access is addressed.
+• Management acknowledges that access remains appropriate.</t>
+  </si>
+  <si>
+    <t>All access by application and system accounts and related access privileges are reviewed as follows:
+• Periodically (at the frequency defined in the entity’s targeted risk analysis, which is performed according to all elements specified in Requirement 12.3.1).
+• The application/system access remains appropriate for the function being performed.
+• Any inappropriate access is addressed.
+• Management acknowledges that access remains appropriate.</t>
+  </si>
+  <si>
+    <t>Access to system components and data is managed via an access control system(s).</t>
+  </si>
+  <si>
+    <t>The access control system(s) is configured to enforce permissions assigned to individuals, applications, and systems based on job classification and function.</t>
+  </si>
+  <si>
+    <t>Processes and mechanisms for identifying users and authenticating access to system components are defined and understood.</t>
+  </si>
+  <si>
+    <t>Access for terminated users is immediately revoked.</t>
+  </si>
+  <si>
+    <t>Authentication policies and procedures are documented and communicated to all users including:
+• Guidance on selecting strong authentication factors.
+• Guidance for how users should protect their authentication factors.
+• Instructions not to reuse previously used passwords/passphrases.
+• Instructions to change passwords/passphrases if there is any suspicion or knowledge that the password/passphrases have been compromised and how to report the incident.</t>
+  </si>
+  <si>
+    <t>Multi-factor authentication (MFA) is implemented to secure access into the CDE.</t>
+  </si>
+  <si>
+    <t>MFA systems are implemented as follows:
+• The MFA system is not susceptible to replay attacks.
+• MFA systems cannot be bypassed by any users, including administrative users unless specifically documented, and authorized by management on an exception basis, for a limited time period.
+• At least two different types of authentication factors are used.
+• Success of all authentication factors is required before access is granted.</t>
+  </si>
+  <si>
+    <t>Use of application and system accounts and associated authentication factors is strictly managed.</t>
+  </si>
+  <si>
+    <t>Passwords/passphrases for any application and system accounts that can be used for interactive login are not hard coded in scripts, configuration/property files, or bespoke and custom source code.
+Note: stored passwords/ passphrases are required to be encrypted in accordance with PCI DSS Requirement 8.3.2.</t>
+  </si>
+  <si>
+    <t>Processes and mechanisms for restricting physical access to cardholder data are defined and understood.</t>
+  </si>
+  <si>
+    <t>Physical access controls manage entry into facilities and systems containing cardholder data.</t>
+  </si>
+  <si>
+    <t>Physical access for personnel and visitors is authorized and managed.</t>
+  </si>
+  <si>
+    <t>Processes and mechanisms for logging and monitoring all access to system components and cardholder data are defined and understood.</t>
+  </si>
+  <si>
+    <t>Additional requirement for service providers only: Failures of critical security control systems are detected, alerted, and addressed promptly, including but not limited to failure of the following critical security control systems:
+• Network security controls.
+• IDS/IPS.
+• FIM.
+• Anti-malware solutions.
+• Physical access controls.
+• Logical access controls.
+• Audit logging mechanisms.
+• Segmentation controls (if used).</t>
+  </si>
+  <si>
+    <t>Processes and mechanisms for regularly testing security of systems and networks are defined and understood.</t>
+  </si>
+  <si>
+    <t>Internal vulnerability scans are performed via authenticated scanning as follows:
+• Systems that are unable to accept credentials for authenticated scanning are documented.
+• Sufficient privileges are used for those systems that accept credentials for scanning.
+• If accounts used for authenticated scanning can be used for interactive login, they are managed in accordance with Requirement 8.2.2.</t>
+  </si>
+  <si>
+    <t>Internal penetration testing is performed:
+• Per the entity’s defined methodology,
+• At least once every 12 months
+• After any significant infrastructure or application upgrade or change
+• By a qualified internal resource or qualified external third-party
+• Organizational independence of the tester exists (not required to be a QSA or ASV).</t>
+  </si>
+  <si>
+    <t>Exploitable vulnerabilities and security weaknesses found during penetration testing are corrected as follows:
+• In accordance with the entity’s assessment of the risk posed by the security issue as defined in Requirement 6.3.1.
+• Penetration testing is repeated to verify the corrections.</t>
+  </si>
+  <si>
+    <t>Additional requirement for multi-tenant service providers only: Multi-tenant service providers support their customers for external penetration testing per Requirement 11.4.3 and 11.4.4.</t>
+  </si>
+  <si>
+    <t>A change-detection mechanism (for example, file integrity monitoring tools) is deployed as follows:
+• To alert personnel to unauthorized modification (including changes, additions, and deletions) of critical files.
+• To perform critical file comparisons at least once weekly.</t>
+  </si>
+  <si>
+    <t>A change- and tamper-detection mechanism is deployed as follows:
+• To alert personnel to unauthorized modification (including indicators of compromise, changes, additions, and deletions) to the security-impacting HTTP headers and the script contents of payment pages as received by the consumer browser.
+• The mechanism is configured to evaluate the received HTTP header and payment pages.
+• The mechanism functions are performed as follows:
+	- At least once weeky,
+OR
+	- Periodically (at the frequency defined in the entity’s targeted risk analysis, which is performed according to all elements specified in Requirement 12.3.1).</t>
+  </si>
+  <si>
+    <t>Support Information Security with Organizational Policies and Programs</t>
+  </si>
+  <si>
+    <t>The security policy clearly defines information security roles and responsibilities for all personnel, and all personnel are aware of and acknowledge their information security responsibilities.</t>
+  </si>
+  <si>
+    <t>Risks to the cardholder data environment are formally identified, evaluated, and managed.</t>
+  </si>
+  <si>
+    <t>A targeted risk analysis is performed for each PCI DSS requirement that the entity meets with the customized approach, to include: 
+• Documented evidence detailing each element specified in Appendix D: Customized Approach (including, at a minimum, a controls matrix and risk analysis). 
+• Approval of documented evidence by senior management. 
+• Performance of the targeted analysis of risk at least once every 12 months.</t>
+  </si>
+  <si>
+    <t>Additional requirement for service providers only: Reviews are performed at least once every three months to confirm that personnel are performing their tasks in accordance with all security policies and operational procedures. Reviews are performed by personnel other than those responsible for performing the given task and include, but are not limited to, the following tasks:
+• Daily log reviews. 
+• Configuration reviews for network security controls. 
+• Applying configuration standards to new systems. 
+• Responding to security alerts. 
+• Change-management processes.</t>
+  </si>
+  <si>
+    <t>Additional requirement for service providers only: PCI DSS scope is documented and confirmed by the entity at least once every six months and upon significant change to the in-scope environment. At a minimum, the scoping validation includes all the elements specified in Requirement 12.5.2.</t>
+  </si>
+  <si>
+    <t>A formal security awareness program is implemented to make all personnel aware of the entity’s information security policy and procedures, and their role in protecting the cardholder data.</t>
+  </si>
+  <si>
+    <t>The frequency of periodic training for incident response personnel is defined in the entity’s targeted risk analysis, which is performed according to all elements specified in Requirement 12.3.1.</t>
+  </si>
+  <si>
+    <t>Multi-tenant service providers protect and separate all customer environments and data.</t>
+  </si>
+  <si>
+    <t>Additional PCI DSS Requirements for Entities Using SSL/Early TLS for Card-Present POS POI Terminal Connections</t>
+  </si>
+  <si>
+    <t>User accounts and access privileges to in-scope system components are reviewed at least once every six months to ensure user accounts and access privileges remain appropriate based on job function, and that all access is authorized.</t>
+  </si>
+  <si>
+    <t>PCI DSS scope is documented and confirmed for accuracy at least once every three months and upon significant changes to the in-scope environment. At a minimum, the scoping validation includes: 
+• Identifying all data flows for the various payment stages (for example, authorization, capture, settlement, chargebacks, and refunds) and acceptance channels (for example, card- present, card-not-present, and e-commerce). 
+• Updating all data-flow diagrams per Requirement 1.2.4. 
+• Identifying all locations where account data is stored, processed, and transmitted, including but not limited to 1) any locations outside of the currently defined CDE, 2) applications that process CHD, 3) transmissions between systems and networks, and 4) file backups. 
+• For any account data found outside of the currently defined CDE, either 1) securely delete it, 2) migrate it into the currently defined CDE, or 3) expand the currently defined CDE to include it. 
+• Identifying all system components in the CDE, connected to the CDE, or that could impact security of the CDE.
+• Identifying all segmentation controls in use and the environment(s) from which the CDE is segmented, including justification for environments being out of scope 
+• Identifying all connections to third-party entities with access to the CDE. 
+• Confirming that all identified data flows, account data, system components, segmentation controls, and connections from third parties with access to the CDE are included in scope.</t>
   </si>
 </sst>
 </file>
@@ -5615,7 +5611,7 @@
     <col min="3" max="3" width="9.44140625" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" customWidth="1"/>
     <col min="5" max="5" width="46" customWidth="1"/>
-    <col min="6" max="6" width="70.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="89.88671875" style="1" customWidth="1"/>
     <col min="7" max="7" width="53.5546875" customWidth="1"/>
     <col min="8" max="8" width="71.44140625" style="1" customWidth="1"/>
   </cols>
@@ -5701,7 +5697,7 @@
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="5" t="s">
-        <v>905</v>
+        <v>846</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -5721,7 +5717,7 @@
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="5" t="s">
-        <v>906</v>
+        <v>847</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5741,7 +5737,7 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="5" t="s">
-        <v>907</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -5761,7 +5757,7 @@
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="5" t="s">
-        <v>908</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -5781,7 +5777,7 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="5" t="s">
-        <v>909</v>
+        <v>850</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5801,7 +5797,7 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="5" t="s">
-        <v>910</v>
+        <v>851</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5821,7 +5817,7 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="5" t="s">
-        <v>911</v>
+        <v>852</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -5841,7 +5837,7 @@
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="5" t="s">
-        <v>912</v>
+        <v>853</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5861,7 +5857,7 @@
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="5" t="s">
-        <v>913</v>
+        <v>854</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5881,7 +5877,7 @@
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="5" t="s">
-        <v>914</v>
+        <v>855</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -5901,7 +5897,7 @@
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="5" t="s">
-        <v>915</v>
+        <v>856</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5941,7 +5937,7 @@
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="5" t="s">
-        <v>916</v>
+        <v>857</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5957,11 +5953,11 @@
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="4" t="s">
-        <v>68</v>
+        <v>1122</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="5" t="s">
-        <v>917</v>
+        <v>858</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -5973,15 +5969,15 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -5993,15 +5989,15 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="5" t="s">
-        <v>918</v>
+        <v>859</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6013,15 +6009,15 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -6033,15 +6029,15 @@
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="5" t="s">
-        <v>919</v>
+        <v>860</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -6053,15 +6049,15 @@
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="5" t="s">
-        <v>920</v>
+        <v>861</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6073,15 +6069,15 @@
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="5" t="s">
-        <v>921</v>
+        <v>862</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6093,15 +6089,15 @@
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6113,15 +6109,15 @@
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6133,15 +6129,15 @@
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -6153,15 +6149,15 @@
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="4" t="s">
-        <v>93</v>
+        <v>1123</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="5" t="s">
-        <v>922</v>
+        <v>863</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -6171,19 +6167,19 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="H28" s="5" t="s">
-        <v>923</v>
+        <v>864</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6195,15 +6191,15 @@
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -6215,15 +6211,15 @@
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="5" t="s">
-        <v>924</v>
+        <v>865</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6235,15 +6231,15 @@
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="5" t="s">
-        <v>925</v>
+        <v>866</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -6255,15 +6251,15 @@
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -6275,15 +6271,15 @@
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="5" t="s">
-        <v>926</v>
+        <v>867</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -6295,15 +6291,15 @@
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="5" t="s">
-        <v>927</v>
+        <v>868</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -6315,15 +6311,15 @@
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6335,15 +6331,15 @@
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -6355,15 +6351,15 @@
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="5" t="s">
-        <v>928</v>
+        <v>869</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6375,15 +6371,15 @@
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6395,15 +6391,15 @@
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="5" t="s">
-        <v>929</v>
+        <v>870</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -6415,15 +6411,15 @@
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="5" t="s">
-        <v>930</v>
+        <v>871</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -6435,15 +6431,15 @@
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="5" t="s">
-        <v>931</v>
+        <v>872</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -6455,15 +6451,15 @@
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="5" t="s">
-        <v>932</v>
+        <v>873</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -6474,11 +6470,11 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H43" s="5"/>
     </row>
@@ -6492,16 +6488,16 @@
         <v>5</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="H44" s="5" t="s">
-        <v>933</v>
+        <v>874</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6513,15 +6509,15 @@
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="4" t="s">
-        <v>137</v>
+        <v>1121</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="5" t="s">
-        <v>934</v>
+        <v>875</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -6533,15 +6529,15 @@
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="4" t="s">
-        <v>139</v>
+        <v>1124</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="5" t="s">
-        <v>935</v>
+        <v>876</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6553,15 +6549,15 @@
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="5" t="s">
-        <v>936</v>
+        <v>877</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
@@ -6573,15 +6569,15 @@
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="5" t="s">
-        <v>937</v>
+        <v>878</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="259.2" x14ac:dyDescent="0.3">
@@ -6593,15 +6589,15 @@
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="5" t="s">
-        <v>938</v>
+        <v>879</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6613,15 +6609,15 @@
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="4" t="s">
-        <v>147</v>
+        <v>1125</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="5" t="s">
-        <v>939</v>
+        <v>880</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6633,15 +6629,15 @@
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="5" t="s">
-        <v>940</v>
+        <v>881</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6653,15 +6649,15 @@
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="5" t="s">
-        <v>941</v>
+        <v>882</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6673,15 +6669,15 @@
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="5" t="s">
-        <v>942</v>
+        <v>883</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6693,15 +6689,15 @@
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="5" t="s">
-        <v>943</v>
+        <v>884</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6713,15 +6709,15 @@
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="5" t="s">
-        <v>944</v>
+        <v>885</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -6733,15 +6729,15 @@
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="5" t="s">
-        <v>945</v>
+        <v>886</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
@@ -6753,15 +6749,15 @@
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="5" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6773,15 +6769,15 @@
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="5" t="s">
-        <v>946</v>
+        <v>887</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -6793,15 +6789,15 @@
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="5" t="s">
-        <v>947</v>
+        <v>888</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
@@ -6813,15 +6809,15 @@
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="4" t="s">
-        <v>168</v>
+        <v>1126</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="5" t="s">
-        <v>948</v>
+        <v>889</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -6833,15 +6829,15 @@
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="4" t="s">
-        <v>170</v>
+        <v>1127</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="5" t="s">
-        <v>949</v>
+        <v>890</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -6852,18 +6848,18 @@
         <v>5</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="4" t="s">
-        <v>173</v>
+        <v>1128</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="5" t="s">
-        <v>950</v>
+        <v>891</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -6874,18 +6870,18 @@
         <v>5</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="5" t="s">
-        <v>951</v>
+        <v>892</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -6896,18 +6892,18 @@
         <v>5</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="4" t="s">
-        <v>179</v>
+        <v>1129</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="5" t="s">
-        <v>952</v>
+        <v>893</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6919,15 +6915,15 @@
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="4" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="5" t="s">
-        <v>953</v>
+        <v>894</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -6939,15 +6935,15 @@
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="4" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="5" t="s">
-        <v>954</v>
+        <v>895</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
@@ -6959,15 +6955,15 @@
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="4" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="5" t="s">
-        <v>955</v>
+        <v>896</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -6979,15 +6975,15 @@
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="4" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="5" t="s">
-        <v>956</v>
+        <v>897</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -6999,15 +6995,15 @@
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="4" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="5" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
@@ -7019,15 +7015,15 @@
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="4" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="5" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -7039,15 +7035,15 @@
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="4" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="5" t="s">
-        <v>957</v>
+        <v>898</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -7059,15 +7055,15 @@
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="4" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="5" t="s">
-        <v>958</v>
+        <v>899</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -7079,15 +7075,15 @@
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="4" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="5" t="s">
-        <v>959</v>
+        <v>900</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -7099,15 +7095,15 @@
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="4" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="5" t="s">
-        <v>960</v>
+        <v>901</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -7119,15 +7115,15 @@
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="4" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="5" t="s">
-        <v>961</v>
+        <v>902</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -7139,15 +7135,15 @@
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="4" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="5" t="s">
-        <v>962</v>
+        <v>903</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -7159,15 +7155,15 @@
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="4" t="s">
-        <v>207</v>
+        <v>1130</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="5" t="s">
-        <v>963</v>
+        <v>904</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7179,15 +7175,15 @@
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="4" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="5" t="s">
-        <v>964</v>
+        <v>905</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -7199,15 +7195,15 @@
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="4" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="5" t="s">
-        <v>965</v>
+        <v>906</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -7219,15 +7215,15 @@
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="4" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="5" t="s">
-        <v>966</v>
+        <v>907</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7237,19 +7233,19 @@
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>216</v>
+        <v>1131</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>967</v>
+        <v>908</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -7261,15 +7257,15 @@
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="4" t="s">
-        <v>219</v>
+        <v>1132</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="5" t="s">
-        <v>968</v>
+        <v>909</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -7281,15 +7277,15 @@
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="4" t="s">
-        <v>221</v>
+        <v>1133</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="5" t="s">
-        <v>969</v>
+        <v>910</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7301,15 +7297,15 @@
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="4" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="5" t="s">
-        <v>970</v>
+        <v>911</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
@@ -7321,15 +7317,15 @@
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="4" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="G85" s="3"/>
       <c r="H85" s="5" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
@@ -7341,15 +7337,15 @@
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="4" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="5" t="s">
-        <v>971</v>
+        <v>912</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7361,15 +7357,15 @@
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="4" t="s">
-        <v>230</v>
+        <v>1134</v>
       </c>
       <c r="G87" s="3"/>
       <c r="H87" s="5" t="s">
-        <v>972</v>
+        <v>913</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -7381,15 +7377,15 @@
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="4" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="5" t="s">
-        <v>973</v>
+        <v>914</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7401,15 +7397,15 @@
       </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="4" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="5" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -7420,11 +7416,11 @@
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="3" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="H90" s="5"/>
     </row>
@@ -7435,19 +7431,19 @@
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7459,15 +7455,15 @@
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="4" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="5" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -7479,15 +7475,15 @@
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="4" t="s">
-        <v>247</v>
+        <v>1135</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="5" t="s">
-        <v>974</v>
+        <v>915</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7499,15 +7495,15 @@
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="4" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="G94" s="3"/>
       <c r="H94" s="5" t="s">
-        <v>975</v>
+        <v>916</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -7519,15 +7515,15 @@
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="4" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="G95" s="3"/>
       <c r="H95" s="5" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -7539,15 +7535,15 @@
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="4" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="5" t="s">
-        <v>976</v>
+        <v>917</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -7559,15 +7555,15 @@
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="4" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="5" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -7579,15 +7575,15 @@
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="4" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="5" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -7599,15 +7595,15 @@
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="4" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="5" t="s">
-        <v>977</v>
+        <v>918</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7619,15 +7615,15 @@
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="4" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="5" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7639,15 +7635,15 @@
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="4" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="5" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -7659,15 +7655,15 @@
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="4" t="s">
-        <v>270</v>
+        <v>1136</v>
       </c>
       <c r="G102" s="3"/>
       <c r="H102" s="5" t="s">
-        <v>978</v>
+        <v>919</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -7679,15 +7675,15 @@
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="4" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="5" t="s">
-        <v>979</v>
+        <v>920</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -7699,15 +7695,15 @@
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="4" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="5" t="s">
-        <v>980</v>
+        <v>921</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7719,15 +7715,15 @@
       </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="4" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="G105" s="3"/>
       <c r="H105" s="5" t="s">
-        <v>981</v>
+        <v>922</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -7739,15 +7735,15 @@
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="4" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="5" t="s">
-        <v>982</v>
+        <v>923</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7759,15 +7755,15 @@
       </c>
       <c r="C107" s="3"/>
       <c r="D107" s="3" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="4" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="5" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7779,15 +7775,15 @@
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="4" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="5" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
@@ -7797,19 +7793,19 @@
       </c>
       <c r="C109" s="3"/>
       <c r="D109" s="3" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7821,15 +7817,15 @@
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="4" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="5" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -7841,18 +7837,18 @@
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="3" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="4" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="G111" s="3"/>
       <c r="H111" s="5" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>39</v>
       </c>
@@ -7861,15 +7857,15 @@
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="3" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="4" t="s">
-        <v>296</v>
+        <v>1137</v>
       </c>
       <c r="G112" s="3"/>
       <c r="H112" s="5" t="s">
-        <v>984</v>
+        <v>925</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
@@ -7881,15 +7877,15 @@
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="4" t="s">
-        <v>298</v>
+        <v>1138</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="5" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -7901,18 +7897,18 @@
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="4" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="5" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>39</v>
       </c>
@@ -7921,15 +7917,15 @@
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="4" t="s">
-        <v>303</v>
+        <v>1139</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="5" t="s">
-        <v>986</v>
+        <v>927</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -7941,15 +7937,15 @@
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="4" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="5" t="s">
-        <v>987</v>
+        <v>928</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -7961,15 +7957,15 @@
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="3" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="4" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="5" t="s">
-        <v>988</v>
+        <v>929</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
@@ -7981,15 +7977,15 @@
       </c>
       <c r="C118" s="3"/>
       <c r="D118" s="3" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="4" t="s">
-        <v>309</v>
+        <v>1140</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="5" t="s">
-        <v>989</v>
+        <v>930</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
@@ -8001,15 +7997,15 @@
       </c>
       <c r="C119" s="3"/>
       <c r="D119" s="3" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="4" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="5" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -8021,15 +8017,15 @@
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="4" t="s">
-        <v>314</v>
+        <v>1141</v>
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="5" t="s">
-        <v>990</v>
+        <v>931</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8041,15 +8037,15 @@
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="3" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="4" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="5" t="s">
-        <v>991</v>
+        <v>932</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -8061,15 +8057,15 @@
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="4" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="G122" s="3"/>
       <c r="H122" s="5" t="s">
-        <v>992</v>
+        <v>933</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
@@ -8081,15 +8077,15 @@
       </c>
       <c r="C123" s="3"/>
       <c r="D123" s="3" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="4" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="G123" s="3"/>
       <c r="H123" s="5" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="316.8" x14ac:dyDescent="0.3">
@@ -8101,15 +8097,15 @@
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="3" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="4" t="s">
-        <v>323</v>
+        <v>1142</v>
       </c>
       <c r="G124" s="3"/>
       <c r="H124" s="5" t="s">
-        <v>993</v>
+        <v>934</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -8121,15 +8117,15 @@
       </c>
       <c r="C125" s="3"/>
       <c r="D125" s="3" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="4" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="5" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -8141,15 +8137,15 @@
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="4" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="5" t="s">
-        <v>994</v>
+        <v>935</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8161,15 +8157,15 @@
       </c>
       <c r="C127" s="3"/>
       <c r="D127" s="3" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="4" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="G127" s="3"/>
       <c r="H127" s="5" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -8181,15 +8177,15 @@
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="3" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="4" t="s">
-        <v>333</v>
+        <v>1143</v>
       </c>
       <c r="G128" s="3"/>
       <c r="H128" s="5" t="s">
-        <v>995</v>
+        <v>936</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8201,15 +8197,15 @@
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="4" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="G129" s="3"/>
       <c r="H129" s="5" t="s">
-        <v>996</v>
+        <v>937</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8221,15 +8217,15 @@
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="4" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="G130" s="3"/>
       <c r="H130" s="5" t="s">
-        <v>997</v>
+        <v>938</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8241,15 +8237,15 @@
       </c>
       <c r="C131" s="3"/>
       <c r="D131" s="3" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="4" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="G131" s="3"/>
       <c r="H131" s="5" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8261,15 +8257,15 @@
       </c>
       <c r="C132" s="3"/>
       <c r="D132" s="3" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="4" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="5" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8281,15 +8277,15 @@
       </c>
       <c r="C133" s="3"/>
       <c r="D133" s="3" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="4" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="5" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
@@ -8300,11 +8296,11 @@
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="3" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="H134" s="5"/>
     </row>
@@ -8315,19 +8311,19 @@
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8339,15 +8335,15 @@
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="4" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="G136" s="3"/>
       <c r="H136" s="5" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -8359,15 +8355,15 @@
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="3" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="4" t="s">
-        <v>358</v>
+        <v>1144</v>
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="5" t="s">
-        <v>998</v>
+        <v>939</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8379,15 +8375,15 @@
       </c>
       <c r="C138" s="3"/>
       <c r="D138" s="3" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="4" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="5" t="s">
-        <v>999</v>
+        <v>940</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8399,15 +8395,15 @@
       </c>
       <c r="C139" s="3"/>
       <c r="D139" s="3" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="4" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="G139" s="3"/>
       <c r="H139" s="5" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -8419,15 +8415,15 @@
       </c>
       <c r="C140" s="3"/>
       <c r="D140" s="3" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="4" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="5" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8439,15 +8435,15 @@
       </c>
       <c r="C141" s="3"/>
       <c r="D141" s="3" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="4" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="G141" s="3"/>
       <c r="H141" s="5" t="s">
-        <v>1000</v>
+        <v>941</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
@@ -8459,15 +8455,15 @@
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="3" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="4" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="G142" s="3"/>
       <c r="H142" s="5" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -8479,15 +8475,15 @@
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="3" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="4" t="s">
-        <v>373</v>
+        <v>1145</v>
       </c>
       <c r="G143" s="3"/>
       <c r="H143" s="5" t="s">
-        <v>1001</v>
+        <v>942</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -8499,18 +8495,18 @@
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="4" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
       <c r="G144" s="3"/>
       <c r="H144" s="5" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>39</v>
       </c>
@@ -8519,15 +8515,15 @@
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="4" t="s">
-        <v>377</v>
+        <v>1146</v>
       </c>
       <c r="G145" s="3"/>
       <c r="H145" s="5" t="s">
-        <v>1003</v>
+        <v>944</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -8539,15 +8535,15 @@
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="E146" s="3"/>
       <c r="F146" s="4" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="G146" s="3"/>
       <c r="H146" s="5" t="s">
-        <v>1004</v>
+        <v>945</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8559,15 +8555,15 @@
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="E147" s="3"/>
       <c r="F147" s="4" t="s">
-        <v>381</v>
+        <v>1147</v>
       </c>
       <c r="G147" s="3"/>
       <c r="H147" s="5" t="s">
-        <v>1005</v>
+        <v>946</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8579,15 +8575,15 @@
       </c>
       <c r="C148" s="3"/>
       <c r="D148" s="3" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="E148" s="3"/>
       <c r="F148" s="4" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="5" t="s">
-        <v>1006</v>
+        <v>947</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8599,15 +8595,15 @@
       </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3" t="s">
-        <v>384</v>
+        <v>357</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="4" t="s">
-        <v>385</v>
+        <v>1148</v>
       </c>
       <c r="G149" s="3"/>
       <c r="H149" s="5" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8619,15 +8615,15 @@
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="4" t="s">
-        <v>388</v>
+        <v>360</v>
       </c>
       <c r="G150" s="3"/>
       <c r="H150" s="5" t="s">
-        <v>389</v>
+        <v>361</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
@@ -8637,19 +8633,19 @@
       </c>
       <c r="C151" s="3"/>
       <c r="D151" s="3" t="s">
-        <v>390</v>
+        <v>362</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>1007</v>
+        <v>948</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8661,15 +8657,15 @@
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3" t="s">
-        <v>394</v>
+        <v>366</v>
       </c>
       <c r="E152" s="3"/>
       <c r="F152" s="4" t="s">
-        <v>395</v>
+        <v>1149</v>
       </c>
       <c r="G152" s="3"/>
       <c r="H152" s="5" t="s">
-        <v>1008</v>
+        <v>949</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -8681,15 +8677,15 @@
       </c>
       <c r="C153" s="3"/>
       <c r="D153" s="3" t="s">
-        <v>396</v>
+        <v>367</v>
       </c>
       <c r="E153" s="3"/>
       <c r="F153" s="4" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="G153" s="3"/>
       <c r="H153" s="5" t="s">
-        <v>1009</v>
+        <v>950</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8701,15 +8697,15 @@
       </c>
       <c r="C154" s="3"/>
       <c r="D154" s="3" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="E154" s="3"/>
       <c r="F154" s="4" t="s">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="G154" s="3"/>
       <c r="H154" s="5" t="s">
-        <v>1010</v>
+        <v>951</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8721,15 +8717,15 @@
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="4" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="G155" s="3"/>
       <c r="H155" s="5" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8741,15 +8737,15 @@
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
       <c r="E156" s="3"/>
       <c r="F156" s="4" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="G156" s="3"/>
       <c r="H156" s="5" t="s">
-        <v>1011</v>
+        <v>952</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -8761,15 +8757,15 @@
       </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3" t="s">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="4" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="G157" s="3"/>
       <c r="H157" s="5" t="s">
-        <v>1012</v>
+        <v>953</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8781,15 +8777,15 @@
       </c>
       <c r="C158" s="3"/>
       <c r="D158" s="3" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="4" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="G158" s="3"/>
       <c r="H158" s="5" t="s">
-        <v>1013</v>
+        <v>954</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -8801,15 +8797,15 @@
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="3" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
       <c r="E159" s="3"/>
       <c r="F159" s="4" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="G159" s="3"/>
       <c r="H159" s="5" t="s">
-        <v>1014</v>
+        <v>955</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
@@ -8821,15 +8817,15 @@
       </c>
       <c r="C160" s="3"/>
       <c r="D160" s="3" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="4" t="s">
-        <v>412</v>
+        <v>1150</v>
       </c>
       <c r="G160" s="3"/>
       <c r="H160" s="5" t="s">
-        <v>1015</v>
+        <v>956</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
@@ -8841,15 +8837,15 @@
       </c>
       <c r="C161" s="3"/>
       <c r="D161" s="3" t="s">
-        <v>413</v>
+        <v>383</v>
       </c>
       <c r="E161" s="3"/>
       <c r="F161" s="4" t="s">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="G161" s="3"/>
       <c r="H161" s="5" t="s">
-        <v>1016</v>
+        <v>957</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -8861,15 +8857,15 @@
       </c>
       <c r="C162" s="3"/>
       <c r="D162" s="3" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="E162" s="3"/>
       <c r="F162" s="4" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="G162" s="3"/>
       <c r="H162" s="5" t="s">
-        <v>1017</v>
+        <v>958</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8881,15 +8877,15 @@
       </c>
       <c r="C163" s="3"/>
       <c r="D163" s="3" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="4" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="G163" s="3"/>
       <c r="H163" s="5" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8901,15 +8897,15 @@
       </c>
       <c r="C164" s="3"/>
       <c r="D164" s="3" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="4" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="G164" s="3"/>
       <c r="H164" s="5" t="s">
-        <v>1018</v>
+        <v>959</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -8921,15 +8917,15 @@
       </c>
       <c r="C165" s="3"/>
       <c r="D165" s="3" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="E165" s="3"/>
       <c r="F165" s="4" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
       <c r="G165" s="3"/>
       <c r="H165" s="5" t="s">
-        <v>1019</v>
+        <v>960</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -8941,15 +8937,15 @@
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="E166" s="3"/>
       <c r="F166" s="4" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="G166" s="3"/>
       <c r="H166" s="5" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -8961,15 +8957,15 @@
       </c>
       <c r="C167" s="3"/>
       <c r="D167" s="3" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="E167" s="3"/>
       <c r="F167" s="4" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="G167" s="3"/>
       <c r="H167" s="5" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -8981,15 +8977,15 @@
       </c>
       <c r="C168" s="3"/>
       <c r="D168" s="3" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="E168" s="3"/>
       <c r="F168" s="4" t="s">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="G168" s="3"/>
       <c r="H168" s="5" t="s">
-        <v>1020</v>
+        <v>961</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9001,15 +8997,15 @@
       </c>
       <c r="C169" s="3"/>
       <c r="D169" s="3" t="s">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="E169" s="3"/>
       <c r="F169" s="4" t="s">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="G169" s="3"/>
       <c r="H169" s="5" t="s">
-        <v>1021</v>
+        <v>962</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9021,15 +9017,15 @@
       </c>
       <c r="C170" s="3"/>
       <c r="D170" s="3" t="s">
-        <v>434</v>
+        <v>404</v>
       </c>
       <c r="E170" s="3"/>
       <c r="F170" s="4" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="G170" s="3"/>
       <c r="H170" s="5" t="s">
-        <v>1022</v>
+        <v>963</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -9041,15 +9037,15 @@
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="3" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="E171" s="3"/>
       <c r="F171" s="4" t="s">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="G171" s="3"/>
       <c r="H171" s="5" t="s">
-        <v>1023</v>
+        <v>964</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -9061,15 +9057,15 @@
       </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3" t="s">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="E172" s="3"/>
       <c r="F172" s="4" t="s">
-        <v>439</v>
+        <v>1151</v>
       </c>
       <c r="G172" s="3"/>
       <c r="H172" s="5" t="s">
-        <v>1024</v>
+        <v>965</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -9081,15 +9077,15 @@
       </c>
       <c r="C173" s="3"/>
       <c r="D173" s="3" t="s">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="E173" s="3"/>
       <c r="F173" s="4" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="G173" s="3"/>
       <c r="H173" s="5" t="s">
-        <v>1025</v>
+        <v>966</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -9101,15 +9097,15 @@
       </c>
       <c r="C174" s="3"/>
       <c r="D174" s="3" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="E174" s="3"/>
       <c r="F174" s="4" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="G174" s="3"/>
       <c r="H174" s="5" t="s">
-        <v>1026</v>
+        <v>967</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -9121,15 +9117,15 @@
       </c>
       <c r="C175" s="3"/>
       <c r="D175" s="3" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="E175" s="3"/>
       <c r="F175" s="4" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
       <c r="G175" s="3"/>
       <c r="H175" s="5" t="s">
-        <v>1027</v>
+        <v>968</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9141,15 +9137,15 @@
       </c>
       <c r="C176" s="3"/>
       <c r="D176" s="3" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="E176" s="3"/>
       <c r="F176" s="4" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="G176" s="3"/>
       <c r="H176" s="5" t="s">
-        <v>1028</v>
+        <v>969</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9161,15 +9157,15 @@
       </c>
       <c r="C177" s="3"/>
       <c r="D177" s="3" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="E177" s="3"/>
       <c r="F177" s="4" t="s">
-        <v>449</v>
+        <v>1152</v>
       </c>
       <c r="G177" s="3"/>
       <c r="H177" s="5" t="s">
-        <v>1029</v>
+        <v>970</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9181,15 +9177,15 @@
       </c>
       <c r="C178" s="3"/>
       <c r="D178" s="3" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="E178" s="3"/>
       <c r="F178" s="4" t="s">
-        <v>451</v>
+        <v>419</v>
       </c>
       <c r="G178" s="3"/>
       <c r="H178" s="5" t="s">
-        <v>1030</v>
+        <v>971</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
@@ -9201,15 +9197,15 @@
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3" t="s">
-        <v>452</v>
+        <v>420</v>
       </c>
       <c r="E179" s="3"/>
       <c r="F179" s="4" t="s">
-        <v>453</v>
+        <v>421</v>
       </c>
       <c r="G179" s="3"/>
       <c r="H179" s="5" t="s">
-        <v>1031</v>
+        <v>972</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9221,15 +9217,15 @@
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3" t="s">
-        <v>454</v>
+        <v>422</v>
       </c>
       <c r="E180" s="3"/>
       <c r="F180" s="4" t="s">
-        <v>455</v>
+        <v>423</v>
       </c>
       <c r="G180" s="3"/>
       <c r="H180" s="5" t="s">
-        <v>1032</v>
+        <v>973</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9241,15 +9237,15 @@
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="E181" s="3"/>
       <c r="F181" s="4" t="s">
-        <v>457</v>
+        <v>425</v>
       </c>
       <c r="G181" s="3"/>
       <c r="H181" s="5" t="s">
-        <v>1033</v>
+        <v>974</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -9261,15 +9257,15 @@
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3" t="s">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="E182" s="3"/>
       <c r="F182" s="4" t="s">
-        <v>459</v>
+        <v>1153</v>
       </c>
       <c r="G182" s="3"/>
       <c r="H182" s="5" t="s">
-        <v>1034</v>
+        <v>975</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9281,15 +9277,15 @@
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3" t="s">
-        <v>460</v>
+        <v>427</v>
       </c>
       <c r="E183" s="3"/>
       <c r="F183" s="4" t="s">
-        <v>461</v>
+        <v>1154</v>
       </c>
       <c r="G183" s="3"/>
       <c r="H183" s="5" t="s">
-        <v>1035</v>
+        <v>976</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -9301,15 +9297,15 @@
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3" t="s">
-        <v>462</v>
+        <v>428</v>
       </c>
       <c r="E184" s="3"/>
       <c r="F184" s="4" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="G184" s="3"/>
       <c r="H184" s="5" t="s">
-        <v>1036</v>
+        <v>977</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -9321,15 +9317,15 @@
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c r="E185" s="3"/>
       <c r="F185" s="4" t="s">
-        <v>465</v>
+        <v>1155</v>
       </c>
       <c r="G185" s="3"/>
       <c r="H185" s="5" t="s">
-        <v>1037</v>
+        <v>978</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -9341,15 +9337,15 @@
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3" t="s">
-        <v>466</v>
+        <v>431</v>
       </c>
       <c r="E186" s="3"/>
       <c r="F186" s="4" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="G186" s="3"/>
       <c r="H186" s="5" t="s">
-        <v>1038</v>
+        <v>979</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
@@ -9359,19 +9355,19 @@
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3" t="s">
-        <v>468</v>
+        <v>433</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>469</v>
+        <v>434</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>471</v>
+        <v>436</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>472</v>
+        <v>437</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9383,15 +9379,15 @@
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3" t="s">
-        <v>473</v>
+        <v>438</v>
       </c>
       <c r="E188" s="3"/>
       <c r="F188" s="4" t="s">
-        <v>474</v>
+        <v>1156</v>
       </c>
       <c r="G188" s="3"/>
       <c r="H188" s="5" t="s">
-        <v>1039</v>
+        <v>980</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9403,15 +9399,15 @@
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="E189" s="3"/>
       <c r="F189" s="4" t="s">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="G189" s="3"/>
       <c r="H189" s="5" t="s">
-        <v>1040</v>
+        <v>981</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9423,15 +9419,15 @@
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3" t="s">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="E190" s="3"/>
       <c r="F190" s="4" t="s">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="G190" s="3"/>
       <c r="H190" s="5" t="s">
-        <v>1041</v>
+        <v>982</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9443,15 +9439,15 @@
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3" t="s">
-        <v>479</v>
+        <v>443</v>
       </c>
       <c r="E191" s="3"/>
       <c r="F191" s="4" t="s">
-        <v>480</v>
+        <v>1157</v>
       </c>
       <c r="G191" s="3"/>
       <c r="H191" s="5" t="s">
-        <v>1042</v>
+        <v>983</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9463,15 +9459,15 @@
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3" t="s">
-        <v>481</v>
+        <v>444</v>
       </c>
       <c r="E192" s="3"/>
       <c r="F192" s="4" t="s">
-        <v>482</v>
+        <v>445</v>
       </c>
       <c r="G192" s="3"/>
       <c r="H192" s="5" t="s">
-        <v>1043</v>
+        <v>984</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -9483,15 +9479,15 @@
       </c>
       <c r="C193" s="3"/>
       <c r="D193" s="3" t="s">
-        <v>483</v>
+        <v>446</v>
       </c>
       <c r="E193" s="3"/>
       <c r="F193" s="4" t="s">
-        <v>484</v>
+        <v>447</v>
       </c>
       <c r="G193" s="3"/>
       <c r="H193" s="5" t="s">
-        <v>485</v>
+        <v>448</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9503,15 +9499,15 @@
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3" t="s">
-        <v>486</v>
+        <v>449</v>
       </c>
       <c r="E194" s="3"/>
       <c r="F194" s="4" t="s">
-        <v>487</v>
+        <v>450</v>
       </c>
       <c r="G194" s="3"/>
       <c r="H194" s="5" t="s">
-        <v>1044</v>
+        <v>985</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -9523,15 +9519,15 @@
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3" t="s">
-        <v>488</v>
+        <v>451</v>
       </c>
       <c r="E195" s="3"/>
       <c r="F195" s="4" t="s">
-        <v>489</v>
+        <v>452</v>
       </c>
       <c r="G195" s="3"/>
       <c r="H195" s="5" t="s">
-        <v>490</v>
+        <v>453</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9543,18 +9539,18 @@
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3" t="s">
-        <v>491</v>
+        <v>454</v>
       </c>
       <c r="E196" s="3"/>
       <c r="F196" s="4" t="s">
-        <v>492</v>
+        <v>455</v>
       </c>
       <c r="G196" s="3"/>
       <c r="H196" s="5" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>39</v>
       </c>
@@ -9563,15 +9559,15 @@
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3" t="s">
-        <v>493</v>
+        <v>456</v>
       </c>
       <c r="E197" s="3"/>
       <c r="F197" s="4" t="s">
-        <v>494</v>
+        <v>1158</v>
       </c>
       <c r="G197" s="3"/>
       <c r="H197" s="5" t="s">
-        <v>1046</v>
+        <v>987</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9583,15 +9579,15 @@
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3" t="s">
-        <v>495</v>
+        <v>457</v>
       </c>
       <c r="E198" s="3"/>
       <c r="F198" s="4" t="s">
-        <v>496</v>
+        <v>458</v>
       </c>
       <c r="G198" s="3"/>
       <c r="H198" s="5" t="s">
-        <v>1047</v>
+        <v>988</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9603,15 +9599,15 @@
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3" t="s">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="E199" s="3"/>
       <c r="F199" s="4" t="s">
-        <v>498</v>
+        <v>460</v>
       </c>
       <c r="G199" s="3"/>
       <c r="H199" s="5" t="s">
-        <v>1048</v>
+        <v>989</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -9623,15 +9619,15 @@
       </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3" t="s">
-        <v>499</v>
+        <v>461</v>
       </c>
       <c r="E200" s="3"/>
       <c r="F200" s="4" t="s">
-        <v>500</v>
+        <v>462</v>
       </c>
       <c r="G200" s="3"/>
       <c r="H200" s="5" t="s">
-        <v>1049</v>
+        <v>990</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9643,15 +9639,15 @@
       </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3" t="s">
-        <v>501</v>
+        <v>463</v>
       </c>
       <c r="E201" s="3"/>
       <c r="F201" s="4" t="s">
-        <v>502</v>
+        <v>464</v>
       </c>
       <c r="G201" s="3"/>
       <c r="H201" s="5" t="s">
-        <v>503</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9663,15 +9659,15 @@
       </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3" t="s">
-        <v>504</v>
+        <v>466</v>
       </c>
       <c r="E202" s="3"/>
       <c r="F202" s="4" t="s">
-        <v>505</v>
+        <v>467</v>
       </c>
       <c r="G202" s="3"/>
       <c r="H202" s="5" t="s">
-        <v>1050</v>
+        <v>991</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9683,15 +9679,15 @@
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3" t="s">
-        <v>506</v>
+        <v>468</v>
       </c>
       <c r="E203" s="3"/>
       <c r="F203" s="4" t="s">
-        <v>507</v>
+        <v>469</v>
       </c>
       <c r="G203" s="3"/>
       <c r="H203" s="5" t="s">
-        <v>508</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9703,15 +9699,15 @@
       </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3" t="s">
-        <v>509</v>
+        <v>471</v>
       </c>
       <c r="E204" s="3"/>
       <c r="F204" s="4" t="s">
-        <v>510</v>
+        <v>472</v>
       </c>
       <c r="G204" s="3"/>
       <c r="H204" s="5" t="s">
-        <v>1051</v>
+        <v>992</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9723,15 +9719,15 @@
       </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3" t="s">
-        <v>511</v>
+        <v>473</v>
       </c>
       <c r="E205" s="3"/>
       <c r="F205" s="4" t="s">
-        <v>512</v>
+        <v>474</v>
       </c>
       <c r="G205" s="3"/>
       <c r="H205" s="5" t="s">
-        <v>1052</v>
+        <v>993</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9743,15 +9739,15 @@
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3" t="s">
-        <v>513</v>
+        <v>475</v>
       </c>
       <c r="E206" s="3"/>
       <c r="F206" s="4" t="s">
-        <v>514</v>
+        <v>476</v>
       </c>
       <c r="G206" s="3"/>
       <c r="H206" s="5" t="s">
-        <v>1053</v>
+        <v>994</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9763,15 +9759,15 @@
       </c>
       <c r="C207" s="3"/>
       <c r="D207" s="3" t="s">
-        <v>515</v>
+        <v>477</v>
       </c>
       <c r="E207" s="3"/>
       <c r="F207" s="4" t="s">
-        <v>516</v>
+        <v>478</v>
       </c>
       <c r="G207" s="3"/>
       <c r="H207" s="5" t="s">
-        <v>517</v>
+        <v>479</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -9783,15 +9779,15 @@
       </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3" t="s">
-        <v>518</v>
+        <v>480</v>
       </c>
       <c r="E208" s="3"/>
       <c r="F208" s="4" t="s">
-        <v>519</v>
+        <v>481</v>
       </c>
       <c r="G208" s="3"/>
       <c r="H208" s="5" t="s">
-        <v>1054</v>
+        <v>995</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -9803,15 +9799,15 @@
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3" t="s">
-        <v>520</v>
+        <v>482</v>
       </c>
       <c r="E209" s="3"/>
       <c r="F209" s="4" t="s">
-        <v>521</v>
+        <v>483</v>
       </c>
       <c r="G209" s="3"/>
       <c r="H209" s="5" t="s">
-        <v>522</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9823,15 +9819,15 @@
       </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3" t="s">
-        <v>523</v>
+        <v>485</v>
       </c>
       <c r="E210" s="3"/>
       <c r="F210" s="4" t="s">
-        <v>524</v>
+        <v>486</v>
       </c>
       <c r="G210" s="3"/>
       <c r="H210" s="5" t="s">
-        <v>1055</v>
+        <v>996</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9843,15 +9839,15 @@
       </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3" t="s">
-        <v>525</v>
+        <v>487</v>
       </c>
       <c r="E211" s="3"/>
       <c r="F211" s="4" t="s">
-        <v>526</v>
+        <v>488</v>
       </c>
       <c r="G211" s="3"/>
       <c r="H211" s="5" t="s">
-        <v>527</v>
+        <v>489</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -9863,15 +9859,15 @@
       </c>
       <c r="C212" s="3"/>
       <c r="D212" s="3" t="s">
-        <v>528</v>
+        <v>490</v>
       </c>
       <c r="E212" s="3"/>
       <c r="F212" s="4" t="s">
-        <v>529</v>
+        <v>491</v>
       </c>
       <c r="G212" s="3"/>
       <c r="H212" s="5" t="s">
-        <v>1056</v>
+        <v>997</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -9883,15 +9879,15 @@
       </c>
       <c r="C213" s="3"/>
       <c r="D213" s="3" t="s">
-        <v>530</v>
+        <v>492</v>
       </c>
       <c r="E213" s="3"/>
       <c r="F213" s="4" t="s">
-        <v>531</v>
+        <v>493</v>
       </c>
       <c r="G213" s="3"/>
       <c r="H213" s="5" t="s">
-        <v>1057</v>
+        <v>998</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9903,15 +9899,15 @@
       </c>
       <c r="C214" s="3"/>
       <c r="D214" s="3" t="s">
-        <v>532</v>
+        <v>494</v>
       </c>
       <c r="E214" s="3"/>
       <c r="F214" s="4" t="s">
-        <v>533</v>
+        <v>495</v>
       </c>
       <c r="G214" s="3"/>
       <c r="H214" s="5" t="s">
-        <v>534</v>
+        <v>496</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -9923,15 +9919,15 @@
       </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3" t="s">
-        <v>535</v>
+        <v>497</v>
       </c>
       <c r="E215" s="3"/>
       <c r="F215" s="4" t="s">
-        <v>536</v>
+        <v>498</v>
       </c>
       <c r="G215" s="3"/>
       <c r="H215" s="5" t="s">
-        <v>537</v>
+        <v>499</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -9943,15 +9939,15 @@
       </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3" t="s">
-        <v>538</v>
+        <v>500</v>
       </c>
       <c r="E216" s="3"/>
       <c r="F216" s="4" t="s">
-        <v>539</v>
+        <v>501</v>
       </c>
       <c r="G216" s="3"/>
       <c r="H216" s="5" t="s">
-        <v>1058</v>
+        <v>999</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -9963,15 +9959,15 @@
       </c>
       <c r="C217" s="3"/>
       <c r="D217" s="3" t="s">
-        <v>540</v>
+        <v>502</v>
       </c>
       <c r="E217" s="3"/>
       <c r="F217" s="4" t="s">
-        <v>541</v>
+        <v>503</v>
       </c>
       <c r="G217" s="3"/>
       <c r="H217" s="5" t="s">
-        <v>1059</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -9983,15 +9979,15 @@
       </c>
       <c r="C218" s="3"/>
       <c r="D218" s="3" t="s">
-        <v>542</v>
+        <v>504</v>
       </c>
       <c r="E218" s="3"/>
       <c r="F218" s="4" t="s">
-        <v>543</v>
+        <v>505</v>
       </c>
       <c r="G218" s="3"/>
       <c r="H218" s="5" t="s">
-        <v>544</v>
+        <v>506</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -10003,15 +9999,15 @@
       </c>
       <c r="C219" s="3"/>
       <c r="D219" s="3" t="s">
-        <v>545</v>
+        <v>507</v>
       </c>
       <c r="E219" s="3"/>
       <c r="F219" s="4" t="s">
-        <v>546</v>
+        <v>508</v>
       </c>
       <c r="G219" s="3"/>
       <c r="H219" s="5" t="s">
-        <v>1060</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
@@ -10022,11 +10018,11 @@
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3" t="s">
-        <v>547</v>
+        <v>509</v>
       </c>
       <c r="F220" s="4"/>
       <c r="G220" s="3" t="s">
-        <v>548</v>
+        <v>510</v>
       </c>
       <c r="H220" s="5"/>
     </row>
@@ -10037,19 +10033,19 @@
       </c>
       <c r="C221" s="3"/>
       <c r="D221" s="3" t="s">
-        <v>549</v>
+        <v>511</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>550</v>
+        <v>512</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>552</v>
+        <v>514</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>1061</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -10061,15 +10057,15 @@
       </c>
       <c r="C222" s="3"/>
       <c r="D222" s="3" t="s">
-        <v>553</v>
+        <v>515</v>
       </c>
       <c r="E222" s="3"/>
       <c r="F222" s="4" t="s">
-        <v>554</v>
+        <v>1159</v>
       </c>
       <c r="G222" s="3"/>
       <c r="H222" s="5" t="s">
-        <v>1062</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -10081,15 +10077,15 @@
       </c>
       <c r="C223" s="3"/>
       <c r="D223" s="3" t="s">
-        <v>555</v>
+        <v>516</v>
       </c>
       <c r="E223" s="3"/>
       <c r="F223" s="4" t="s">
-        <v>556</v>
+        <v>517</v>
       </c>
       <c r="G223" s="3"/>
       <c r="H223" s="5" t="s">
-        <v>1063</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10101,15 +10097,15 @@
       </c>
       <c r="C224" s="3"/>
       <c r="D224" s="3" t="s">
-        <v>557</v>
+        <v>518</v>
       </c>
       <c r="E224" s="3"/>
       <c r="F224" s="4" t="s">
-        <v>558</v>
+        <v>519</v>
       </c>
       <c r="G224" s="3"/>
       <c r="H224" s="5" t="s">
-        <v>1064</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10121,15 +10117,15 @@
       </c>
       <c r="C225" s="3"/>
       <c r="D225" s="3" t="s">
-        <v>559</v>
+        <v>520</v>
       </c>
       <c r="E225" s="3"/>
       <c r="F225" s="4" t="s">
-        <v>560</v>
+        <v>521</v>
       </c>
       <c r="G225" s="3"/>
       <c r="H225" s="5" t="s">
-        <v>1065</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10141,15 +10137,15 @@
       </c>
       <c r="C226" s="3"/>
       <c r="D226" s="3" t="s">
-        <v>561</v>
+        <v>522</v>
       </c>
       <c r="E226" s="3"/>
       <c r="F226" s="4" t="s">
-        <v>562</v>
+        <v>523</v>
       </c>
       <c r="G226" s="3"/>
       <c r="H226" s="5" t="s">
-        <v>563</v>
+        <v>524</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10161,15 +10157,15 @@
       </c>
       <c r="C227" s="3"/>
       <c r="D227" s="3" t="s">
-        <v>564</v>
+        <v>525</v>
       </c>
       <c r="E227" s="3"/>
       <c r="F227" s="4" t="s">
-        <v>565</v>
+        <v>526</v>
       </c>
       <c r="G227" s="3"/>
       <c r="H227" s="5" t="s">
-        <v>566</v>
+        <v>527</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -10181,15 +10177,15 @@
       </c>
       <c r="C228" s="3"/>
       <c r="D228" s="3" t="s">
-        <v>567</v>
+        <v>528</v>
       </c>
       <c r="E228" s="3"/>
       <c r="F228" s="4" t="s">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="G228" s="3"/>
       <c r="H228" s="5" t="s">
-        <v>1066</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
@@ -10201,15 +10197,15 @@
       </c>
       <c r="C229" s="3"/>
       <c r="D229" s="3" t="s">
-        <v>569</v>
+        <v>530</v>
       </c>
       <c r="E229" s="3"/>
       <c r="F229" s="4" t="s">
-        <v>570</v>
+        <v>531</v>
       </c>
       <c r="G229" s="3"/>
       <c r="H229" s="5" t="s">
-        <v>571</v>
+        <v>532</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
@@ -10221,15 +10217,15 @@
       </c>
       <c r="C230" s="3"/>
       <c r="D230" s="3" t="s">
-        <v>572</v>
+        <v>533</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="4" t="s">
-        <v>573</v>
+        <v>534</v>
       </c>
       <c r="G230" s="3"/>
       <c r="H230" s="5" t="s">
-        <v>574</v>
+        <v>535</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -10241,15 +10237,15 @@
       </c>
       <c r="C231" s="3"/>
       <c r="D231" s="3" t="s">
-        <v>575</v>
+        <v>536</v>
       </c>
       <c r="E231" s="3"/>
       <c r="F231" s="4" t="s">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="G231" s="3"/>
       <c r="H231" s="5" t="s">
-        <v>1067</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -10261,15 +10257,15 @@
       </c>
       <c r="C232" s="3"/>
       <c r="D232" s="3" t="s">
-        <v>577</v>
+        <v>538</v>
       </c>
       <c r="E232" s="3"/>
       <c r="F232" s="4" t="s">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="G232" s="3"/>
       <c r="H232" s="5" t="s">
-        <v>579</v>
+        <v>540</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10281,15 +10277,15 @@
       </c>
       <c r="C233" s="3"/>
       <c r="D233" s="3" t="s">
-        <v>580</v>
+        <v>541</v>
       </c>
       <c r="E233" s="3"/>
       <c r="F233" s="4" t="s">
-        <v>581</v>
+        <v>542</v>
       </c>
       <c r="G233" s="3"/>
       <c r="H233" s="5" t="s">
-        <v>1068</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -10301,15 +10297,15 @@
       </c>
       <c r="C234" s="3"/>
       <c r="D234" s="3" t="s">
-        <v>582</v>
+        <v>543</v>
       </c>
       <c r="E234" s="3"/>
       <c r="F234" s="4" t="s">
-        <v>583</v>
+        <v>544</v>
       </c>
       <c r="G234" s="3"/>
       <c r="H234" s="5" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10321,15 +10317,15 @@
       </c>
       <c r="C235" s="3"/>
       <c r="D235" s="3" t="s">
-        <v>585</v>
+        <v>546</v>
       </c>
       <c r="E235" s="3"/>
       <c r="F235" s="4" t="s">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="G235" s="3"/>
       <c r="H235" s="5" t="s">
-        <v>587</v>
+        <v>548</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10341,15 +10337,15 @@
       </c>
       <c r="C236" s="3"/>
       <c r="D236" s="3" t="s">
-        <v>588</v>
+        <v>549</v>
       </c>
       <c r="E236" s="3"/>
       <c r="F236" s="4" t="s">
-        <v>589</v>
+        <v>550</v>
       </c>
       <c r="G236" s="3"/>
       <c r="H236" s="5" t="s">
-        <v>1069</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10361,15 +10357,15 @@
       </c>
       <c r="C237" s="3"/>
       <c r="D237" s="3" t="s">
-        <v>590</v>
+        <v>551</v>
       </c>
       <c r="E237" s="3"/>
       <c r="F237" s="4" t="s">
-        <v>591</v>
+        <v>552</v>
       </c>
       <c r="G237" s="3"/>
       <c r="H237" s="5" t="s">
-        <v>1070</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -10381,15 +10377,15 @@
       </c>
       <c r="C238" s="3"/>
       <c r="D238" s="3" t="s">
-        <v>592</v>
+        <v>553</v>
       </c>
       <c r="E238" s="3"/>
       <c r="F238" s="4" t="s">
-        <v>593</v>
+        <v>554</v>
       </c>
       <c r="G238" s="3"/>
       <c r="H238" s="5" t="s">
-        <v>1071</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -10401,15 +10397,15 @@
       </c>
       <c r="C239" s="3"/>
       <c r="D239" s="3" t="s">
-        <v>594</v>
+        <v>555</v>
       </c>
       <c r="E239" s="3"/>
       <c r="F239" s="4" t="s">
-        <v>595</v>
+        <v>556</v>
       </c>
       <c r="G239" s="3"/>
       <c r="H239" s="5" t="s">
-        <v>596</v>
+        <v>557</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10421,15 +10417,15 @@
       </c>
       <c r="C240" s="3"/>
       <c r="D240" s="3" t="s">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="E240" s="3"/>
       <c r="F240" s="4" t="s">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="G240" s="3"/>
       <c r="H240" s="5" t="s">
-        <v>599</v>
+        <v>560</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -10441,15 +10437,15 @@
       </c>
       <c r="C241" s="3"/>
       <c r="D241" s="3" t="s">
-        <v>600</v>
+        <v>561</v>
       </c>
       <c r="E241" s="3"/>
       <c r="F241" s="4" t="s">
-        <v>601</v>
+        <v>562</v>
       </c>
       <c r="G241" s="3"/>
       <c r="H241" s="5" t="s">
-        <v>602</v>
+        <v>563</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10461,15 +10457,15 @@
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="3" t="s">
-        <v>603</v>
+        <v>564</v>
       </c>
       <c r="E242" s="3"/>
       <c r="F242" s="4" t="s">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="G242" s="3"/>
       <c r="H242" s="5" t="s">
-        <v>605</v>
+        <v>566</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10481,15 +10477,15 @@
       </c>
       <c r="C243" s="3"/>
       <c r="D243" s="3" t="s">
-        <v>606</v>
+        <v>567</v>
       </c>
       <c r="E243" s="3"/>
       <c r="F243" s="4" t="s">
-        <v>607</v>
+        <v>568</v>
       </c>
       <c r="G243" s="3"/>
       <c r="H243" s="5" t="s">
-        <v>1072</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -10501,15 +10497,15 @@
       </c>
       <c r="C244" s="3"/>
       <c r="D244" s="3" t="s">
-        <v>608</v>
+        <v>569</v>
       </c>
       <c r="E244" s="3"/>
       <c r="F244" s="4" t="s">
-        <v>609</v>
+        <v>570</v>
       </c>
       <c r="G244" s="3"/>
       <c r="H244" s="5" t="s">
-        <v>1073</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10521,15 +10517,15 @@
       </c>
       <c r="C245" s="3"/>
       <c r="D245" s="3" t="s">
-        <v>610</v>
+        <v>571</v>
       </c>
       <c r="E245" s="3"/>
       <c r="F245" s="4" t="s">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="G245" s="3"/>
       <c r="H245" s="5" t="s">
-        <v>612</v>
+        <v>573</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
@@ -10541,15 +10537,15 @@
       </c>
       <c r="C246" s="3"/>
       <c r="D246" s="3" t="s">
-        <v>613</v>
+        <v>574</v>
       </c>
       <c r="E246" s="3"/>
       <c r="F246" s="4" t="s">
-        <v>614</v>
+        <v>575</v>
       </c>
       <c r="G246" s="3"/>
       <c r="H246" s="5" t="s">
-        <v>615</v>
+        <v>576</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10561,15 +10557,15 @@
       </c>
       <c r="C247" s="3"/>
       <c r="D247" s="3" t="s">
-        <v>616</v>
+        <v>577</v>
       </c>
       <c r="E247" s="3"/>
       <c r="F247" s="4" t="s">
-        <v>617</v>
+        <v>578</v>
       </c>
       <c r="G247" s="3"/>
       <c r="H247" s="5" t="s">
-        <v>618</v>
+        <v>579</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10581,15 +10577,15 @@
       </c>
       <c r="C248" s="3"/>
       <c r="D248" s="3" t="s">
-        <v>619</v>
+        <v>580</v>
       </c>
       <c r="E248" s="3"/>
       <c r="F248" s="4" t="s">
-        <v>620</v>
+        <v>581</v>
       </c>
       <c r="G248" s="3"/>
       <c r="H248" s="5" t="s">
-        <v>621</v>
+        <v>582</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10601,15 +10597,15 @@
       </c>
       <c r="C249" s="3"/>
       <c r="D249" s="3" t="s">
-        <v>622</v>
+        <v>583</v>
       </c>
       <c r="E249" s="3"/>
       <c r="F249" s="4" t="s">
-        <v>623</v>
+        <v>584</v>
       </c>
       <c r="G249" s="3"/>
       <c r="H249" s="5" t="s">
-        <v>624</v>
+        <v>585</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
@@ -10621,15 +10617,15 @@
       </c>
       <c r="C250" s="3"/>
       <c r="D250" s="3" t="s">
-        <v>625</v>
+        <v>586</v>
       </c>
       <c r="E250" s="3"/>
       <c r="F250" s="4" t="s">
-        <v>626</v>
+        <v>587</v>
       </c>
       <c r="G250" s="3"/>
       <c r="H250" s="5" t="s">
-        <v>627</v>
+        <v>588</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -10641,15 +10637,15 @@
       </c>
       <c r="C251" s="3"/>
       <c r="D251" s="3" t="s">
-        <v>628</v>
+        <v>589</v>
       </c>
       <c r="E251" s="3"/>
       <c r="F251" s="4" t="s">
-        <v>629</v>
+        <v>590</v>
       </c>
       <c r="G251" s="3"/>
       <c r="H251" s="5" t="s">
-        <v>630</v>
+        <v>591</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10661,15 +10657,15 @@
       </c>
       <c r="C252" s="3"/>
       <c r="D252" s="3" t="s">
-        <v>631</v>
+        <v>592</v>
       </c>
       <c r="E252" s="3"/>
       <c r="F252" s="4" t="s">
-        <v>632</v>
+        <v>593</v>
       </c>
       <c r="G252" s="3"/>
       <c r="H252" s="5" t="s">
-        <v>1074</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
@@ -10681,15 +10677,15 @@
       </c>
       <c r="C253" s="3"/>
       <c r="D253" s="3" t="s">
-        <v>633</v>
+        <v>594</v>
       </c>
       <c r="E253" s="3"/>
       <c r="F253" s="4" t="s">
-        <v>634</v>
+        <v>1160</v>
       </c>
       <c r="G253" s="3"/>
       <c r="H253" s="5" t="s">
-        <v>1075</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
@@ -10701,15 +10697,15 @@
       </c>
       <c r="C254" s="3"/>
       <c r="D254" s="3" t="s">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="E254" s="3"/>
       <c r="F254" s="4" t="s">
-        <v>636</v>
+        <v>596</v>
       </c>
       <c r="G254" s="3"/>
       <c r="H254" s="5" t="s">
-        <v>1076</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="255" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
@@ -10721,15 +10717,15 @@
       </c>
       <c r="C255" s="3"/>
       <c r="D255" s="3" t="s">
-        <v>637</v>
+        <v>597</v>
       </c>
       <c r="E255" s="3"/>
       <c r="F255" s="4" t="s">
-        <v>638</v>
+        <v>598</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="5" t="s">
-        <v>1077</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
@@ -10739,19 +10735,19 @@
       </c>
       <c r="C256" s="3"/>
       <c r="D256" s="3" t="s">
-        <v>639</v>
+        <v>599</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>640</v>
+        <v>600</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>641</v>
+        <v>601</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>642</v>
+        <v>602</v>
       </c>
       <c r="H256" s="5" t="s">
-        <v>643</v>
+        <v>603</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10763,15 +10759,15 @@
       </c>
       <c r="C257" s="3"/>
       <c r="D257" s="3" t="s">
-        <v>644</v>
+        <v>604</v>
       </c>
       <c r="E257" s="3"/>
       <c r="F257" s="4" t="s">
-        <v>645</v>
+        <v>1161</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="5" t="s">
-        <v>1078</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -10783,15 +10779,15 @@
       </c>
       <c r="C258" s="3"/>
       <c r="D258" s="3" t="s">
-        <v>646</v>
+        <v>605</v>
       </c>
       <c r="E258" s="3"/>
       <c r="F258" s="4" t="s">
-        <v>647</v>
+        <v>606</v>
       </c>
       <c r="G258" s="3"/>
       <c r="H258" s="5" t="s">
-        <v>1079</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10803,15 +10799,15 @@
       </c>
       <c r="C259" s="3"/>
       <c r="D259" s="3" t="s">
-        <v>648</v>
+        <v>607</v>
       </c>
       <c r="E259" s="3"/>
       <c r="F259" s="4" t="s">
-        <v>649</v>
+        <v>608</v>
       </c>
       <c r="G259" s="3"/>
       <c r="H259" s="5" t="s">
-        <v>1080</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10823,15 +10819,15 @@
       </c>
       <c r="C260" s="3"/>
       <c r="D260" s="3" t="s">
-        <v>650</v>
+        <v>609</v>
       </c>
       <c r="E260" s="3"/>
       <c r="F260" s="4" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="G260" s="3"/>
       <c r="H260" s="5" t="s">
-        <v>1081</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="261" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -10843,15 +10839,15 @@
       </c>
       <c r="C261" s="3"/>
       <c r="D261" s="3" t="s">
-        <v>652</v>
+        <v>611</v>
       </c>
       <c r="E261" s="3"/>
       <c r="F261" s="4" t="s">
-        <v>653</v>
+        <v>612</v>
       </c>
       <c r="G261" s="3"/>
       <c r="H261" s="5" t="s">
-        <v>1082</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="262" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10863,15 +10859,15 @@
       </c>
       <c r="C262" s="3"/>
       <c r="D262" s="3" t="s">
-        <v>654</v>
+        <v>613</v>
       </c>
       <c r="E262" s="3"/>
       <c r="F262" s="4" t="s">
-        <v>655</v>
+        <v>614</v>
       </c>
       <c r="G262" s="3"/>
       <c r="H262" s="5" t="s">
-        <v>1083</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="263" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -10883,15 +10879,15 @@
       </c>
       <c r="C263" s="3"/>
       <c r="D263" s="3" t="s">
-        <v>656</v>
+        <v>615</v>
       </c>
       <c r="E263" s="3"/>
       <c r="F263" s="4" t="s">
-        <v>657</v>
+        <v>616</v>
       </c>
       <c r="G263" s="3"/>
       <c r="H263" s="5" t="s">
-        <v>658</v>
+        <v>617</v>
       </c>
     </row>
     <row r="264" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -10903,15 +10899,15 @@
       </c>
       <c r="C264" s="3"/>
       <c r="D264" s="3" t="s">
-        <v>659</v>
+        <v>618</v>
       </c>
       <c r="E264" s="3"/>
       <c r="F264" s="4" t="s">
-        <v>660</v>
+        <v>619</v>
       </c>
       <c r="G264" s="3"/>
       <c r="H264" s="5" t="s">
-        <v>1084</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -10923,15 +10919,15 @@
       </c>
       <c r="C265" s="3"/>
       <c r="D265" s="3" t="s">
-        <v>661</v>
+        <v>620</v>
       </c>
       <c r="E265" s="3"/>
       <c r="F265" s="4" t="s">
-        <v>662</v>
+        <v>621</v>
       </c>
       <c r="G265" s="3"/>
       <c r="H265" s="5" t="s">
-        <v>1085</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="266" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -10943,15 +10939,15 @@
       </c>
       <c r="C266" s="3"/>
       <c r="D266" s="3" t="s">
-        <v>663</v>
+        <v>622</v>
       </c>
       <c r="E266" s="3"/>
       <c r="F266" s="4" t="s">
-        <v>664</v>
+        <v>1162</v>
       </c>
       <c r="G266" s="3"/>
       <c r="H266" s="5" t="s">
-        <v>1086</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="267" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -10963,15 +10959,15 @@
       </c>
       <c r="C267" s="3"/>
       <c r="D267" s="3" t="s">
-        <v>665</v>
+        <v>623</v>
       </c>
       <c r="E267" s="3"/>
       <c r="F267" s="4" t="s">
-        <v>666</v>
+        <v>624</v>
       </c>
       <c r="G267" s="3"/>
       <c r="H267" s="5" t="s">
-        <v>1087</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="268" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -10983,15 +10979,15 @@
       </c>
       <c r="C268" s="3"/>
       <c r="D268" s="3" t="s">
-        <v>667</v>
+        <v>625</v>
       </c>
       <c r="E268" s="3"/>
       <c r="F268" s="4" t="s">
-        <v>668</v>
+        <v>626</v>
       </c>
       <c r="G268" s="3"/>
       <c r="H268" s="5" t="s">
-        <v>1088</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="269" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -11003,15 +10999,15 @@
       </c>
       <c r="C269" s="3"/>
       <c r="D269" s="3" t="s">
-        <v>669</v>
+        <v>627</v>
       </c>
       <c r="E269" s="3"/>
       <c r="F269" s="4" t="s">
-        <v>670</v>
+        <v>628</v>
       </c>
       <c r="G269" s="3"/>
       <c r="H269" s="5" t="s">
-        <v>1089</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="270" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11023,15 +11019,15 @@
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="3" t="s">
-        <v>671</v>
+        <v>629</v>
       </c>
       <c r="E270" s="3"/>
       <c r="F270" s="4" t="s">
-        <v>672</v>
+        <v>630</v>
       </c>
       <c r="G270" s="3"/>
       <c r="H270" s="5" t="s">
-        <v>1090</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="271" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
@@ -11043,15 +11039,15 @@
       </c>
       <c r="C271" s="3"/>
       <c r="D271" s="3" t="s">
-        <v>673</v>
+        <v>631</v>
       </c>
       <c r="E271" s="3"/>
       <c r="F271" s="4" t="s">
-        <v>674</v>
+        <v>632</v>
       </c>
       <c r="G271" s="3"/>
       <c r="H271" s="5" t="s">
-        <v>1091</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="272" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -11063,15 +11059,15 @@
       </c>
       <c r="C272" s="3"/>
       <c r="D272" s="3" t="s">
-        <v>675</v>
+        <v>633</v>
       </c>
       <c r="E272" s="3"/>
       <c r="F272" s="4" t="s">
-        <v>676</v>
+        <v>1163</v>
       </c>
       <c r="G272" s="3"/>
       <c r="H272" s="5" t="s">
-        <v>1092</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="273" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -11083,15 +11079,15 @@
       </c>
       <c r="C273" s="3"/>
       <c r="D273" s="3" t="s">
-        <v>677</v>
+        <v>634</v>
       </c>
       <c r="E273" s="3"/>
       <c r="F273" s="4" t="s">
-        <v>678</v>
+        <v>635</v>
       </c>
       <c r="G273" s="3"/>
       <c r="H273" s="5" t="s">
-        <v>1093</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="274" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -11103,15 +11099,15 @@
       </c>
       <c r="C274" s="3"/>
       <c r="D274" s="3" t="s">
-        <v>679</v>
+        <v>636</v>
       </c>
       <c r="E274" s="3"/>
       <c r="F274" s="4" t="s">
-        <v>680</v>
+        <v>1164</v>
       </c>
       <c r="G274" s="3"/>
       <c r="H274" s="5" t="s">
-        <v>1094</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="275" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
@@ -11123,15 +11119,15 @@
       </c>
       <c r="C275" s="3"/>
       <c r="D275" s="3" t="s">
-        <v>681</v>
+        <v>637</v>
       </c>
       <c r="E275" s="3"/>
       <c r="F275" s="4" t="s">
-        <v>682</v>
+        <v>638</v>
       </c>
       <c r="G275" s="3"/>
       <c r="H275" s="5" t="s">
-        <v>1095</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="276" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
@@ -11143,15 +11139,15 @@
       </c>
       <c r="C276" s="3"/>
       <c r="D276" s="3" t="s">
-        <v>683</v>
+        <v>639</v>
       </c>
       <c r="E276" s="3"/>
       <c r="F276" s="4" t="s">
-        <v>684</v>
+        <v>640</v>
       </c>
       <c r="G276" s="3"/>
       <c r="H276" s="5" t="s">
-        <v>1096</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="277" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -11163,15 +11159,15 @@
       </c>
       <c r="C277" s="3"/>
       <c r="D277" s="3" t="s">
-        <v>685</v>
+        <v>641</v>
       </c>
       <c r="E277" s="3"/>
       <c r="F277" s="4" t="s">
-        <v>686</v>
+        <v>1165</v>
       </c>
       <c r="G277" s="3"/>
       <c r="H277" s="5" t="s">
-        <v>1097</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="278" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11183,15 +11179,15 @@
       </c>
       <c r="C278" s="3"/>
       <c r="D278" s="3" t="s">
-        <v>687</v>
+        <v>642</v>
       </c>
       <c r="E278" s="3"/>
       <c r="F278" s="4" t="s">
-        <v>688</v>
+        <v>643</v>
       </c>
       <c r="G278" s="3"/>
       <c r="H278" s="5" t="s">
-        <v>689</v>
+        <v>644</v>
       </c>
     </row>
     <row r="279" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -11203,15 +11199,15 @@
       </c>
       <c r="C279" s="3"/>
       <c r="D279" s="3" t="s">
-        <v>690</v>
+        <v>645</v>
       </c>
       <c r="E279" s="3"/>
       <c r="F279" s="4" t="s">
-        <v>691</v>
+        <v>646</v>
       </c>
       <c r="G279" s="3"/>
       <c r="H279" s="5" t="s">
-        <v>1098</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="280" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -11223,15 +11219,15 @@
       </c>
       <c r="C280" s="3"/>
       <c r="D280" s="3" t="s">
-        <v>692</v>
+        <v>647</v>
       </c>
       <c r="E280" s="3"/>
       <c r="F280" s="4" t="s">
-        <v>693</v>
+        <v>648</v>
       </c>
       <c r="G280" s="3"/>
       <c r="H280" s="5" t="s">
-        <v>1099</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="281" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -11243,15 +11239,15 @@
       </c>
       <c r="C281" s="3"/>
       <c r="D281" s="3" t="s">
-        <v>694</v>
+        <v>649</v>
       </c>
       <c r="E281" s="3"/>
       <c r="F281" s="4" t="s">
-        <v>695</v>
+        <v>1166</v>
       </c>
       <c r="G281" s="3"/>
       <c r="H281" s="5" t="s">
-        <v>696</v>
+        <v>650</v>
       </c>
     </row>
     <row r="282" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11263,15 +11259,15 @@
       </c>
       <c r="C282" s="3"/>
       <c r="D282" s="3" t="s">
-        <v>697</v>
+        <v>651</v>
       </c>
       <c r="E282" s="3"/>
       <c r="F282" s="4" t="s">
-        <v>698</v>
+        <v>652</v>
       </c>
       <c r="G282" s="3"/>
       <c r="H282" s="5" t="s">
-        <v>699</v>
+        <v>653</v>
       </c>
     </row>
     <row r="283" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
@@ -11283,15 +11279,15 @@
       </c>
       <c r="C283" s="3"/>
       <c r="D283" s="3" t="s">
-        <v>700</v>
+        <v>654</v>
       </c>
       <c r="E283" s="3"/>
       <c r="F283" s="4" t="s">
-        <v>701</v>
+        <v>1167</v>
       </c>
       <c r="G283" s="3"/>
       <c r="H283" s="5" t="s">
-        <v>1100</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
@@ -11302,11 +11298,11 @@
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3" t="s">
-        <v>702</v>
+        <v>655</v>
       </c>
       <c r="F284" s="4"/>
       <c r="G284" s="3" t="s">
-        <v>703</v>
+        <v>656</v>
       </c>
       <c r="H284" s="5"/>
     </row>
@@ -11317,19 +11313,19 @@
       </c>
       <c r="C285" s="3"/>
       <c r="D285" s="3" t="s">
-        <v>704</v>
+        <v>657</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>705</v>
+        <v>658</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>706</v>
+        <v>1168</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>707</v>
+        <v>659</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>1101</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="286" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -11341,15 +11337,15 @@
       </c>
       <c r="C286" s="3"/>
       <c r="D286" s="3" t="s">
-        <v>708</v>
+        <v>660</v>
       </c>
       <c r="E286" s="3"/>
       <c r="F286" s="4" t="s">
-        <v>709</v>
+        <v>661</v>
       </c>
       <c r="G286" s="3"/>
       <c r="H286" s="5" t="s">
-        <v>1102</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="287" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -11361,15 +11357,15 @@
       </c>
       <c r="C287" s="3"/>
       <c r="D287" s="3" t="s">
-        <v>710</v>
+        <v>662</v>
       </c>
       <c r="E287" s="3"/>
       <c r="F287" s="4" t="s">
-        <v>711</v>
+        <v>663</v>
       </c>
       <c r="G287" s="3"/>
       <c r="H287" s="5" t="s">
-        <v>1103</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="288" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -11381,15 +11377,15 @@
       </c>
       <c r="C288" s="3"/>
       <c r="D288" s="3" t="s">
-        <v>712</v>
+        <v>664</v>
       </c>
       <c r="E288" s="3"/>
       <c r="F288" s="4" t="s">
-        <v>713</v>
+        <v>665</v>
       </c>
       <c r="G288" s="3"/>
       <c r="H288" s="5" t="s">
-        <v>1104</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="289" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -11401,15 +11397,15 @@
       </c>
       <c r="C289" s="3"/>
       <c r="D289" s="3" t="s">
-        <v>714</v>
+        <v>666</v>
       </c>
       <c r="E289" s="3"/>
       <c r="F289" s="4" t="s">
-        <v>715</v>
+        <v>1169</v>
       </c>
       <c r="G289" s="3"/>
       <c r="H289" s="5" t="s">
-        <v>1105</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="290" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -11421,15 +11417,15 @@
       </c>
       <c r="C290" s="3"/>
       <c r="D290" s="3" t="s">
-        <v>716</v>
+        <v>667</v>
       </c>
       <c r="E290" s="3"/>
       <c r="F290" s="4" t="s">
-        <v>717</v>
+        <v>668</v>
       </c>
       <c r="G290" s="3"/>
       <c r="H290" s="5" t="s">
-        <v>718</v>
+        <v>669</v>
       </c>
     </row>
     <row r="291" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11441,15 +11437,15 @@
       </c>
       <c r="C291" s="3"/>
       <c r="D291" s="3" t="s">
-        <v>719</v>
+        <v>670</v>
       </c>
       <c r="E291" s="3"/>
       <c r="F291" s="4" t="s">
-        <v>720</v>
+        <v>671</v>
       </c>
       <c r="G291" s="3"/>
       <c r="H291" s="5" t="s">
-        <v>1106</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="292" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -11461,15 +11457,15 @@
       </c>
       <c r="C292" s="3"/>
       <c r="D292" s="3" t="s">
-        <v>721</v>
+        <v>672</v>
       </c>
       <c r="E292" s="3"/>
       <c r="F292" s="4" t="s">
-        <v>722</v>
+        <v>673</v>
       </c>
       <c r="G292" s="3"/>
       <c r="H292" s="5" t="s">
-        <v>1107</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="293" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11481,15 +11477,15 @@
       </c>
       <c r="C293" s="3"/>
       <c r="D293" s="3" t="s">
-        <v>723</v>
+        <v>674</v>
       </c>
       <c r="E293" s="3"/>
       <c r="F293" s="4" t="s">
-        <v>724</v>
+        <v>1170</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="5" t="s">
-        <v>725</v>
+        <v>675</v>
       </c>
     </row>
     <row r="294" spans="1:8" ht="216" x14ac:dyDescent="0.3">
@@ -11501,15 +11497,15 @@
       </c>
       <c r="C294" s="3"/>
       <c r="D294" s="3" t="s">
-        <v>726</v>
+        <v>676</v>
       </c>
       <c r="E294" s="3"/>
       <c r="F294" s="4" t="s">
-        <v>727</v>
+        <v>677</v>
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="5" t="s">
-        <v>1108</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="295" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -11521,15 +11517,15 @@
       </c>
       <c r="C295" s="3"/>
       <c r="D295" s="3" t="s">
-        <v>728</v>
+        <v>678</v>
       </c>
       <c r="E295" s="3"/>
       <c r="F295" s="4" t="s">
-        <v>729</v>
+        <v>1171</v>
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="5" t="s">
-        <v>1109</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="296" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -11541,15 +11537,15 @@
       </c>
       <c r="C296" s="3"/>
       <c r="D296" s="3" t="s">
-        <v>730</v>
+        <v>679</v>
       </c>
       <c r="E296" s="3"/>
       <c r="F296" s="4" t="s">
-        <v>731</v>
+        <v>680</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="5" t="s">
-        <v>1110</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="297" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
@@ -11561,15 +11557,15 @@
       </c>
       <c r="C297" s="3"/>
       <c r="D297" s="3" t="s">
-        <v>732</v>
+        <v>681</v>
       </c>
       <c r="E297" s="3"/>
       <c r="F297" s="4" t="s">
-        <v>733</v>
+        <v>682</v>
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="5" t="s">
-        <v>1111</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
@@ -11581,15 +11577,15 @@
       </c>
       <c r="C298" s="3"/>
       <c r="D298" s="3" t="s">
-        <v>734</v>
+        <v>683</v>
       </c>
       <c r="E298" s="3"/>
       <c r="F298" s="4" t="s">
-        <v>735</v>
+        <v>684</v>
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="5" t="s">
-        <v>736</v>
+        <v>685</v>
       </c>
     </row>
     <row r="299" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -11601,15 +11597,15 @@
       </c>
       <c r="C299" s="3"/>
       <c r="D299" s="3" t="s">
-        <v>737</v>
+        <v>686</v>
       </c>
       <c r="E299" s="3"/>
       <c r="F299" s="4" t="s">
-        <v>738</v>
+        <v>687</v>
       </c>
       <c r="G299" s="3"/>
       <c r="H299" s="5" t="s">
-        <v>1112</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="300" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -11621,15 +11617,15 @@
       </c>
       <c r="C300" s="3"/>
       <c r="D300" s="3" t="s">
-        <v>739</v>
+        <v>688</v>
       </c>
       <c r="E300" s="3"/>
       <c r="F300" s="4" t="s">
-        <v>740</v>
+        <v>1172</v>
       </c>
       <c r="G300" s="3"/>
       <c r="H300" s="5" t="s">
-        <v>1113</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="301" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -11641,15 +11637,15 @@
       </c>
       <c r="C301" s="3"/>
       <c r="D301" s="3" t="s">
-        <v>741</v>
+        <v>689</v>
       </c>
       <c r="E301" s="3"/>
       <c r="F301" s="4" t="s">
-        <v>742</v>
+        <v>690</v>
       </c>
       <c r="G301" s="3"/>
       <c r="H301" s="5" t="s">
-        <v>1114</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
@@ -11661,15 +11657,15 @@
       </c>
       <c r="C302" s="3"/>
       <c r="D302" s="3" t="s">
-        <v>743</v>
+        <v>691</v>
       </c>
       <c r="E302" s="3"/>
       <c r="F302" s="4" t="s">
-        <v>744</v>
+        <v>692</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="5" t="s">
-        <v>1115</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="303" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11681,15 +11677,15 @@
       </c>
       <c r="C303" s="3"/>
       <c r="D303" s="3" t="s">
-        <v>745</v>
+        <v>693</v>
       </c>
       <c r="E303" s="3"/>
       <c r="F303" s="4" t="s">
-        <v>746</v>
+        <v>694</v>
       </c>
       <c r="G303" s="3"/>
       <c r="H303" s="5" t="s">
-        <v>1116</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="304" spans="1:8" ht="331.2" x14ac:dyDescent="0.3">
@@ -11701,15 +11697,15 @@
       </c>
       <c r="C304" s="3"/>
       <c r="D304" s="3" t="s">
-        <v>747</v>
+        <v>695</v>
       </c>
       <c r="E304" s="3"/>
       <c r="F304" s="4" t="s">
-        <v>748</v>
+        <v>696</v>
       </c>
       <c r="G304" s="3"/>
       <c r="H304" s="5" t="s">
-        <v>1117</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="305" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -11721,15 +11717,15 @@
       </c>
       <c r="C305" s="3"/>
       <c r="D305" s="3" t="s">
-        <v>749</v>
+        <v>697</v>
       </c>
       <c r="E305" s="3"/>
       <c r="F305" s="4" t="s">
-        <v>750</v>
+        <v>1173</v>
       </c>
       <c r="G305" s="3"/>
       <c r="H305" s="5" t="s">
-        <v>1118</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="306" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -11741,15 +11737,15 @@
       </c>
       <c r="C306" s="3"/>
       <c r="D306" s="3" t="s">
-        <v>751</v>
+        <v>698</v>
       </c>
       <c r="E306" s="3"/>
       <c r="F306" s="4" t="s">
-        <v>752</v>
+        <v>699</v>
       </c>
       <c r="G306" s="3"/>
       <c r="H306" s="5" t="s">
-        <v>1119</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
@@ -11761,15 +11757,15 @@
       </c>
       <c r="C307" s="3"/>
       <c r="D307" s="3" t="s">
-        <v>753</v>
+        <v>700</v>
       </c>
       <c r="E307" s="3"/>
       <c r="F307" s="4" t="s">
-        <v>754</v>
+        <v>701</v>
       </c>
       <c r="G307" s="3"/>
       <c r="H307" s="5" t="s">
-        <v>1120</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="308" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -11781,15 +11777,15 @@
       </c>
       <c r="C308" s="3"/>
       <c r="D308" s="3" t="s">
-        <v>755</v>
+        <v>702</v>
       </c>
       <c r="E308" s="3"/>
       <c r="F308" s="4" t="s">
-        <v>756</v>
+        <v>1174</v>
       </c>
       <c r="G308" s="3"/>
       <c r="H308" s="5" t="s">
-        <v>1121</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="309" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -11801,15 +11797,15 @@
       </c>
       <c r="C309" s="3"/>
       <c r="D309" s="3" t="s">
-        <v>757</v>
+        <v>703</v>
       </c>
       <c r="E309" s="3"/>
       <c r="F309" s="4" t="s">
-        <v>758</v>
+        <v>704</v>
       </c>
       <c r="G309" s="3"/>
       <c r="H309" s="5" t="s">
-        <v>1122</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="310" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -11821,15 +11817,15 @@
       </c>
       <c r="C310" s="3"/>
       <c r="D310" s="3" t="s">
-        <v>759</v>
+        <v>705</v>
       </c>
       <c r="E310" s="3"/>
       <c r="F310" s="4" t="s">
-        <v>760</v>
+        <v>706</v>
       </c>
       <c r="G310" s="3"/>
       <c r="H310" s="5" t="s">
-        <v>1123</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="311" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -11841,15 +11837,15 @@
       </c>
       <c r="C311" s="3"/>
       <c r="D311" s="3" t="s">
-        <v>761</v>
+        <v>707</v>
       </c>
       <c r="E311" s="3"/>
       <c r="F311" s="4" t="s">
-        <v>762</v>
+        <v>708</v>
       </c>
       <c r="G311" s="3"/>
       <c r="H311" s="5" t="s">
-        <v>1124</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="312" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11861,15 +11857,15 @@
       </c>
       <c r="C312" s="3"/>
       <c r="D312" s="3" t="s">
-        <v>763</v>
+        <v>709</v>
       </c>
       <c r="E312" s="3"/>
       <c r="F312" s="4" t="s">
-        <v>764</v>
+        <v>710</v>
       </c>
       <c r="G312" s="3"/>
       <c r="H312" s="5" t="s">
-        <v>1125</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
@@ -11881,15 +11877,15 @@
       </c>
       <c r="C313" s="3"/>
       <c r="D313" s="3" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
       <c r="E313" s="3"/>
       <c r="F313" s="4" t="s">
-        <v>766</v>
+        <v>712</v>
       </c>
       <c r="G313" s="3"/>
       <c r="H313" s="5" t="s">
-        <v>767</v>
+        <v>713</v>
       </c>
     </row>
     <row r="314" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -11901,15 +11897,15 @@
       </c>
       <c r="C314" s="3"/>
       <c r="D314" s="3" t="s">
-        <v>768</v>
+        <v>714</v>
       </c>
       <c r="E314" s="3"/>
       <c r="F314" s="4" t="s">
-        <v>769</v>
+        <v>715</v>
       </c>
       <c r="G314" s="3"/>
       <c r="H314" s="5" t="s">
-        <v>1126</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="315" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11921,15 +11917,15 @@
       </c>
       <c r="C315" s="3"/>
       <c r="D315" s="3" t="s">
-        <v>770</v>
+        <v>716</v>
       </c>
       <c r="E315" s="3"/>
       <c r="F315" s="4" t="s">
-        <v>771</v>
+        <v>717</v>
       </c>
       <c r="G315" s="3"/>
       <c r="H315" s="5" t="s">
-        <v>772</v>
+        <v>718</v>
       </c>
     </row>
     <row r="316" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -11941,15 +11937,15 @@
       </c>
       <c r="C316" s="3"/>
       <c r="D316" s="3" t="s">
-        <v>773</v>
+        <v>719</v>
       </c>
       <c r="E316" s="3"/>
       <c r="F316" s="4" t="s">
-        <v>774</v>
+        <v>720</v>
       </c>
       <c r="G316" s="3"/>
       <c r="H316" s="5" t="s">
-        <v>1127</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="317" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -11961,15 +11957,15 @@
       </c>
       <c r="C317" s="3"/>
       <c r="D317" s="3" t="s">
-        <v>775</v>
+        <v>721</v>
       </c>
       <c r="E317" s="3"/>
       <c r="F317" s="4" t="s">
-        <v>776</v>
+        <v>722</v>
       </c>
       <c r="G317" s="3"/>
       <c r="H317" s="5" t="s">
-        <v>1128</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="318" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -11981,15 +11977,15 @@
       </c>
       <c r="C318" s="3"/>
       <c r="D318" s="3" t="s">
-        <v>777</v>
+        <v>723</v>
       </c>
       <c r="E318" s="3"/>
       <c r="F318" s="4" t="s">
-        <v>778</v>
+        <v>724</v>
       </c>
       <c r="G318" s="3"/>
       <c r="H318" s="5" t="s">
-        <v>1129</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="319" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12001,15 +11997,15 @@
       </c>
       <c r="C319" s="3"/>
       <c r="D319" s="3" t="s">
-        <v>779</v>
+        <v>725</v>
       </c>
       <c r="E319" s="3"/>
       <c r="F319" s="4" t="s">
-        <v>780</v>
+        <v>726</v>
       </c>
       <c r="G319" s="3"/>
       <c r="H319" s="5" t="s">
-        <v>1130</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="320" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12021,15 +12017,15 @@
       </c>
       <c r="C320" s="3"/>
       <c r="D320" s="3" t="s">
-        <v>781</v>
+        <v>727</v>
       </c>
       <c r="E320" s="3"/>
       <c r="F320" s="4" t="s">
-        <v>782</v>
+        <v>728</v>
       </c>
       <c r="G320" s="3"/>
       <c r="H320" s="5" t="s">
-        <v>783</v>
+        <v>729</v>
       </c>
     </row>
     <row r="321" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12041,15 +12037,15 @@
       </c>
       <c r="C321" s="3"/>
       <c r="D321" s="3" t="s">
-        <v>784</v>
+        <v>730</v>
       </c>
       <c r="E321" s="3"/>
       <c r="F321" s="4" t="s">
-        <v>785</v>
+        <v>731</v>
       </c>
       <c r="G321" s="3"/>
       <c r="H321" s="5" t="s">
-        <v>1131</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="322" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -12061,15 +12057,15 @@
       </c>
       <c r="C322" s="3"/>
       <c r="D322" s="3" t="s">
-        <v>786</v>
+        <v>732</v>
       </c>
       <c r="E322" s="3"/>
       <c r="F322" s="4" t="s">
-        <v>787</v>
+        <v>733</v>
       </c>
       <c r="G322" s="3"/>
       <c r="H322" s="5" t="s">
-        <v>1132</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="323" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -12081,15 +12077,15 @@
       </c>
       <c r="C323" s="3"/>
       <c r="D323" s="3" t="s">
-        <v>788</v>
+        <v>734</v>
       </c>
       <c r="E323" s="3"/>
       <c r="F323" s="4" t="s">
-        <v>789</v>
+        <v>735</v>
       </c>
       <c r="G323" s="3"/>
       <c r="H323" s="5" t="s">
-        <v>1133</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="324" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12101,15 +12097,15 @@
       </c>
       <c r="C324" s="3"/>
       <c r="D324" s="3" t="s">
-        <v>790</v>
+        <v>736</v>
       </c>
       <c r="E324" s="3"/>
       <c r="F324" s="4" t="s">
-        <v>791</v>
+        <v>737</v>
       </c>
       <c r="G324" s="3"/>
       <c r="H324" s="5" t="s">
-        <v>792</v>
+        <v>738</v>
       </c>
     </row>
     <row r="325" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
@@ -12121,15 +12117,15 @@
       </c>
       <c r="C325" s="3"/>
       <c r="D325" s="3" t="s">
-        <v>793</v>
+        <v>739</v>
       </c>
       <c r="E325" s="3"/>
       <c r="F325" s="4" t="s">
-        <v>794</v>
+        <v>740</v>
       </c>
       <c r="G325" s="3"/>
       <c r="H325" s="5" t="s">
-        <v>1134</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="326" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12141,15 +12137,15 @@
       </c>
       <c r="C326" s="3"/>
       <c r="D326" s="3" t="s">
-        <v>795</v>
+        <v>741</v>
       </c>
       <c r="E326" s="3"/>
       <c r="F326" s="4" t="s">
-        <v>796</v>
+        <v>742</v>
       </c>
       <c r="G326" s="3"/>
       <c r="H326" s="5" t="s">
-        <v>1135</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="327" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12161,15 +12157,15 @@
       </c>
       <c r="C327" s="3"/>
       <c r="D327" s="3" t="s">
-        <v>797</v>
+        <v>743</v>
       </c>
       <c r="E327" s="3"/>
       <c r="F327" s="4" t="s">
-        <v>798</v>
+        <v>744</v>
       </c>
       <c r="G327" s="3"/>
       <c r="H327" s="5" t="s">
-        <v>1136</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="328" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12181,15 +12177,15 @@
       </c>
       <c r="C328" s="3"/>
       <c r="D328" s="3" t="s">
-        <v>799</v>
+        <v>745</v>
       </c>
       <c r="E328" s="3"/>
       <c r="F328" s="4" t="s">
-        <v>800</v>
+        <v>746</v>
       </c>
       <c r="G328" s="3"/>
       <c r="H328" s="5" t="s">
-        <v>801</v>
+        <v>747</v>
       </c>
     </row>
     <row r="329" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12201,15 +12197,15 @@
       </c>
       <c r="C329" s="3"/>
       <c r="D329" s="3" t="s">
-        <v>802</v>
+        <v>748</v>
       </c>
       <c r="E329" s="3"/>
       <c r="F329" s="4" t="s">
-        <v>803</v>
+        <v>1175</v>
       </c>
       <c r="G329" s="3"/>
       <c r="H329" s="5" t="s">
-        <v>1137</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="330" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -12221,15 +12217,15 @@
       </c>
       <c r="C330" s="3"/>
       <c r="D330" s="3" t="s">
-        <v>804</v>
+        <v>749</v>
       </c>
       <c r="E330" s="3"/>
       <c r="F330" s="4" t="s">
-        <v>805</v>
+        <v>750</v>
       </c>
       <c r="G330" s="3"/>
       <c r="H330" s="5" t="s">
-        <v>1138</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="331" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12241,15 +12237,15 @@
       </c>
       <c r="C331" s="3"/>
       <c r="D331" s="3" t="s">
-        <v>806</v>
+        <v>751</v>
       </c>
       <c r="E331" s="3"/>
       <c r="F331" s="4" t="s">
-        <v>807</v>
+        <v>752</v>
       </c>
       <c r="G331" s="3"/>
       <c r="H331" s="5" t="s">
-        <v>808</v>
+        <v>753</v>
       </c>
     </row>
     <row r="332" spans="1:8" ht="144" x14ac:dyDescent="0.3">
@@ -12261,15 +12257,15 @@
       </c>
       <c r="C332" s="3"/>
       <c r="D332" s="3" t="s">
-        <v>809</v>
+        <v>754</v>
       </c>
       <c r="E332" s="3"/>
       <c r="F332" s="4" t="s">
-        <v>810</v>
+        <v>755</v>
       </c>
       <c r="G332" s="3"/>
       <c r="H332" s="5" t="s">
-        <v>1139</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
@@ -12279,19 +12275,19 @@
       </c>
       <c r="C333" s="3"/>
       <c r="D333" s="3" t="s">
-        <v>811</v>
+        <v>756</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>812</v>
+        <v>757</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>813</v>
+        <v>758</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>814</v>
+        <v>759</v>
       </c>
       <c r="H333" s="5" t="s">
-        <v>815</v>
+        <v>760</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
@@ -12301,19 +12297,19 @@
       </c>
       <c r="C334" s="3"/>
       <c r="D334" s="3" t="s">
-        <v>816</v>
+        <v>761</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>817</v>
+        <v>762</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>818</v>
+        <v>763</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>819</v>
+        <v>764</v>
       </c>
       <c r="H334" s="5" t="s">
-        <v>1140</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="335" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12325,15 +12321,15 @@
       </c>
       <c r="C335" s="3"/>
       <c r="D335" s="3" t="s">
-        <v>820</v>
+        <v>765</v>
       </c>
       <c r="E335" s="3"/>
       <c r="F335" s="4" t="s">
-        <v>821</v>
+        <v>1176</v>
       </c>
       <c r="G335" s="3"/>
       <c r="H335" s="5" t="s">
-        <v>1141</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="336" spans="1:8" ht="72" x14ac:dyDescent="0.3">
@@ -12345,15 +12341,15 @@
       </c>
       <c r="C336" s="3"/>
       <c r="D336" s="3" t="s">
-        <v>822</v>
+        <v>766</v>
       </c>
       <c r="E336" s="3"/>
       <c r="F336" s="4" t="s">
-        <v>823</v>
+        <v>767</v>
       </c>
       <c r="G336" s="3"/>
       <c r="H336" s="5" t="s">
-        <v>1142</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="337" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12365,15 +12361,15 @@
       </c>
       <c r="C337" s="3"/>
       <c r="D337" s="3" t="s">
-        <v>824</v>
+        <v>768</v>
       </c>
       <c r="E337" s="3"/>
       <c r="F337" s="4" t="s">
-        <v>825</v>
+        <v>769</v>
       </c>
       <c r="G337" s="3"/>
       <c r="H337" s="5" t="s">
-        <v>1143</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="338" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12385,15 +12381,15 @@
       </c>
       <c r="C338" s="3"/>
       <c r="D338" s="3" t="s">
-        <v>826</v>
+        <v>770</v>
       </c>
       <c r="E338" s="3"/>
       <c r="F338" s="4" t="s">
-        <v>827</v>
+        <v>771</v>
       </c>
       <c r="G338" s="3"/>
       <c r="H338" s="5" t="s">
-        <v>1144</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="339" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12405,15 +12401,15 @@
       </c>
       <c r="C339" s="3"/>
       <c r="D339" s="3" t="s">
-        <v>828</v>
+        <v>772</v>
       </c>
       <c r="E339" s="3"/>
       <c r="F339" s="4" t="s">
-        <v>829</v>
+        <v>773</v>
       </c>
       <c r="G339" s="3"/>
       <c r="H339" s="5" t="s">
-        <v>1145</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="340" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12425,15 +12421,15 @@
       </c>
       <c r="C340" s="3"/>
       <c r="D340" s="3" t="s">
-        <v>830</v>
+        <v>774</v>
       </c>
       <c r="E340" s="3"/>
       <c r="F340" s="4" t="s">
-        <v>831</v>
+        <v>775</v>
       </c>
       <c r="G340" s="3"/>
       <c r="H340" s="5" t="s">
-        <v>1146</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="341" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -12445,15 +12441,15 @@
       </c>
       <c r="C341" s="3"/>
       <c r="D341" s="3" t="s">
-        <v>832</v>
+        <v>776</v>
       </c>
       <c r="E341" s="3"/>
       <c r="F341" s="4" t="s">
-        <v>833</v>
+        <v>777</v>
       </c>
       <c r="G341" s="3"/>
       <c r="H341" s="5" t="s">
-        <v>1147</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="342" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12465,15 +12461,15 @@
       </c>
       <c r="C342" s="3"/>
       <c r="D342" s="3" t="s">
-        <v>834</v>
+        <v>778</v>
       </c>
       <c r="E342" s="3"/>
       <c r="F342" s="4" t="s">
-        <v>835</v>
+        <v>779</v>
       </c>
       <c r="G342" s="3"/>
       <c r="H342" s="5" t="s">
-        <v>1148</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="343" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -12485,15 +12481,15 @@
       </c>
       <c r="C343" s="3"/>
       <c r="D343" s="3" t="s">
-        <v>836</v>
+        <v>780</v>
       </c>
       <c r="E343" s="3"/>
       <c r="F343" s="4" t="s">
-        <v>837</v>
+        <v>781</v>
       </c>
       <c r="G343" s="3"/>
       <c r="H343" s="5" t="s">
-        <v>1149</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="344" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12503,19 +12499,19 @@
       </c>
       <c r="C344" s="3"/>
       <c r="D344" s="3" t="s">
-        <v>838</v>
+        <v>782</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>839</v>
+        <v>783</v>
       </c>
       <c r="F344" s="4" t="s">
-        <v>840</v>
+        <v>1177</v>
       </c>
       <c r="G344" s="3" t="s">
-        <v>841</v>
+        <v>784</v>
       </c>
       <c r="H344" s="5" t="s">
-        <v>1150</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="345" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12527,15 +12523,15 @@
       </c>
       <c r="C345" s="3"/>
       <c r="D345" s="3" t="s">
-        <v>842</v>
+        <v>785</v>
       </c>
       <c r="E345" s="3"/>
       <c r="F345" s="4" t="s">
-        <v>843</v>
+        <v>786</v>
       </c>
       <c r="G345" s="3"/>
       <c r="H345" s="5" t="s">
-        <v>1151</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="346" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12547,15 +12543,15 @@
       </c>
       <c r="C346" s="3"/>
       <c r="D346" s="3" t="s">
-        <v>844</v>
+        <v>787</v>
       </c>
       <c r="E346" s="3"/>
       <c r="F346" s="4" t="s">
-        <v>845</v>
+        <v>788</v>
       </c>
       <c r="G346" s="3"/>
       <c r="H346" s="5" t="s">
-        <v>1152</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="347" spans="1:8" ht="216" x14ac:dyDescent="0.3">
@@ -12567,15 +12563,15 @@
       </c>
       <c r="C347" s="3"/>
       <c r="D347" s="3" t="s">
-        <v>846</v>
+        <v>789</v>
       </c>
       <c r="E347" s="3"/>
       <c r="F347" s="4" t="s">
-        <v>847</v>
+        <v>790</v>
       </c>
       <c r="G347" s="3"/>
       <c r="H347" s="5" t="s">
-        <v>1153</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="348" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12587,15 +12583,15 @@
       </c>
       <c r="C348" s="3"/>
       <c r="D348" s="3" t="s">
-        <v>848</v>
+        <v>791</v>
       </c>
       <c r="E348" s="3"/>
       <c r="F348" s="4" t="s">
-        <v>849</v>
+        <v>792</v>
       </c>
       <c r="G348" s="3"/>
       <c r="H348" s="5" t="s">
-        <v>1154</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.3">
@@ -12605,19 +12601,19 @@
       </c>
       <c r="C349" s="3"/>
       <c r="D349" s="3" t="s">
-        <v>850</v>
+        <v>793</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>851</v>
+        <v>794</v>
       </c>
       <c r="F349" s="4" t="s">
-        <v>852</v>
+        <v>795</v>
       </c>
       <c r="G349" s="3" t="s">
-        <v>853</v>
+        <v>796</v>
       </c>
       <c r="H349" s="5" t="s">
-        <v>1155</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.3">
@@ -12629,15 +12625,15 @@
       </c>
       <c r="C350" s="3"/>
       <c r="D350" s="3" t="s">
-        <v>854</v>
+        <v>797</v>
       </c>
       <c r="E350" s="3"/>
       <c r="F350" s="4" t="s">
-        <v>855</v>
+        <v>798</v>
       </c>
       <c r="G350" s="3"/>
       <c r="H350" s="5" t="s">
-        <v>1156</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="351" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -12649,15 +12645,15 @@
       </c>
       <c r="C351" s="3"/>
       <c r="D351" s="3" t="s">
-        <v>856</v>
+        <v>799</v>
       </c>
       <c r="E351" s="3"/>
       <c r="F351" s="4" t="s">
-        <v>857</v>
+        <v>800</v>
       </c>
       <c r="G351" s="3"/>
       <c r="H351" s="5" t="s">
-        <v>1157</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="352" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -12669,15 +12665,15 @@
       </c>
       <c r="C352" s="3"/>
       <c r="D352" s="3" t="s">
-        <v>858</v>
+        <v>801</v>
       </c>
       <c r="E352" s="3"/>
       <c r="F352" s="4" t="s">
-        <v>859</v>
+        <v>802</v>
       </c>
       <c r="G352" s="3"/>
       <c r="H352" s="5" t="s">
-        <v>1158</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="353" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -12689,15 +12685,15 @@
       </c>
       <c r="C353" s="3"/>
       <c r="D353" s="3" t="s">
-        <v>860</v>
+        <v>803</v>
       </c>
       <c r="E353" s="3"/>
       <c r="F353" s="4" t="s">
-        <v>861</v>
+        <v>804</v>
       </c>
       <c r="G353" s="3"/>
       <c r="H353" s="5" t="s">
-        <v>1159</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="354" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -12709,15 +12705,15 @@
       </c>
       <c r="C354" s="3"/>
       <c r="D354" s="3" t="s">
-        <v>862</v>
+        <v>805</v>
       </c>
       <c r="E354" s="3"/>
       <c r="F354" s="4" t="s">
-        <v>863</v>
+        <v>806</v>
       </c>
       <c r="G354" s="3"/>
       <c r="H354" s="5" t="s">
-        <v>1160</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.3">
@@ -12729,15 +12725,15 @@
       </c>
       <c r="C355" s="3"/>
       <c r="D355" s="3" t="s">
-        <v>864</v>
+        <v>807</v>
       </c>
       <c r="E355" s="3"/>
       <c r="F355" s="4" t="s">
-        <v>744</v>
+        <v>692</v>
       </c>
       <c r="G355" s="3"/>
       <c r="H355" s="5" t="s">
-        <v>1161</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="356" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
@@ -12749,15 +12745,15 @@
       </c>
       <c r="C356" s="3"/>
       <c r="D356" s="3" t="s">
-        <v>865</v>
+        <v>808</v>
       </c>
       <c r="E356" s="3"/>
       <c r="F356" s="4" t="s">
-        <v>883</v>
+        <v>1179</v>
       </c>
       <c r="G356" s="3"/>
       <c r="H356" s="5" t="s">
-        <v>1162</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="357" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
@@ -12769,15 +12765,15 @@
       </c>
       <c r="C357" s="3"/>
       <c r="D357" s="3" t="s">
-        <v>866</v>
+        <v>809</v>
       </c>
       <c r="E357" s="3"/>
       <c r="F357" s="4" t="s">
-        <v>884</v>
+        <v>826</v>
       </c>
       <c r="G357" s="3"/>
       <c r="H357" s="5" t="s">
-        <v>1163</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="358" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12789,15 +12785,15 @@
       </c>
       <c r="C358" s="3"/>
       <c r="D358" s="3" t="s">
-        <v>867</v>
+        <v>810</v>
       </c>
       <c r="E358" s="3"/>
       <c r="F358" s="4" t="s">
-        <v>885</v>
+        <v>827</v>
       </c>
       <c r="G358" s="3"/>
       <c r="H358" s="5" t="s">
-        <v>1164</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="359" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -12809,15 +12805,15 @@
       </c>
       <c r="C359" s="3"/>
       <c r="D359" s="3" t="s">
-        <v>868</v>
+        <v>811</v>
       </c>
       <c r="E359" s="3"/>
       <c r="F359" s="4" t="s">
-        <v>886</v>
+        <v>828</v>
       </c>
       <c r="G359" s="3"/>
       <c r="H359" s="5" t="s">
-        <v>1165</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="360" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
@@ -12829,15 +12825,15 @@
       </c>
       <c r="C360" s="3"/>
       <c r="D360" s="3" t="s">
-        <v>869</v>
+        <v>812</v>
       </c>
       <c r="E360" s="3"/>
       <c r="F360" s="4" t="s">
-        <v>887</v>
+        <v>829</v>
       </c>
       <c r="G360" s="3"/>
       <c r="H360" s="5" t="s">
-        <v>1166</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="361" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -12849,15 +12845,15 @@
       </c>
       <c r="C361" s="3"/>
       <c r="D361" s="3" t="s">
-        <v>870</v>
+        <v>813</v>
       </c>
       <c r="E361" s="3"/>
       <c r="F361" s="4" t="s">
-        <v>888</v>
+        <v>830</v>
       </c>
       <c r="G361" s="3"/>
       <c r="H361" s="5" t="s">
-        <v>1167</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="362" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
@@ -12869,15 +12865,15 @@
       </c>
       <c r="C362" s="3"/>
       <c r="D362" s="3" t="s">
-        <v>871</v>
+        <v>814</v>
       </c>
       <c r="E362" s="3"/>
       <c r="F362" s="4" t="s">
-        <v>889</v>
+        <v>831</v>
       </c>
       <c r="G362" s="3"/>
       <c r="H362" s="5" t="s">
-        <v>1168</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="363" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
@@ -12889,15 +12885,15 @@
       </c>
       <c r="C363" s="3"/>
       <c r="D363" s="3" t="s">
-        <v>872</v>
+        <v>815</v>
       </c>
       <c r="E363" s="3"/>
       <c r="F363" s="4" t="s">
-        <v>890</v>
+        <v>832</v>
       </c>
       <c r="G363" s="3"/>
       <c r="H363" s="5" t="s">
-        <v>1169</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="364" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
@@ -12909,15 +12905,15 @@
       </c>
       <c r="C364" s="3"/>
       <c r="D364" s="3" t="s">
-        <v>873</v>
+        <v>816</v>
       </c>
       <c r="E364" s="3"/>
       <c r="F364" s="4" t="s">
-        <v>891</v>
+        <v>833</v>
       </c>
       <c r="G364" s="3"/>
       <c r="H364" s="5" t="s">
-        <v>1170</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="365" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -12929,15 +12925,15 @@
       </c>
       <c r="C365" s="3"/>
       <c r="D365" s="3" t="s">
-        <v>874</v>
+        <v>817</v>
       </c>
       <c r="E365" s="3"/>
       <c r="F365" s="4" t="s">
-        <v>892</v>
+        <v>834</v>
       </c>
       <c r="G365" s="3"/>
       <c r="H365" s="5" t="s">
-        <v>1171</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="366" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12949,15 +12945,15 @@
       </c>
       <c r="C366" s="3"/>
       <c r="D366" s="3" t="s">
-        <v>875</v>
+        <v>818</v>
       </c>
       <c r="E366" s="3"/>
       <c r="F366" s="4" t="s">
-        <v>893</v>
+        <v>835</v>
       </c>
       <c r="G366" s="3"/>
       <c r="H366" s="5" t="s">
-        <v>1172</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="367" spans="1:8" ht="216" x14ac:dyDescent="0.3">
@@ -12969,15 +12965,15 @@
       </c>
       <c r="C367" s="3"/>
       <c r="D367" s="3" t="s">
-        <v>876</v>
+        <v>819</v>
       </c>
       <c r="E367" s="3"/>
       <c r="F367" s="4" t="s">
-        <v>894</v>
+        <v>836</v>
       </c>
       <c r="G367" s="3"/>
       <c r="H367" s="5" t="s">
-        <v>1173</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="368" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
@@ -12988,18 +12984,18 @@
         <v>5</v>
       </c>
       <c r="C368" s="15" t="s">
-        <v>895</v>
+        <v>837</v>
       </c>
       <c r="D368" s="14" t="s">
-        <v>896</v>
+        <v>838</v>
       </c>
       <c r="E368" s="3"/>
       <c r="F368" s="4" t="s">
-        <v>897</v>
+        <v>839</v>
       </c>
       <c r="G368" s="3"/>
       <c r="H368" s="5" t="s">
-        <v>1174</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="369" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -13011,15 +13007,15 @@
       </c>
       <c r="C369" s="3"/>
       <c r="D369" s="3" t="s">
-        <v>877</v>
+        <v>820</v>
       </c>
       <c r="E369" s="3"/>
       <c r="F369" s="4" t="s">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="G369" s="3"/>
       <c r="H369" s="5" t="s">
-        <v>1175</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="370" spans="1:8" ht="259.2" x14ac:dyDescent="0.3">
@@ -13031,15 +13027,15 @@
       </c>
       <c r="C370" s="3"/>
       <c r="D370" s="3" t="s">
-        <v>878</v>
+        <v>821</v>
       </c>
       <c r="E370" s="3"/>
       <c r="F370" s="4" t="s">
-        <v>899</v>
+        <v>841</v>
       </c>
       <c r="G370" s="3"/>
       <c r="H370" s="5" t="s">
-        <v>1176</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="371" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -13051,15 +13047,15 @@
       </c>
       <c r="C371" s="3"/>
       <c r="D371" s="3" t="s">
-        <v>879</v>
+        <v>822</v>
       </c>
       <c r="E371" s="3"/>
       <c r="F371" s="4" t="s">
-        <v>900</v>
+        <v>842</v>
       </c>
       <c r="G371" s="3"/>
       <c r="H371" s="5" t="s">
-        <v>1177</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="372" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -13071,15 +13067,15 @@
       </c>
       <c r="C372" s="3"/>
       <c r="D372" s="3" t="s">
-        <v>880</v>
+        <v>823</v>
       </c>
       <c r="E372" s="3"/>
       <c r="F372" s="4" t="s">
-        <v>901</v>
+        <v>1178</v>
       </c>
       <c r="G372" s="3"/>
       <c r="H372" s="5" t="s">
-        <v>1178</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.3">
@@ -13091,15 +13087,15 @@
       </c>
       <c r="C373" s="3"/>
       <c r="D373" s="3" t="s">
-        <v>881</v>
+        <v>824</v>
       </c>
       <c r="E373" s="3"/>
       <c r="F373" s="4" t="s">
-        <v>902</v>
+        <v>843</v>
       </c>
       <c r="G373" s="3"/>
       <c r="H373" s="5" t="s">
-        <v>903</v>
+        <v>844</v>
       </c>
     </row>
     <row r="374" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -13111,15 +13107,15 @@
       </c>
       <c r="C374" s="7"/>
       <c r="D374" s="7" t="s">
-        <v>882</v>
+        <v>825</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="8" t="s">
-        <v>904</v>
+        <v>845</v>
       </c>
       <c r="G374" s="7"/>
       <c r="H374" s="9" t="s">
-        <v>1179</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel/pci-dss/pcidss-4_0.xlsx
+++ b/tools/excel/pci-dss/pcidss-4_0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\tarkadia\projects\intuitem\ciso-assistant-community\tools\excel\pci-dss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464575E1-C45A-4BD9-81FB-3436128585DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E8011A-2F0E-4ACE-A8FF-E4864DE2D9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="-15750" windowWidth="12570" windowHeight="15855" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7965" yWindow="-11535" windowWidth="17730" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="1179">
   <si>
     <t>type</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>name</t>
-  </si>
-  <si>
-    <t>Payment Card Industry Data Security Standard</t>
   </si>
   <si>
     <t>description</t>
@@ -5467,55 +5464,55 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5537,15 +5534,15 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -5553,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -5569,31 +5566,31 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5618,13 +5615,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>8</v>
@@ -5633,13 +5630,13 @@
         <v>10</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -5650,11 +5647,11 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H2" s="5"/>
     </row>
@@ -5665,499 +5662,499 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="5" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="3">
         <v>4</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="5" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="5" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3">
         <v>4</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3">
         <v>4</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="5" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="3">
         <v>4</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="5" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3">
         <v>4</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="5" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3">
         <v>4</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="5" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="3">
         <v>4</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="5" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="3">
         <v>4</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="5" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="3">
         <v>3</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3">
         <v>4</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="4" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="5" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3">
         <v>4</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="3">
         <v>4</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="5" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3">
         <v>3</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="3">
         <v>4</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3">
         <v>4</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3">
         <v>4</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="5" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
       </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="3">
         <v>3</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="3">
         <v>4</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="4" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -6167,299 +6164,299 @@
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="H28" s="5" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="3">
         <v>3</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="3">
         <v>4</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="5" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="3">
         <v>4</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="5" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="3">
         <v>3</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="3">
         <v>4</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="5" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="3">
         <v>4</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" s="3">
         <v>4</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="3">
         <v>4</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="3">
         <v>4</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="5" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3">
         <v>4</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="3">
         <v>4</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="5" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3">
         <v>3</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G40" s="3"/>
       <c r="H40" s="5" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="3">
         <v>4</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="5" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="3">
         <v>4</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="5" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
@@ -6470,11 +6467,11 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H43" s="5"/>
     </row>
@@ -6488,742 +6485,742 @@
         <v>5</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="G44" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="H44" s="5" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="3">
         <v>3</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="5" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="3">
         <v>4</v>
       </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="4" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G46" s="3"/>
       <c r="H46" s="5" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="3">
         <v>4</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="5" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="3">
         <v>3</v>
       </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="5" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="3">
         <v>4</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G49" s="3"/>
       <c r="H49" s="5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B50" s="3">
         <v>3</v>
       </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="4" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="5" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="3">
         <v>4</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="5" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3">
         <v>5</v>
       </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="5" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" s="3">
         <v>5</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="5" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="3">
         <v>5</v>
       </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B55" s="3">
         <v>4</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G55" s="3"/>
       <c r="H55" s="5" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56" s="3">
         <v>4</v>
       </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="5" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57" s="3">
         <v>3</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="3">
         <v>4</v>
       </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="3">
         <v>4</v>
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B60" s="3">
         <v>3</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="4" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="5" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B61" s="3">
         <v>4</v>
       </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="4" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="5" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B62" s="3">
         <v>5</v>
       </c>
       <c r="C62" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D62" s="14" t="s">
         <v>164</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>165</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="4" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="5" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B63" s="3">
         <v>5</v>
       </c>
       <c r="C63" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>166</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>167</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="5" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B64" s="3">
         <v>5</v>
       </c>
       <c r="C64" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D64" s="14" t="s">
         <v>169</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>170</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="4" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="5" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B65" s="3">
         <v>3</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B66" s="3">
         <v>4</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B67" s="3">
         <v>5</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="5" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B68" s="3">
         <v>5</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B69" s="3">
         <v>5</v>
       </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B70" s="3">
         <v>5</v>
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B71" s="3">
         <v>3</v>
       </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B72" s="3">
         <v>4</v>
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="5" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B73" s="3">
         <v>4</v>
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="5" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B74" s="3">
         <v>4</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B75" s="3">
         <v>4</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G75" s="3"/>
       <c r="H75" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B76" s="3">
         <v>4</v>
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E76" s="3"/>
       <c r="F76" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B77" s="3">
         <v>4</v>
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="4" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B78" s="3">
         <v>4</v>
       </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B79" s="3">
         <v>4</v>
       </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B80" s="3">
         <v>4</v>
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="5" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -7233,179 +7230,179 @@
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="F81" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G81" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="H81" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B82" s="3">
         <v>3</v>
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="4" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B83" s="3">
         <v>4</v>
       </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="4" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B84" s="3">
         <v>4</v>
       </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B85" s="3">
         <v>3</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G85" s="3"/>
       <c r="H85" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B86" s="3">
         <v>4</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B87" s="3">
         <v>5</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="4" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G87" s="3"/>
       <c r="H87" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B88" s="3">
         <v>5</v>
       </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B89" s="3">
         <v>4</v>
       </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
@@ -7416,11 +7413,11 @@
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H90" s="5"/>
     </row>
@@ -7431,359 +7428,359 @@
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E91" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="F91" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="G91" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="H91" s="5" t="s">
         <v>227</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B92" s="3">
         <v>3</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G92" s="3"/>
       <c r="H92" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B93" s="3">
         <v>4</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="4" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="5" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B94" s="3">
         <v>4</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G94" s="3"/>
       <c r="H94" s="5" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B95" s="3">
         <v>3</v>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G95" s="3"/>
       <c r="H95" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B96" s="3">
         <v>4</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="5" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B97" s="3">
         <v>4</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G97" s="3"/>
       <c r="H97" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B98" s="3">
         <v>4</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B99" s="3">
         <v>5</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G99" s="3"/>
       <c r="H99" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B100" s="3">
         <v>3</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B101" s="3">
         <v>4</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B102" s="3">
         <v>4</v>
       </c>
       <c r="C102" s="3"/>
       <c r="D102" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="4" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G102" s="3"/>
       <c r="H102" s="5" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B103" s="3">
         <v>5</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="5" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="104" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B104" s="3">
         <v>4</v>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="5" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B105" s="3">
         <v>4</v>
       </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G105" s="3"/>
       <c r="H105" s="5" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B106" s="3">
         <v>4</v>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="107" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B107" s="3">
         <v>3</v>
       </c>
       <c r="C107" s="3"/>
       <c r="D107" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G107" s="3"/>
       <c r="H107" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B108" s="3">
         <v>4</v>
       </c>
       <c r="C108" s="3"/>
       <c r="D108" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
@@ -7793,499 +7790,499 @@
       </c>
       <c r="C109" s="3"/>
       <c r="D109" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E109" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="F109" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="G109" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="H109" s="5" t="s">
         <v>272</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="110" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B110" s="3">
         <v>3</v>
       </c>
       <c r="C110" s="3"/>
       <c r="D110" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B111" s="3">
         <v>4</v>
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G111" s="3"/>
       <c r="H111" s="5" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B112" s="3">
         <v>4</v>
       </c>
       <c r="C112" s="3"/>
       <c r="D112" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="4" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G112" s="3"/>
       <c r="H112" s="5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B113" s="3">
         <v>3</v>
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="4" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G113" s="3"/>
       <c r="H113" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B114" s="3">
         <v>4</v>
       </c>
       <c r="C114" s="3"/>
       <c r="D114" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="5" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B115" s="3">
         <v>4</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="5" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="116" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B116" s="3">
         <v>4</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="5" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B117" s="3">
         <v>5</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="5" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B118" s="3">
         <v>4</v>
       </c>
       <c r="C118" s="3"/>
       <c r="D118" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="4" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B119" s="3">
         <v>3</v>
       </c>
       <c r="C119" s="3"/>
       <c r="D119" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G119" s="3"/>
       <c r="H119" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B120" s="3">
         <v>4</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="4" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G120" s="3"/>
       <c r="H120" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B121" s="3">
         <v>4</v>
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B122" s="3">
         <v>4</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G122" s="3"/>
       <c r="H122" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B123" s="3">
         <v>3</v>
       </c>
       <c r="C123" s="3"/>
       <c r="D123" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G123" s="3"/>
       <c r="H123" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B124" s="3">
         <v>4</v>
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="4" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G124" s="3"/>
       <c r="H124" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B125" s="3">
         <v>4</v>
       </c>
       <c r="C125" s="3"/>
       <c r="D125" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B126" s="3">
         <v>4</v>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G126" s="3"/>
       <c r="H126" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B127" s="3">
         <v>3</v>
       </c>
       <c r="C127" s="3"/>
       <c r="D127" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G127" s="3"/>
       <c r="H127" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B128" s="3">
         <v>4</v>
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="4" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G128" s="3"/>
       <c r="H128" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B129" s="3">
         <v>4</v>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G129" s="3"/>
       <c r="H129" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="130" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B130" s="3">
         <v>4</v>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G130" s="3"/>
       <c r="H130" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B131" s="3">
         <v>4</v>
       </c>
       <c r="C131" s="3"/>
       <c r="D131" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G131" s="3"/>
       <c r="H131" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B132" s="3">
         <v>4</v>
       </c>
       <c r="C132" s="3"/>
       <c r="D132" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G132" s="3"/>
       <c r="H132" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="133" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B133" s="3">
         <v>4</v>
       </c>
       <c r="C133" s="3"/>
       <c r="D133" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
@@ -8296,11 +8293,11 @@
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F134" s="4"/>
       <c r="G134" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H134" s="5"/>
     </row>
@@ -8311,319 +8308,319 @@
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E135" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="E135" s="3" t="s">
+      <c r="F135" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="F135" s="4" t="s">
+      <c r="G135" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="H135" s="5" t="s">
         <v>329</v>
-      </c>
-      <c r="H135" s="5" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B136" s="3">
         <v>3</v>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G136" s="3"/>
       <c r="H136" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B137" s="3">
         <v>4</v>
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="4" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G137" s="3"/>
       <c r="H137" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="138" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B138" s="3">
         <v>4</v>
       </c>
       <c r="C138" s="3"/>
       <c r="D138" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G138" s="3"/>
       <c r="H138" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B139" s="3">
         <v>3</v>
       </c>
       <c r="C139" s="3"/>
       <c r="D139" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G139" s="3"/>
       <c r="H139" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="140" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B140" s="3">
         <v>4</v>
       </c>
       <c r="C140" s="3"/>
       <c r="D140" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G140" s="3"/>
       <c r="H140" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="141" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B141" s="3">
         <v>4</v>
       </c>
       <c r="C141" s="3"/>
       <c r="D141" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G141" s="3"/>
       <c r="H141" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B142" s="3">
         <v>4</v>
       </c>
       <c r="C142" s="3"/>
       <c r="D142" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G142" s="3"/>
       <c r="H142" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B143" s="3">
         <v>4</v>
       </c>
       <c r="C143" s="3"/>
       <c r="D143" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="4" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G143" s="3"/>
       <c r="H143" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B144" s="3">
         <v>4</v>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G144" s="3"/>
       <c r="H144" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B145" s="3">
         <v>5</v>
       </c>
       <c r="C145" s="3"/>
       <c r="D145" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="4" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G145" s="3"/>
       <c r="H145" s="5" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B146" s="3">
         <v>4</v>
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E146" s="3"/>
       <c r="F146" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G146" s="3"/>
       <c r="H146" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B147" s="3">
         <v>3</v>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E147" s="3"/>
       <c r="F147" s="4" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G147" s="3"/>
       <c r="H147" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B148" s="3">
         <v>4</v>
       </c>
       <c r="C148" s="3"/>
       <c r="D148" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E148" s="3"/>
       <c r="F148" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="5" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B149" s="3">
         <v>4</v>
       </c>
       <c r="C149" s="3"/>
       <c r="D149" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="4" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G149" s="3"/>
       <c r="H149" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B150" s="3">
         <v>4</v>
       </c>
       <c r="C150" s="3"/>
       <c r="D150" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G150" s="3"/>
       <c r="H150" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
@@ -8633,719 +8630,719 @@
       </c>
       <c r="C151" s="3"/>
       <c r="D151" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E151" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E151" s="3" t="s">
+      <c r="F151" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="G151" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="G151" s="3" t="s">
-        <v>365</v>
-      </c>
       <c r="H151" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="152" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B152" s="3">
         <v>3</v>
       </c>
       <c r="C152" s="3"/>
       <c r="D152" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E152" s="3"/>
       <c r="F152" s="4" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G152" s="3"/>
       <c r="H152" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="153" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B153" s="3">
         <v>4</v>
       </c>
       <c r="C153" s="3"/>
       <c r="D153" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E153" s="3"/>
       <c r="F153" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G153" s="3"/>
       <c r="H153" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="154" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B154" s="3">
         <v>4</v>
       </c>
       <c r="C154" s="3"/>
       <c r="D154" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E154" s="3"/>
       <c r="F154" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G154" s="3"/>
       <c r="H154" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="155" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B155" s="3">
         <v>3</v>
       </c>
       <c r="C155" s="3"/>
       <c r="D155" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G155" s="3"/>
       <c r="H155" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="156" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B156" s="3">
         <v>4</v>
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E156" s="3"/>
       <c r="F156" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G156" s="3"/>
       <c r="H156" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B157" s="3">
         <v>4</v>
       </c>
       <c r="C157" s="3"/>
       <c r="D157" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G157" s="3"/>
       <c r="H157" s="5" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="158" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B158" s="3">
         <v>4</v>
       </c>
       <c r="C158" s="3"/>
       <c r="D158" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G158" s="3"/>
       <c r="H158" s="5" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B159" s="3">
         <v>4</v>
       </c>
       <c r="C159" s="3"/>
       <c r="D159" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E159" s="3"/>
       <c r="F159" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G159" s="3"/>
       <c r="H159" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B160" s="3">
         <v>4</v>
       </c>
       <c r="C160" s="3"/>
       <c r="D160" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="4" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G160" s="3"/>
       <c r="H160" s="5" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B161" s="3">
         <v>4</v>
       </c>
       <c r="C161" s="3"/>
       <c r="D161" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E161" s="3"/>
       <c r="F161" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G161" s="3"/>
       <c r="H161" s="5" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B162" s="3">
         <v>4</v>
       </c>
       <c r="C162" s="3"/>
       <c r="D162" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E162" s="3"/>
       <c r="F162" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G162" s="3"/>
       <c r="H162" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B163" s="3">
         <v>4</v>
       </c>
       <c r="C163" s="3"/>
       <c r="D163" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G163" s="3"/>
       <c r="H163" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="164" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B164" s="3">
         <v>3</v>
       </c>
       <c r="C164" s="3"/>
       <c r="D164" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G164" s="3"/>
       <c r="H164" s="5" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B165" s="3">
         <v>4</v>
       </c>
       <c r="C165" s="3"/>
       <c r="D165" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E165" s="3"/>
       <c r="F165" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G165" s="3"/>
       <c r="H165" s="5" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B166" s="3">
         <v>4</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E166" s="3"/>
       <c r="F166" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G166" s="3"/>
       <c r="H166" s="5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B167" s="3">
         <v>4</v>
       </c>
       <c r="C167" s="3"/>
       <c r="D167" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E167" s="3"/>
       <c r="F167" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G167" s="3"/>
       <c r="H167" s="5" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="168" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B168" s="3">
         <v>4</v>
       </c>
       <c r="C168" s="3"/>
       <c r="D168" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E168" s="3"/>
       <c r="F168" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G168" s="3"/>
       <c r="H168" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B169" s="3">
         <v>4</v>
       </c>
       <c r="C169" s="3"/>
       <c r="D169" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E169" s="3"/>
       <c r="F169" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G169" s="3"/>
       <c r="H169" s="5" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B170" s="3">
         <v>4</v>
       </c>
       <c r="C170" s="3"/>
       <c r="D170" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E170" s="3"/>
       <c r="F170" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G170" s="3"/>
       <c r="H170" s="5" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B171" s="3">
         <v>4</v>
       </c>
       <c r="C171" s="3"/>
       <c r="D171" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E171" s="3"/>
       <c r="F171" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G171" s="3"/>
       <c r="H171" s="5" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B172" s="3">
         <v>4</v>
       </c>
       <c r="C172" s="3"/>
       <c r="D172" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E172" s="3"/>
       <c r="F172" s="4" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G172" s="3"/>
       <c r="H172" s="5" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B173" s="3">
         <v>4</v>
       </c>
       <c r="C173" s="3"/>
       <c r="D173" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E173" s="3"/>
       <c r="F173" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G173" s="3"/>
       <c r="H173" s="5" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B174" s="3">
         <v>4</v>
       </c>
       <c r="C174" s="3"/>
       <c r="D174" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E174" s="3"/>
       <c r="F174" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G174" s="3"/>
       <c r="H174" s="5" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B175" s="3">
         <v>5</v>
       </c>
       <c r="C175" s="3"/>
       <c r="D175" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E175" s="3"/>
       <c r="F175" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G175" s="3"/>
       <c r="H175" s="5" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B176" s="3">
         <v>4</v>
       </c>
       <c r="C176" s="3"/>
       <c r="D176" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E176" s="3"/>
       <c r="F176" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G176" s="3"/>
       <c r="H176" s="5" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B177" s="3">
         <v>3</v>
       </c>
       <c r="C177" s="3"/>
       <c r="D177" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E177" s="3"/>
       <c r="F177" s="4" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G177" s="3"/>
       <c r="H177" s="5" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B178" s="3">
         <v>4</v>
       </c>
       <c r="C178" s="3"/>
       <c r="D178" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E178" s="3"/>
       <c r="F178" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G178" s="3"/>
       <c r="H178" s="5" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B179" s="3">
         <v>4</v>
       </c>
       <c r="C179" s="3"/>
       <c r="D179" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E179" s="3"/>
       <c r="F179" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G179" s="3"/>
       <c r="H179" s="5" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B180" s="3">
         <v>4</v>
       </c>
       <c r="C180" s="3"/>
       <c r="D180" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E180" s="3"/>
       <c r="F180" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G180" s="3"/>
       <c r="H180" s="5" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B181" s="3">
         <v>3</v>
       </c>
       <c r="C181" s="3"/>
       <c r="D181" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E181" s="3"/>
       <c r="F181" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G181" s="3"/>
       <c r="H181" s="5" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B182" s="3">
         <v>4</v>
       </c>
       <c r="C182" s="3"/>
       <c r="D182" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E182" s="3"/>
       <c r="F182" s="4" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G182" s="3"/>
       <c r="H182" s="5" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B183" s="3">
         <v>3</v>
       </c>
       <c r="C183" s="3"/>
       <c r="D183" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E183" s="3"/>
       <c r="F183" s="4" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G183" s="3"/>
       <c r="H183" s="5" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B184" s="3">
         <v>4</v>
       </c>
       <c r="C184" s="3"/>
       <c r="D184" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E184" s="3"/>
       <c r="F184" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G184" s="3"/>
       <c r="H184" s="5" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B185" s="3">
         <v>4</v>
       </c>
       <c r="C185" s="3"/>
       <c r="D185" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E185" s="3"/>
       <c r="F185" s="4" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G185" s="3"/>
       <c r="H185" s="5" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="186" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B186" s="3">
         <v>4</v>
       </c>
       <c r="C186" s="3"/>
       <c r="D186" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E186" s="3"/>
       <c r="F186" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G186" s="3"/>
       <c r="H186" s="5" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
@@ -9355,659 +9352,659 @@
       </c>
       <c r="C187" s="3"/>
       <c r="D187" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="E187" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="E187" s="3" t="s">
+      <c r="F187" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="F187" s="4" t="s">
+      <c r="G187" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="G187" s="3" t="s">
+      <c r="H187" s="5" t="s">
         <v>436</v>
-      </c>
-      <c r="H187" s="5" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B188" s="3">
         <v>3</v>
       </c>
       <c r="C188" s="3"/>
       <c r="D188" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E188" s="3"/>
       <c r="F188" s="4" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G188" s="3"/>
       <c r="H188" s="5" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B189" s="3">
         <v>4</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E189" s="3"/>
       <c r="F189" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G189" s="3"/>
       <c r="H189" s="5" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B190" s="3">
         <v>4</v>
       </c>
       <c r="C190" s="3"/>
       <c r="D190" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E190" s="3"/>
       <c r="F190" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G190" s="3"/>
       <c r="H190" s="5" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B191" s="3">
         <v>3</v>
       </c>
       <c r="C191" s="3"/>
       <c r="D191" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E191" s="3"/>
       <c r="F191" s="4" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G191" s="3"/>
       <c r="H191" s="5" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B192" s="3">
         <v>4</v>
       </c>
       <c r="C192" s="3"/>
       <c r="D192" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E192" s="3"/>
       <c r="F192" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G192" s="3"/>
       <c r="H192" s="5" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B193" s="3">
         <v>5</v>
       </c>
       <c r="C193" s="3"/>
       <c r="D193" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E193" s="3"/>
       <c r="F193" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G193" s="3"/>
       <c r="H193" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B194" s="3">
         <v>4</v>
       </c>
       <c r="C194" s="3"/>
       <c r="D194" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E194" s="3"/>
       <c r="F194" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G194" s="3"/>
       <c r="H194" s="5" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B195" s="3">
         <v>4</v>
       </c>
       <c r="C195" s="3"/>
       <c r="D195" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E195" s="3"/>
       <c r="F195" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G195" s="3"/>
       <c r="H195" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B196" s="3">
         <v>4</v>
       </c>
       <c r="C196" s="3"/>
       <c r="D196" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E196" s="3"/>
       <c r="F196" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G196" s="3"/>
       <c r="H196" s="5" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B197" s="3">
         <v>3</v>
       </c>
       <c r="C197" s="3"/>
       <c r="D197" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E197" s="3"/>
       <c r="F197" s="4" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G197" s="3"/>
       <c r="H197" s="5" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B198" s="3">
         <v>4</v>
       </c>
       <c r="C198" s="3"/>
       <c r="D198" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E198" s="3"/>
       <c r="F198" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G198" s="3"/>
       <c r="H198" s="5" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="199" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B199" s="3">
         <v>5</v>
       </c>
       <c r="C199" s="3"/>
       <c r="D199" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E199" s="3"/>
       <c r="F199" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G199" s="3"/>
       <c r="H199" s="5" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B200" s="3">
         <v>4</v>
       </c>
       <c r="C200" s="3"/>
       <c r="D200" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E200" s="3"/>
       <c r="F200" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G200" s="3"/>
       <c r="H200" s="5" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B201" s="3">
         <v>4</v>
       </c>
       <c r="C201" s="3"/>
       <c r="D201" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E201" s="3"/>
       <c r="F201" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G201" s="3"/>
       <c r="H201" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B202" s="3">
         <v>4</v>
       </c>
       <c r="C202" s="3"/>
       <c r="D202" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E202" s="3"/>
       <c r="F202" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G202" s="3"/>
       <c r="H202" s="5" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="203" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B203" s="3">
         <v>3</v>
       </c>
       <c r="C203" s="3"/>
       <c r="D203" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E203" s="3"/>
       <c r="F203" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G203" s="3"/>
       <c r="H203" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B204" s="3">
         <v>4</v>
       </c>
       <c r="C204" s="3"/>
       <c r="D204" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E204" s="3"/>
       <c r="F204" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G204" s="3"/>
       <c r="H204" s="5" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B205" s="3">
         <v>5</v>
       </c>
       <c r="C205" s="3"/>
       <c r="D205" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E205" s="3"/>
       <c r="F205" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G205" s="3"/>
       <c r="H205" s="5" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B206" s="3">
         <v>5</v>
       </c>
       <c r="C206" s="3"/>
       <c r="D206" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E206" s="3"/>
       <c r="F206" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G206" s="3"/>
       <c r="H206" s="5" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B207" s="3">
         <v>4</v>
       </c>
       <c r="C207" s="3"/>
       <c r="D207" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E207" s="3"/>
       <c r="F207" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G207" s="3"/>
       <c r="H207" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B208" s="3">
         <v>4</v>
       </c>
       <c r="C208" s="3"/>
       <c r="D208" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E208" s="3"/>
       <c r="F208" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G208" s="3"/>
       <c r="H208" s="5" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B209" s="3">
         <v>4</v>
       </c>
       <c r="C209" s="3"/>
       <c r="D209" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E209" s="3"/>
       <c r="F209" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G209" s="3"/>
       <c r="H209" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B210" s="3">
         <v>4</v>
       </c>
       <c r="C210" s="3"/>
       <c r="D210" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E210" s="3"/>
       <c r="F210" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G210" s="3"/>
       <c r="H210" s="5" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B211" s="3">
         <v>5</v>
       </c>
       <c r="C211" s="3"/>
       <c r="D211" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E211" s="3"/>
       <c r="F211" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G211" s="3"/>
       <c r="H211" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B212" s="3">
         <v>4</v>
       </c>
       <c r="C212" s="3"/>
       <c r="D212" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E212" s="3"/>
       <c r="F212" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G212" s="3"/>
       <c r="H212" s="5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B213" s="3">
         <v>4</v>
       </c>
       <c r="C213" s="3"/>
       <c r="D213" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E213" s="3"/>
       <c r="F213" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G213" s="3"/>
       <c r="H213" s="5" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B214" s="3">
         <v>3</v>
       </c>
       <c r="C214" s="3"/>
       <c r="D214" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E214" s="3"/>
       <c r="F214" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G214" s="3"/>
       <c r="H214" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B215" s="3">
         <v>4</v>
       </c>
       <c r="C215" s="3"/>
       <c r="D215" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E215" s="3"/>
       <c r="F215" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G215" s="3"/>
       <c r="H215" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B216" s="3">
         <v>5</v>
       </c>
       <c r="C216" s="3"/>
       <c r="D216" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E216" s="3"/>
       <c r="F216" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G216" s="3"/>
       <c r="H216" s="5" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B217" s="3">
         <v>5</v>
       </c>
       <c r="C217" s="3"/>
       <c r="D217" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E217" s="3"/>
       <c r="F217" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G217" s="3"/>
       <c r="H217" s="5" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B218" s="3">
         <v>6</v>
       </c>
       <c r="C218" s="3"/>
       <c r="D218" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E218" s="3"/>
       <c r="F218" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G218" s="3"/>
       <c r="H218" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="219" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B219" s="3">
         <v>5</v>
       </c>
       <c r="C219" s="3"/>
       <c r="D219" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E219" s="3"/>
       <c r="F219" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G219" s="3"/>
       <c r="H219" s="5" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
@@ -10018,11 +10015,11 @@
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F220" s="4"/>
       <c r="G220" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H220" s="5"/>
     </row>
@@ -10033,699 +10030,699 @@
       </c>
       <c r="C221" s="3"/>
       <c r="D221" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E221" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="E221" s="3" t="s">
+      <c r="F221" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="F221" s="4" t="s">
+      <c r="G221" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="G221" s="3" t="s">
-        <v>514</v>
-      </c>
       <c r="H221" s="5" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="222" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B222" s="3">
         <v>3</v>
       </c>
       <c r="C222" s="3"/>
       <c r="D222" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E222" s="3"/>
       <c r="F222" s="4" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G222" s="3"/>
       <c r="H222" s="5" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="223" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B223" s="3">
         <v>4</v>
       </c>
       <c r="C223" s="3"/>
       <c r="D223" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E223" s="3"/>
       <c r="F223" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G223" s="3"/>
       <c r="H223" s="5" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="224" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B224" s="3">
         <v>4</v>
       </c>
       <c r="C224" s="3"/>
       <c r="D224" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E224" s="3"/>
       <c r="F224" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G224" s="3"/>
       <c r="H224" s="5" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B225" s="3">
         <v>3</v>
       </c>
       <c r="C225" s="3"/>
       <c r="D225" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E225" s="3"/>
       <c r="F225" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G225" s="3"/>
       <c r="H225" s="5" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B226" s="3">
         <v>4</v>
       </c>
       <c r="C226" s="3"/>
       <c r="D226" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E226" s="3"/>
       <c r="F226" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G226" s="3"/>
       <c r="H226" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="227" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B227" s="3">
         <v>5</v>
       </c>
       <c r="C227" s="3"/>
       <c r="D227" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E227" s="3"/>
       <c r="F227" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G227" s="3"/>
       <c r="H227" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B228" s="3">
         <v>5</v>
       </c>
       <c r="C228" s="3"/>
       <c r="D228" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E228" s="3"/>
       <c r="F228" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G228" s="3"/>
       <c r="H228" s="5" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B229" s="3">
         <v>5</v>
       </c>
       <c r="C229" s="3"/>
       <c r="D229" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E229" s="3"/>
       <c r="F229" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G229" s="3"/>
       <c r="H229" s="5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B230" s="3">
         <v>5</v>
       </c>
       <c r="C230" s="3"/>
       <c r="D230" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E230" s="3"/>
       <c r="F230" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G230" s="3"/>
       <c r="H230" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B231" s="3">
         <v>5</v>
       </c>
       <c r="C231" s="3"/>
       <c r="D231" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E231" s="3"/>
       <c r="F231" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G231" s="3"/>
       <c r="H231" s="5" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B232" s="3">
         <v>5</v>
       </c>
       <c r="C232" s="3"/>
       <c r="D232" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E232" s="3"/>
       <c r="F232" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G232" s="3"/>
       <c r="H232" s="5" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B233" s="3">
         <v>5</v>
       </c>
       <c r="C233" s="3"/>
       <c r="D233" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E233" s="3"/>
       <c r="F233" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G233" s="3"/>
       <c r="H233" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B234" s="3">
         <v>4</v>
       </c>
       <c r="C234" s="3"/>
       <c r="D234" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E234" s="3"/>
       <c r="F234" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G234" s="3"/>
       <c r="H234" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B235" s="3">
         <v>3</v>
       </c>
       <c r="C235" s="3"/>
       <c r="D235" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E235" s="3"/>
       <c r="F235" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G235" s="3"/>
       <c r="H235" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B236" s="3">
         <v>4</v>
       </c>
       <c r="C236" s="3"/>
       <c r="D236" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E236" s="3"/>
       <c r="F236" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G236" s="3"/>
       <c r="H236" s="5" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B237" s="3">
         <v>4</v>
       </c>
       <c r="C237" s="3"/>
       <c r="D237" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E237" s="3"/>
       <c r="F237" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G237" s="3"/>
       <c r="H237" s="5" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B238" s="3">
         <v>4</v>
       </c>
       <c r="C238" s="3"/>
       <c r="D238" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E238" s="3"/>
       <c r="F238" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G238" s="3"/>
       <c r="H238" s="5" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B239" s="3">
         <v>4</v>
       </c>
       <c r="C239" s="3"/>
       <c r="D239" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E239" s="3"/>
       <c r="F239" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G239" s="3"/>
       <c r="H239" s="5" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B240" s="3">
         <v>3</v>
       </c>
       <c r="C240" s="3"/>
       <c r="D240" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E240" s="3"/>
       <c r="F240" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G240" s="3"/>
       <c r="H240" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B241" s="3">
         <v>4</v>
       </c>
       <c r="C241" s="3"/>
       <c r="D241" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E241" s="3"/>
       <c r="F241" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G241" s="3"/>
       <c r="H241" s="5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B242" s="3">
         <v>5</v>
       </c>
       <c r="C242" s="3"/>
       <c r="D242" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E242" s="3"/>
       <c r="F242" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G242" s="3"/>
       <c r="H242" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B243" s="3">
         <v>4</v>
       </c>
       <c r="C243" s="3"/>
       <c r="D243" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E243" s="3"/>
       <c r="F243" s="4" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G243" s="3"/>
       <c r="H243" s="5" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B244" s="3">
         <v>5</v>
       </c>
       <c r="C244" s="3"/>
       <c r="D244" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E244" s="3"/>
       <c r="F244" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G244" s="3"/>
       <c r="H244" s="5" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B245" s="3">
         <v>4</v>
       </c>
       <c r="C245" s="3"/>
       <c r="D245" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E245" s="3"/>
       <c r="F245" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G245" s="3"/>
       <c r="H245" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B246" s="3">
         <v>3</v>
       </c>
       <c r="C246" s="3"/>
       <c r="D246" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E246" s="3"/>
       <c r="F246" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G246" s="3"/>
       <c r="H246" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B247" s="3">
         <v>4</v>
       </c>
       <c r="C247" s="3"/>
       <c r="D247" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E247" s="3"/>
       <c r="F247" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G247" s="3"/>
       <c r="H247" s="5" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B248" s="3">
         <v>3</v>
       </c>
       <c r="C248" s="3"/>
       <c r="D248" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E248" s="3"/>
       <c r="F248" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G248" s="3"/>
       <c r="H248" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B249" s="3">
         <v>4</v>
       </c>
       <c r="C249" s="3"/>
       <c r="D249" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E249" s="3"/>
       <c r="F249" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G249" s="3"/>
       <c r="H249" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B250" s="3">
         <v>4</v>
       </c>
       <c r="C250" s="3"/>
       <c r="D250" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E250" s="3"/>
       <c r="F250" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G250" s="3"/>
       <c r="H250" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B251" s="3">
         <v>4</v>
       </c>
       <c r="C251" s="3"/>
       <c r="D251" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E251" s="3"/>
       <c r="F251" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G251" s="3"/>
       <c r="H251" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B252" s="3">
         <v>3</v>
       </c>
       <c r="C252" s="3"/>
       <c r="D252" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E252" s="3"/>
       <c r="F252" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G252" s="3"/>
       <c r="H252" s="5" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="253" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B253" s="3">
         <v>4</v>
       </c>
       <c r="C253" s="3"/>
       <c r="D253" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E253" s="3"/>
       <c r="F253" s="4" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G253" s="3"/>
       <c r="H253" s="5" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B254" s="3">
         <v>4</v>
       </c>
       <c r="C254" s="3"/>
       <c r="D254" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E254" s="3"/>
       <c r="F254" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G254" s="3"/>
       <c r="H254" s="5" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="255" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B255" s="3">
         <v>4</v>
       </c>
       <c r="C255" s="3"/>
       <c r="D255" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E255" s="3"/>
       <c r="F255" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G255" s="3"/>
       <c r="H255" s="5" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.3">
@@ -10735,559 +10732,559 @@
       </c>
       <c r="C256" s="3"/>
       <c r="D256" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E256" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="E256" s="3" t="s">
+      <c r="F256" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="F256" s="4" t="s">
+      <c r="G256" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="G256" s="3" t="s">
+      <c r="H256" s="5" t="s">
         <v>602</v>
-      </c>
-      <c r="H256" s="5" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B257" s="3">
         <v>3</v>
       </c>
       <c r="C257" s="3"/>
       <c r="D257" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E257" s="3"/>
       <c r="F257" s="4" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G257" s="3"/>
       <c r="H257" s="5" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B258" s="3">
         <v>4</v>
       </c>
       <c r="C258" s="3"/>
       <c r="D258" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E258" s="3"/>
       <c r="F258" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G258" s="3"/>
       <c r="H258" s="5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B259" s="3">
         <v>4</v>
       </c>
       <c r="C259" s="3"/>
       <c r="D259" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E259" s="3"/>
       <c r="F259" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G259" s="3"/>
       <c r="H259" s="5" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B260" s="3">
         <v>3</v>
       </c>
       <c r="C260" s="3"/>
       <c r="D260" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E260" s="3"/>
       <c r="F260" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G260" s="3"/>
       <c r="H260" s="5" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="261" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B261" s="3">
         <v>4</v>
       </c>
       <c r="C261" s="3"/>
       <c r="D261" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E261" s="3"/>
       <c r="F261" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G261" s="3"/>
       <c r="H261" s="5" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="262" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B262" s="3">
         <v>4</v>
       </c>
       <c r="C262" s="3"/>
       <c r="D262" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E262" s="3"/>
       <c r="F262" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G262" s="3"/>
       <c r="H262" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="263" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B263" s="3">
         <v>3</v>
       </c>
       <c r="C263" s="3"/>
       <c r="D263" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E263" s="3"/>
       <c r="F263" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G263" s="3"/>
       <c r="H263" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="264" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B264" s="3">
         <v>4</v>
       </c>
       <c r="C264" s="3"/>
       <c r="D264" s="3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E264" s="3"/>
       <c r="F264" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G264" s="3"/>
       <c r="H264" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B265" s="3">
         <v>5</v>
       </c>
       <c r="C265" s="3"/>
       <c r="D265" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E265" s="3"/>
       <c r="F265" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G265" s="3"/>
       <c r="H265" s="5" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="266" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B266" s="3">
         <v>5</v>
       </c>
       <c r="C266" s="3"/>
       <c r="D266" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E266" s="3"/>
       <c r="F266" s="4" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G266" s="3"/>
       <c r="H266" s="5" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="267" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B267" s="3">
         <v>5</v>
       </c>
       <c r="C267" s="3"/>
       <c r="D267" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E267" s="3"/>
       <c r="F267" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G267" s="3"/>
       <c r="H267" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="268" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B268" s="3">
         <v>4</v>
       </c>
       <c r="C268" s="3"/>
       <c r="D268" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E268" s="3"/>
       <c r="F268" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G268" s="3"/>
       <c r="H268" s="5" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="269" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B269" s="3">
         <v>5</v>
       </c>
       <c r="C269" s="3"/>
       <c r="D269" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E269" s="3"/>
       <c r="F269" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="G269" s="3"/>
       <c r="H269" s="5" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="270" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B270" s="3">
         <v>3</v>
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E270" s="3"/>
       <c r="F270" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G270" s="3"/>
       <c r="H270" s="5" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="271" spans="1:8" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B271" s="3">
         <v>4</v>
       </c>
       <c r="C271" s="3"/>
       <c r="D271" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E271" s="3"/>
       <c r="F271" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G271" s="3"/>
       <c r="H271" s="5" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="272" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B272" s="3">
         <v>4</v>
       </c>
       <c r="C272" s="3"/>
       <c r="D272" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E272" s="3"/>
       <c r="F272" s="4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G272" s="3"/>
       <c r="H272" s="5" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="273" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B273" s="3">
         <v>4</v>
       </c>
       <c r="C273" s="3"/>
       <c r="D273" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E273" s="3"/>
       <c r="F273" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G273" s="3"/>
       <c r="H273" s="5" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="274" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B274" s="3">
         <v>4</v>
       </c>
       <c r="C274" s="3"/>
       <c r="D274" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E274" s="3"/>
       <c r="F274" s="4" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G274" s="3"/>
       <c r="H274" s="5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="275" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B275" s="3">
         <v>4</v>
       </c>
       <c r="C275" s="3"/>
       <c r="D275" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E275" s="3"/>
       <c r="F275" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G275" s="3"/>
       <c r="H275" s="5" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="276" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B276" s="3">
         <v>4</v>
       </c>
       <c r="C276" s="3"/>
       <c r="D276" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E276" s="3"/>
       <c r="F276" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="G276" s="3"/>
       <c r="H276" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="277" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B277" s="3">
         <v>4</v>
       </c>
       <c r="C277" s="3"/>
       <c r="D277" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E277" s="3"/>
       <c r="F277" s="4" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G277" s="3"/>
       <c r="H277" s="5" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="278" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B278" s="3">
         <v>3</v>
       </c>
       <c r="C278" s="3"/>
       <c r="D278" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E278" s="3"/>
       <c r="F278" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="G278" s="3"/>
       <c r="H278" s="5" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="279" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B279" s="3">
         <v>4</v>
       </c>
       <c r="C279" s="3"/>
       <c r="D279" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E279" s="3"/>
       <c r="F279" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G279" s="3"/>
       <c r="H279" s="5" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="280" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B280" s="3">
         <v>5</v>
       </c>
       <c r="C280" s="3"/>
       <c r="D280" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E280" s="3"/>
       <c r="F280" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G280" s="3"/>
       <c r="H280" s="5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="281" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B281" s="3">
         <v>4</v>
       </c>
       <c r="C281" s="3"/>
       <c r="D281" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E281" s="3"/>
       <c r="F281" s="4" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G281" s="3"/>
       <c r="H281" s="5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="282" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B282" s="3">
         <v>3</v>
       </c>
       <c r="C282" s="3"/>
       <c r="D282" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E282" s="3"/>
       <c r="F282" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G282" s="3"/>
       <c r="H282" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="283" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B283" s="3">
         <v>4</v>
       </c>
       <c r="C283" s="3"/>
       <c r="D283" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E283" s="3"/>
       <c r="F283" s="4" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G283" s="3"/>
       <c r="H283" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.3">
@@ -11298,11 +11295,11 @@
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F284" s="4"/>
       <c r="G284" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H284" s="5"/>
     </row>
@@ -11313,959 +11310,959 @@
       </c>
       <c r="C285" s="3"/>
       <c r="D285" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="E285" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="E285" s="3" t="s">
+      <c r="F285" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G285" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="F285" s="4" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G285" s="3" t="s">
-        <v>659</v>
-      </c>
       <c r="H285" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="286" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B286" s="3">
         <v>3</v>
       </c>
       <c r="C286" s="3"/>
       <c r="D286" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E286" s="3"/>
       <c r="F286" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G286" s="3"/>
       <c r="H286" s="5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="287" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B287" s="3">
         <v>4</v>
       </c>
       <c r="C287" s="3"/>
       <c r="D287" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E287" s="3"/>
       <c r="F287" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G287" s="3"/>
       <c r="H287" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="288" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B288" s="3">
         <v>4</v>
       </c>
       <c r="C288" s="3"/>
       <c r="D288" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E288" s="3"/>
       <c r="F288" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G288" s="3"/>
       <c r="H288" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="289" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B289" s="3">
         <v>4</v>
       </c>
       <c r="C289" s="3"/>
       <c r="D289" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E289" s="3"/>
       <c r="F289" s="4" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G289" s="3"/>
       <c r="H289" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="290" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B290" s="3">
         <v>4</v>
       </c>
       <c r="C290" s="3"/>
       <c r="D290" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E290" s="3"/>
       <c r="F290" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G290" s="3"/>
       <c r="H290" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="291" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B291" s="3">
         <v>3</v>
       </c>
       <c r="C291" s="3"/>
       <c r="D291" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E291" s="3"/>
       <c r="F291" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G291" s="3"/>
       <c r="H291" s="5" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="292" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B292" s="3">
         <v>4</v>
       </c>
       <c r="C292" s="3"/>
       <c r="D292" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E292" s="3"/>
       <c r="F292" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G292" s="3"/>
       <c r="H292" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="293" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B293" s="3">
         <v>3</v>
       </c>
       <c r="C293" s="3"/>
       <c r="D293" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E293" s="3"/>
       <c r="F293" s="4" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G293" s="3"/>
       <c r="H293" s="5" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="294" spans="1:8" ht="216" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B294" s="3">
         <v>4</v>
       </c>
       <c r="C294" s="3"/>
       <c r="D294" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E294" s="3"/>
       <c r="F294" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G294" s="3"/>
       <c r="H294" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="295" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B295" s="3">
         <v>4</v>
       </c>
       <c r="C295" s="3"/>
       <c r="D295" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E295" s="3"/>
       <c r="F295" s="4" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G295" s="3"/>
       <c r="H295" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="296" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B296" s="3">
         <v>4</v>
       </c>
       <c r="C296" s="3"/>
       <c r="D296" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E296" s="3"/>
       <c r="F296" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G296" s="3"/>
       <c r="H296" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="297" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B297" s="3">
         <v>4</v>
       </c>
       <c r="C297" s="3"/>
       <c r="D297" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E297" s="3"/>
       <c r="F297" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G297" s="3"/>
       <c r="H297" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B298" s="3">
         <v>3</v>
       </c>
       <c r="C298" s="3"/>
       <c r="D298" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E298" s="3"/>
       <c r="F298" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G298" s="3"/>
       <c r="H298" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="299" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B299" s="3">
         <v>4</v>
       </c>
       <c r="C299" s="3"/>
       <c r="D299" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E299" s="3"/>
       <c r="F299" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G299" s="3"/>
       <c r="H299" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="300" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B300" s="3">
         <v>4</v>
       </c>
       <c r="C300" s="3"/>
       <c r="D300" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E300" s="3"/>
       <c r="F300" s="4" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G300" s="3"/>
       <c r="H300" s="5" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="301" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B301" s="3">
         <v>5</v>
       </c>
       <c r="C301" s="3"/>
       <c r="D301" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E301" s="3"/>
       <c r="F301" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G301" s="3"/>
       <c r="H301" s="5" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B302" s="3">
         <v>3</v>
       </c>
       <c r="C302" s="3"/>
       <c r="D302" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E302" s="3"/>
       <c r="F302" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G302" s="3"/>
       <c r="H302" s="5" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="303" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B303" s="3">
         <v>4</v>
       </c>
       <c r="C303" s="3"/>
       <c r="D303" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E303" s="3"/>
       <c r="F303" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G303" s="3"/>
       <c r="H303" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="304" spans="1:8" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B304" s="3">
         <v>4</v>
       </c>
       <c r="C304" s="3"/>
       <c r="D304" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E304" s="3"/>
       <c r="F304" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G304" s="3"/>
       <c r="H304" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="305" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B305" s="3">
         <v>5</v>
       </c>
       <c r="C305" s="3"/>
       <c r="D305" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E305" s="3"/>
       <c r="F305" s="4" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G305" s="3"/>
       <c r="H305" s="5" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="306" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B306" s="3">
         <v>4</v>
       </c>
       <c r="C306" s="3"/>
       <c r="D306" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E306" s="3"/>
       <c r="F306" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G306" s="3"/>
       <c r="H306" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B307" s="3">
         <v>3</v>
       </c>
       <c r="C307" s="3"/>
       <c r="D307" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E307" s="3"/>
       <c r="F307" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G307" s="3"/>
       <c r="H307" s="5" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="308" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B308" s="3">
         <v>4</v>
       </c>
       <c r="C308" s="3"/>
       <c r="D308" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E308" s="3"/>
       <c r="F308" s="4" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G308" s="3"/>
       <c r="H308" s="5" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="309" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B309" s="3">
         <v>4</v>
       </c>
       <c r="C309" s="3"/>
       <c r="D309" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E309" s="3"/>
       <c r="F309" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G309" s="3"/>
       <c r="H309" s="5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="310" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B310" s="3">
         <v>4</v>
       </c>
       <c r="C310" s="3"/>
       <c r="D310" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E310" s="3"/>
       <c r="F310" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G310" s="3"/>
       <c r="H310" s="5" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="311" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B311" s="3">
         <v>5</v>
       </c>
       <c r="C311" s="3"/>
       <c r="D311" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E311" s="3"/>
       <c r="F311" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G311" s="3"/>
       <c r="H311" s="5" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="312" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B312" s="3">
         <v>5</v>
       </c>
       <c r="C312" s="3"/>
       <c r="D312" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E312" s="3"/>
       <c r="F312" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G312" s="3"/>
       <c r="H312" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B313" s="3">
         <v>3</v>
       </c>
       <c r="C313" s="3"/>
       <c r="D313" s="3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E313" s="3"/>
       <c r="F313" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G313" s="3"/>
       <c r="H313" s="5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="314" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B314" s="3">
         <v>4</v>
       </c>
       <c r="C314" s="3"/>
       <c r="D314" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E314" s="3"/>
       <c r="F314" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G314" s="3"/>
       <c r="H314" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="315" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B315" s="3">
         <v>3</v>
       </c>
       <c r="C315" s="3"/>
       <c r="D315" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E315" s="3"/>
       <c r="F315" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G315" s="3"/>
       <c r="H315" s="5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="316" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B316" s="3">
         <v>4</v>
       </c>
       <c r="C316" s="3"/>
       <c r="D316" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E316" s="3"/>
       <c r="F316" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G316" s="3"/>
       <c r="H316" s="5" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="317" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B317" s="3">
         <v>4</v>
       </c>
       <c r="C317" s="3"/>
       <c r="D317" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E317" s="3"/>
       <c r="F317" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G317" s="3"/>
       <c r="H317" s="5" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="318" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B318" s="3">
         <v>4</v>
       </c>
       <c r="C318" s="3"/>
       <c r="D318" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E318" s="3"/>
       <c r="F318" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G318" s="3"/>
       <c r="H318" s="5" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="319" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B319" s="3">
         <v>4</v>
       </c>
       <c r="C319" s="3"/>
       <c r="D319" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E319" s="3"/>
       <c r="F319" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G319" s="3"/>
       <c r="H319" s="5" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="320" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B320" s="3">
         <v>4</v>
       </c>
       <c r="C320" s="3"/>
       <c r="D320" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E320" s="3"/>
       <c r="F320" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G320" s="3"/>
       <c r="H320" s="5" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="321" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B321" s="3">
         <v>3</v>
       </c>
       <c r="C321" s="3"/>
       <c r="D321" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E321" s="3"/>
       <c r="F321" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G321" s="3"/>
       <c r="H321" s="5" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="322" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B322" s="3">
         <v>4</v>
       </c>
       <c r="C322" s="3"/>
       <c r="D322" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E322" s="3"/>
       <c r="F322" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G322" s="3"/>
       <c r="H322" s="5" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="323" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B323" s="3">
         <v>4</v>
       </c>
       <c r="C323" s="3"/>
       <c r="D323" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E323" s="3"/>
       <c r="F323" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G323" s="3"/>
       <c r="H323" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="324" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B324" s="3">
         <v>3</v>
       </c>
       <c r="C324" s="3"/>
       <c r="D324" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E324" s="3"/>
       <c r="F324" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G324" s="3"/>
       <c r="H324" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="325" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B325" s="3">
         <v>4</v>
       </c>
       <c r="C325" s="3"/>
       <c r="D325" s="3" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E325" s="3"/>
       <c r="F325" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G325" s="3"/>
       <c r="H325" s="5" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="326" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B326" s="3">
         <v>4</v>
       </c>
       <c r="C326" s="3"/>
       <c r="D326" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E326" s="3"/>
       <c r="F326" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G326" s="3"/>
       <c r="H326" s="5" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="327" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B327" s="3">
         <v>4</v>
       </c>
       <c r="C327" s="3"/>
       <c r="D327" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E327" s="3"/>
       <c r="F327" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G327" s="3"/>
       <c r="H327" s="5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="328" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B328" s="3">
         <v>4</v>
       </c>
       <c r="C328" s="3"/>
       <c r="D328" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E328" s="3"/>
       <c r="F328" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G328" s="3"/>
       <c r="H328" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="329" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B329" s="3">
         <v>5</v>
       </c>
       <c r="C329" s="3"/>
       <c r="D329" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E329" s="3"/>
       <c r="F329" s="4" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G329" s="3"/>
       <c r="H329" s="5" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="330" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B330" s="3">
         <v>4</v>
       </c>
       <c r="C330" s="3"/>
       <c r="D330" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E330" s="3"/>
       <c r="F330" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G330" s="3"/>
       <c r="H330" s="5" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="331" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B331" s="3">
         <v>4</v>
       </c>
       <c r="C331" s="3"/>
       <c r="D331" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E331" s="3"/>
       <c r="F331" s="4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G331" s="3"/>
       <c r="H331" s="5" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="332" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B332" s="3">
         <v>4</v>
       </c>
       <c r="C332" s="3"/>
       <c r="D332" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E332" s="3"/>
       <c r="F332" s="4" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G332" s="3"/>
       <c r="H332" s="5" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.3">
@@ -12275,19 +12272,19 @@
       </c>
       <c r="C333" s="3"/>
       <c r="D333" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="E333" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="E333" s="3" t="s">
+      <c r="F333" s="4" t="s">
         <v>757</v>
       </c>
-      <c r="F333" s="4" t="s">
+      <c r="G333" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="G333" s="3" t="s">
+      <c r="H333" s="5" t="s">
         <v>759</v>
-      </c>
-      <c r="H333" s="5" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.3">
@@ -12297,199 +12294,199 @@
       </c>
       <c r="C334" s="3"/>
       <c r="D334" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="E334" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="E334" s="3" t="s">
+      <c r="F334" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="F334" s="4" t="s">
+      <c r="G334" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="G334" s="3" t="s">
-        <v>764</v>
-      </c>
       <c r="H334" s="5" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="335" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B335" s="3">
         <v>3</v>
       </c>
       <c r="C335" s="3"/>
       <c r="D335" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E335" s="3"/>
       <c r="F335" s="4" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G335" s="3"/>
       <c r="H335" s="5" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="336" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B336" s="3">
         <v>4</v>
       </c>
       <c r="C336" s="3"/>
       <c r="D336" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E336" s="3"/>
       <c r="F336" s="4" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G336" s="3"/>
       <c r="H336" s="5" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="337" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B337" s="3">
         <v>4</v>
       </c>
       <c r="C337" s="3"/>
       <c r="D337" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E337" s="3"/>
       <c r="F337" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G337" s="3"/>
       <c r="H337" s="5" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="338" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B338" s="3">
         <v>4</v>
       </c>
       <c r="C338" s="3"/>
       <c r="D338" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E338" s="3"/>
       <c r="F338" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G338" s="3"/>
       <c r="H338" s="5" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="339" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B339" s="3">
         <v>4</v>
       </c>
       <c r="C339" s="3"/>
       <c r="D339" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E339" s="3"/>
       <c r="F339" s="4" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G339" s="3"/>
       <c r="H339" s="5" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="340" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B340" s="3">
         <v>3</v>
       </c>
       <c r="C340" s="3"/>
       <c r="D340" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E340" s="3"/>
       <c r="F340" s="4" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G340" s="3"/>
       <c r="H340" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="341" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B341" s="3">
         <v>4</v>
       </c>
       <c r="C341" s="3"/>
       <c r="D341" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E341" s="3"/>
       <c r="F341" s="4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G341" s="3"/>
       <c r="H341" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="342" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B342" s="3">
         <v>4</v>
       </c>
       <c r="C342" s="3"/>
       <c r="D342" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E342" s="3"/>
       <c r="F342" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G342" s="3"/>
       <c r="H342" s="5" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="343" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B343" s="3">
         <v>4</v>
       </c>
       <c r="C343" s="3"/>
       <c r="D343" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E343" s="3"/>
       <c r="F343" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G343" s="3"/>
       <c r="H343" s="5" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="344" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -12499,99 +12496,99 @@
       </c>
       <c r="C344" s="3"/>
       <c r="D344" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="E344" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="E344" s="3" t="s">
+      <c r="F344" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="G344" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="F344" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G344" s="3" t="s">
-        <v>784</v>
-      </c>
       <c r="H344" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="345" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B345" s="3">
         <v>3</v>
       </c>
       <c r="C345" s="3"/>
       <c r="D345" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E345" s="3"/>
       <c r="F345" s="4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G345" s="3"/>
       <c r="H345" s="5" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="346" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B346" s="3">
         <v>4</v>
       </c>
       <c r="C346" s="3"/>
       <c r="D346" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E346" s="3"/>
       <c r="F346" s="4" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G346" s="3"/>
       <c r="H346" s="5" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="347" spans="1:8" ht="216" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B347" s="3">
         <v>4</v>
       </c>
       <c r="C347" s="3"/>
       <c r="D347" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E347" s="3"/>
       <c r="F347" s="4" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G347" s="3"/>
       <c r="H347" s="5" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="348" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B348" s="3">
         <v>4</v>
       </c>
       <c r="C348" s="3"/>
       <c r="D348" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E348" s="3"/>
       <c r="F348" s="4" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G348" s="3"/>
       <c r="H348" s="5" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.3">
@@ -12601,521 +12598,521 @@
       </c>
       <c r="C349" s="3"/>
       <c r="D349" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="E349" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="E349" s="3" t="s">
+      <c r="F349" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="F349" s="4" t="s">
+      <c r="G349" s="3" t="s">
         <v>795</v>
       </c>
-      <c r="G349" s="3" t="s">
-        <v>796</v>
-      </c>
       <c r="H349" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B350" s="3">
         <v>3</v>
       </c>
       <c r="C350" s="3"/>
       <c r="D350" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E350" s="3"/>
       <c r="F350" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G350" s="3"/>
       <c r="H350" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="351" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B351" s="3">
         <v>4</v>
       </c>
       <c r="C351" s="3"/>
       <c r="D351" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E351" s="3"/>
       <c r="F351" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G351" s="3"/>
       <c r="H351" s="5" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="352" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B352" s="3">
         <v>4</v>
       </c>
       <c r="C352" s="3"/>
       <c r="D352" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E352" s="3"/>
       <c r="F352" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G352" s="3"/>
       <c r="H352" s="5" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="353" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B353" s="3">
         <v>4</v>
       </c>
       <c r="C353" s="3"/>
       <c r="D353" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E353" s="3"/>
       <c r="F353" s="4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G353" s="3"/>
       <c r="H353" s="5" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="354" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B354" s="3">
         <v>4</v>
       </c>
       <c r="C354" s="3"/>
       <c r="D354" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E354" s="3"/>
       <c r="F354" s="4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G354" s="3"/>
       <c r="H354" s="5" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B355" s="3">
         <v>3</v>
       </c>
       <c r="C355" s="3"/>
       <c r="D355" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E355" s="3"/>
       <c r="F355" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G355" s="3"/>
       <c r="H355" s="5" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="356" spans="1:8" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B356" s="3">
         <v>4</v>
       </c>
       <c r="C356" s="3"/>
       <c r="D356" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E356" s="3"/>
       <c r="F356" s="4" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G356" s="3"/>
       <c r="H356" s="5" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="357" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B357" s="3">
         <v>4</v>
       </c>
       <c r="C357" s="3"/>
       <c r="D357" s="3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E357" s="3"/>
       <c r="F357" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G357" s="3"/>
       <c r="H357" s="5" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="358" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B358" s="3">
         <v>5</v>
       </c>
       <c r="C358" s="3"/>
       <c r="D358" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E358" s="3"/>
       <c r="F358" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G358" s="3"/>
       <c r="H358" s="5" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="359" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B359" s="3">
         <v>4</v>
       </c>
       <c r="C359" s="3"/>
       <c r="D359" s="3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E359" s="3"/>
       <c r="F359" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G359" s="3"/>
       <c r="H359" s="5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="360" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B360" s="3">
         <v>4</v>
       </c>
       <c r="C360" s="3"/>
       <c r="D360" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E360" s="3"/>
       <c r="F360" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G360" s="3"/>
       <c r="H360" s="5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="361" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B361" s="3">
         <v>4</v>
       </c>
       <c r="C361" s="3"/>
       <c r="D361" s="3" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E361" s="3"/>
       <c r="F361" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G361" s="3"/>
       <c r="H361" s="5" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="362" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B362" s="3">
         <v>5</v>
       </c>
       <c r="C362" s="3"/>
       <c r="D362" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E362" s="3"/>
       <c r="F362" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G362" s="3"/>
       <c r="H362" s="5" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="363" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B363" s="3">
         <v>5</v>
       </c>
       <c r="C363" s="3"/>
       <c r="D363" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E363" s="3"/>
       <c r="F363" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G363" s="3"/>
       <c r="H363" s="5" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="364" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B364" s="3">
         <v>4</v>
       </c>
       <c r="C364" s="3"/>
       <c r="D364" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E364" s="3"/>
       <c r="F364" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G364" s="3"/>
       <c r="H364" s="5" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="365" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B365" s="3">
         <v>5</v>
       </c>
       <c r="C365" s="3"/>
       <c r="D365" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E365" s="3"/>
       <c r="F365" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G365" s="3"/>
       <c r="H365" s="5" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="366" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B366" s="3">
         <v>3</v>
       </c>
       <c r="C366" s="3"/>
       <c r="D366" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E366" s="3"/>
       <c r="F366" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G366" s="3"/>
       <c r="H366" s="5" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="367" spans="1:8" ht="216" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B367" s="3">
         <v>4</v>
       </c>
       <c r="C367" s="3"/>
       <c r="D367" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E367" s="3"/>
       <c r="F367" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G367" s="3"/>
       <c r="H367" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="368" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B368" s="3">
         <v>5</v>
       </c>
       <c r="C368" s="15" t="s">
+        <v>836</v>
+      </c>
+      <c r="D368" s="14" t="s">
         <v>837</v>
-      </c>
-      <c r="D368" s="14" t="s">
-        <v>838</v>
       </c>
       <c r="E368" s="3"/>
       <c r="F368" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G368" s="3"/>
       <c r="H368" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="369" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B369" s="3">
         <v>4</v>
       </c>
       <c r="C369" s="3"/>
       <c r="D369" s="3" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E369" s="3"/>
       <c r="F369" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G369" s="3"/>
       <c r="H369" s="5" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="370" spans="1:8" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B370" s="3">
         <v>4</v>
       </c>
       <c r="C370" s="3"/>
       <c r="D370" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E370" s="3"/>
       <c r="F370" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G370" s="3"/>
       <c r="H370" s="5" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="371" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B371" s="3">
         <v>3</v>
       </c>
       <c r="C371" s="3"/>
       <c r="D371" s="3" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E371" s="3"/>
       <c r="F371" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G371" s="3"/>
       <c r="H371" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="372" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B372" s="3">
         <v>4</v>
       </c>
       <c r="C372" s="3"/>
       <c r="D372" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E372" s="3"/>
       <c r="F372" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G372" s="3"/>
       <c r="H372" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B373" s="3">
         <v>3</v>
       </c>
       <c r="C373" s="3"/>
       <c r="D373" s="3" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E373" s="3"/>
       <c r="F373" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G373" s="3"/>
       <c r="H373" s="5" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="374" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A374" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B374" s="7">
         <v>4</v>
       </c>
       <c r="C374" s="7"/>
       <c r="D374" s="7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E374" s="7"/>
       <c r="F374" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G374" s="7"/>
       <c r="H374" s="9" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
